--- a/RFQ Generator Beta Version/Templates/DE TEMPLATE.xlsx
+++ b/RFQ Generator Beta Version/Templates/DE TEMPLATE.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6BA627F3-EAD7-4866-AE23-D38B5805CA63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40C5827C-AF09-4AE1-8537-7DD3EB9EAE19}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{02CCD737-9343-44DD-A110-541534088332}"/>
   </bookViews>
@@ -19,7 +19,7 @@
     <definedName name="_xlnm.Print_Area" localSheetId="0">PRICED!$A$2:$T$45</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">PRICED!$2:$18</definedName>
   </definedNames>
-  <calcPr calcId="191029" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -176,10 +176,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
-    <numFmt numFmtId="171" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="180" formatCode="&quot;RM&quot;#,##0.00_);\(&quot;RM&quot;#,##0.00\)"/>
+    <numFmt numFmtId="164" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="165" formatCode="&quot;RM&quot;#,##0.00_);\(&quot;RM&quot;#,##0.00\)"/>
   </numFmts>
-  <fonts count="15" x14ac:knownFonts="1">
+  <fonts count="14" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -239,12 +239,6 @@
       <b/>
       <i/>
       <sz val="11"/>
-      <name val="Franklin Gothic Book"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color indexed="8"/>
       <name val="Franklin Gothic Book"/>
       <family val="2"/>
     </font>
@@ -424,24 +418,23 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="171" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="180" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="110">
+  <cellXfs count="98">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="justify"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -449,17 +442,10 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -467,18 +453,11 @@
     <xf numFmtId="14" fontId="4" fillId="0" borderId="3" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -487,11 +466,8 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -500,8 +476,6 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -509,7 +483,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="40" fontId="5" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -518,27 +492,19 @@
     <xf numFmtId="40" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="171" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="39" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="39" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -553,33 +519,67 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="5" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="5" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="4" fontId="5" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="4" fontId="5" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="4" fontId="5" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="4" fontId="5" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -637,45 +637,27 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="5" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="5" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -2068,24 +2050,24 @@
   <dimension ref="A2:W76"/>
   <sheetFormatPr defaultColWidth="3.6640625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="2" width="3.6640625" style="6" customWidth="1"/>
-    <col min="3" max="3" width="2.5546875" style="6" customWidth="1"/>
-    <col min="4" max="4" width="3.33203125" style="6" customWidth="1"/>
-    <col min="5" max="5" width="24.44140625" style="6" customWidth="1"/>
-    <col min="6" max="6" width="2.33203125" style="6" customWidth="1"/>
-    <col min="7" max="7" width="41" style="6" customWidth="1"/>
-    <col min="8" max="8" width="3.6640625" style="6" customWidth="1"/>
-    <col min="9" max="9" width="2.5546875" style="6" customWidth="1"/>
-    <col min="10" max="11" width="3.6640625" style="6" hidden="1" customWidth="1"/>
-    <col min="12" max="12" width="5.6640625" style="6" customWidth="1"/>
-    <col min="13" max="13" width="4" style="6" customWidth="1"/>
-    <col min="14" max="14" width="4.44140625" style="6" customWidth="1"/>
-    <col min="15" max="15" width="3.6640625" style="6" customWidth="1"/>
-    <col min="16" max="16" width="2.88671875" style="6" customWidth="1"/>
-    <col min="17" max="17" width="3.5546875" style="6" customWidth="1"/>
-    <col min="18" max="19" width="3.6640625" style="6" customWidth="1"/>
-    <col min="20" max="20" width="5.44140625" style="6" customWidth="1"/>
-    <col min="21" max="16384" width="3.6640625" style="6"/>
+    <col min="1" max="2" width="3.6640625" style="5" customWidth="1"/>
+    <col min="3" max="3" width="2.5546875" style="5" customWidth="1"/>
+    <col min="4" max="4" width="3.33203125" style="5" customWidth="1"/>
+    <col min="5" max="5" width="24.44140625" style="5" customWidth="1"/>
+    <col min="6" max="6" width="2.33203125" style="5" customWidth="1"/>
+    <col min="7" max="7" width="41" style="5" customWidth="1"/>
+    <col min="8" max="8" width="3.6640625" style="5" customWidth="1"/>
+    <col min="9" max="9" width="2.5546875" style="5" customWidth="1"/>
+    <col min="10" max="11" width="3.6640625" style="5" hidden="1" customWidth="1"/>
+    <col min="12" max="12" width="5.6640625" style="5" customWidth="1"/>
+    <col min="13" max="13" width="4" style="5" customWidth="1"/>
+    <col min="14" max="14" width="4.44140625" style="5" customWidth="1"/>
+    <col min="15" max="15" width="3.6640625" style="5" customWidth="1"/>
+    <col min="16" max="16" width="2.88671875" style="5" customWidth="1"/>
+    <col min="17" max="17" width="3.5546875" style="5" customWidth="1"/>
+    <col min="18" max="19" width="3.6640625" style="5" customWidth="1"/>
+    <col min="20" max="20" width="5.44140625" style="5" customWidth="1"/>
+    <col min="21" max="16384" width="3.6640625" style="5"/>
   </cols>
   <sheetData>
     <row r="2" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -2095,895 +2077,860 @@
       <c r="D2" s="2"/>
       <c r="E2" s="3"/>
       <c r="F2" s="4"/>
-      <c r="G2" s="5"/>
-      <c r="H2" s="5"/>
-      <c r="I2" s="5"/>
-      <c r="J2" s="5"/>
-      <c r="K2" s="5"/>
-      <c r="L2" s="5"/>
-      <c r="Q2" s="7"/>
-      <c r="R2" s="7"/>
-      <c r="S2" s="7"/>
-      <c r="T2" s="7"/>
+      <c r="Q2" s="6"/>
+      <c r="R2" s="6"/>
+      <c r="S2" s="6"/>
+      <c r="T2" s="6"/>
     </row>
     <row r="3" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="98"/>
-      <c r="B3" s="98"/>
-      <c r="C3" s="98"/>
-      <c r="D3" s="98"/>
-      <c r="E3" s="98"/>
-      <c r="F3" s="98"/>
-      <c r="G3" s="98"/>
-      <c r="H3" s="98"/>
-      <c r="I3" s="98"/>
-      <c r="J3" s="98"/>
-      <c r="K3" s="98"/>
-      <c r="L3" s="98"/>
-      <c r="M3" s="98"/>
-      <c r="N3" s="98"/>
-      <c r="O3" s="98"/>
-      <c r="P3" s="98"/>
-      <c r="Q3" s="98"/>
-      <c r="R3" s="98"/>
-      <c r="S3" s="98"/>
-      <c r="T3" s="98"/>
+      <c r="A3" s="63"/>
+      <c r="B3" s="63"/>
+      <c r="C3" s="63"/>
+      <c r="D3" s="63"/>
+      <c r="E3" s="63"/>
+      <c r="F3" s="63"/>
+      <c r="G3" s="63"/>
+      <c r="H3" s="63"/>
+      <c r="I3" s="63"/>
+      <c r="J3" s="63"/>
+      <c r="K3" s="63"/>
+      <c r="L3" s="63"/>
+      <c r="M3" s="63"/>
+      <c r="N3" s="63"/>
+      <c r="O3" s="63"/>
+      <c r="P3" s="63"/>
+      <c r="Q3" s="63"/>
+      <c r="R3" s="63"/>
+      <c r="S3" s="63"/>
+      <c r="T3" s="63"/>
     </row>
     <row r="4" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="99"/>
-      <c r="B4" s="99"/>
-      <c r="C4" s="99"/>
-      <c r="D4" s="99"/>
-      <c r="E4" s="99"/>
-      <c r="F4" s="99"/>
-      <c r="G4" s="99"/>
-      <c r="H4" s="99"/>
-      <c r="I4" s="99"/>
-      <c r="J4" s="99"/>
-      <c r="K4" s="99"/>
-      <c r="L4" s="99"/>
-      <c r="M4" s="99"/>
-      <c r="N4" s="99"/>
-      <c r="O4" s="99"/>
-      <c r="P4" s="99"/>
-      <c r="Q4" s="99"/>
-      <c r="R4" s="99"/>
-      <c r="S4" s="99"/>
-      <c r="T4" s="99"/>
-    </row>
-    <row r="5" spans="1:20" s="9" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="100"/>
-      <c r="B5" s="100"/>
-      <c r="C5" s="100"/>
-      <c r="D5" s="100"/>
-      <c r="E5" s="100"/>
-      <c r="F5" s="100"/>
-      <c r="G5" s="100"/>
-      <c r="H5" s="100"/>
-      <c r="I5" s="100"/>
-      <c r="J5" s="100"/>
-      <c r="K5" s="100"/>
-      <c r="L5" s="100"/>
-      <c r="M5" s="100"/>
-      <c r="N5" s="100"/>
-      <c r="O5" s="100"/>
-      <c r="P5" s="100"/>
-      <c r="Q5" s="100"/>
-      <c r="R5" s="100"/>
-      <c r="S5" s="100"/>
-      <c r="T5" s="100"/>
+      <c r="A4" s="64"/>
+      <c r="B4" s="64"/>
+      <c r="C4" s="64"/>
+      <c r="D4" s="64"/>
+      <c r="E4" s="64"/>
+      <c r="F4" s="64"/>
+      <c r="G4" s="64"/>
+      <c r="H4" s="64"/>
+      <c r="I4" s="64"/>
+      <c r="J4" s="64"/>
+      <c r="K4" s="64"/>
+      <c r="L4" s="64"/>
+      <c r="M4" s="64"/>
+      <c r="N4" s="64"/>
+      <c r="O4" s="64"/>
+      <c r="P4" s="64"/>
+      <c r="Q4" s="64"/>
+      <c r="R4" s="64"/>
+      <c r="S4" s="64"/>
+      <c r="T4" s="64"/>
+    </row>
+    <row r="5" spans="1:20" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="65"/>
+      <c r="B5" s="65"/>
+      <c r="C5" s="65"/>
+      <c r="D5" s="65"/>
+      <c r="E5" s="65"/>
+      <c r="F5" s="65"/>
+      <c r="G5" s="65"/>
+      <c r="H5" s="65"/>
+      <c r="I5" s="65"/>
+      <c r="J5" s="65"/>
+      <c r="K5" s="65"/>
+      <c r="L5" s="65"/>
+      <c r="M5" s="65"/>
+      <c r="N5" s="65"/>
+      <c r="O5" s="65"/>
+      <c r="P5" s="65"/>
+      <c r="Q5" s="65"/>
+      <c r="R5" s="65"/>
+      <c r="S5" s="65"/>
+      <c r="T5" s="65"/>
     </row>
     <row r="6" spans="1:20" ht="30.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="98"/>
-      <c r="B6" s="98"/>
-      <c r="C6" s="98"/>
-      <c r="D6" s="98"/>
-      <c r="E6" s="98"/>
-      <c r="F6" s="98"/>
-      <c r="G6" s="98"/>
-      <c r="H6" s="98"/>
-      <c r="I6" s="98"/>
-      <c r="J6" s="98"/>
-      <c r="K6" s="98"/>
-      <c r="L6" s="98"/>
-      <c r="M6" s="98"/>
-      <c r="N6" s="98"/>
-      <c r="O6" s="98"/>
-      <c r="P6" s="98"/>
-      <c r="Q6" s="98"/>
-      <c r="R6" s="98"/>
-      <c r="S6" s="98"/>
-      <c r="T6" s="98"/>
+      <c r="A6" s="63"/>
+      <c r="B6" s="63"/>
+      <c r="C6" s="63"/>
+      <c r="D6" s="63"/>
+      <c r="E6" s="63"/>
+      <c r="F6" s="63"/>
+      <c r="G6" s="63"/>
+      <c r="H6" s="63"/>
+      <c r="I6" s="63"/>
+      <c r="J6" s="63"/>
+      <c r="K6" s="63"/>
+      <c r="L6" s="63"/>
+      <c r="M6" s="63"/>
+      <c r="N6" s="63"/>
+      <c r="O6" s="63"/>
+      <c r="P6" s="63"/>
+      <c r="Q6" s="63"/>
+      <c r="R6" s="63"/>
+      <c r="S6" s="63"/>
+      <c r="T6" s="63"/>
     </row>
     <row r="7" spans="1:20" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="8"/>
-      <c r="B7" s="8"/>
-      <c r="C7" s="8"/>
-      <c r="D7" s="8"/>
-      <c r="E7" s="8"/>
-      <c r="F7" s="8"/>
-      <c r="G7" s="8"/>
-      <c r="H7" s="8"/>
-      <c r="I7" s="8"/>
-      <c r="J7" s="8"/>
-      <c r="K7" s="8"/>
-      <c r="L7" s="8"/>
-      <c r="M7" s="8"/>
-      <c r="N7" s="8"/>
-      <c r="O7" s="8"/>
-      <c r="P7" s="8"/>
-      <c r="Q7" s="8"/>
-      <c r="R7" s="8"/>
-      <c r="S7" s="8"/>
-      <c r="T7" s="8"/>
+      <c r="A7" s="7"/>
+      <c r="B7" s="7"/>
+      <c r="C7" s="7"/>
+      <c r="D7" s="7"/>
+      <c r="E7" s="7"/>
+      <c r="F7" s="7"/>
+      <c r="G7" s="7"/>
+      <c r="H7" s="7"/>
+      <c r="I7" s="7"/>
+      <c r="J7" s="7"/>
+      <c r="K7" s="7"/>
+      <c r="L7" s="7"/>
+      <c r="M7" s="7"/>
+      <c r="N7" s="7"/>
+      <c r="O7" s="7"/>
+      <c r="P7" s="7"/>
+      <c r="Q7" s="7"/>
+      <c r="R7" s="7"/>
+      <c r="S7" s="7"/>
+      <c r="T7" s="7"/>
     </row>
     <row r="8" spans="1:20" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="8"/>
-      <c r="B8" s="8"/>
-      <c r="C8" s="8"/>
-      <c r="D8" s="8"/>
-      <c r="E8" s="8"/>
-      <c r="F8" s="8"/>
-      <c r="G8" s="8"/>
-      <c r="H8" s="8"/>
-      <c r="I8" s="8"/>
-      <c r="J8" s="8"/>
-      <c r="K8" s="8"/>
-      <c r="L8" s="8"/>
-      <c r="M8" s="8"/>
-      <c r="N8" s="8"/>
-      <c r="O8" s="8"/>
-      <c r="P8" s="8"/>
-      <c r="Q8" s="8"/>
-      <c r="R8" s="8"/>
-      <c r="S8" s="8"/>
-      <c r="T8" s="8"/>
+      <c r="A8" s="7"/>
+      <c r="B8" s="7"/>
+      <c r="C8" s="7"/>
+      <c r="D8" s="7"/>
+      <c r="E8" s="7"/>
+      <c r="F8" s="7"/>
+      <c r="G8" s="7"/>
+      <c r="H8" s="7"/>
+      <c r="I8" s="7"/>
+      <c r="J8" s="7"/>
+      <c r="K8" s="7"/>
+      <c r="L8" s="7"/>
+      <c r="M8" s="7"/>
+      <c r="N8" s="7"/>
+      <c r="O8" s="7"/>
+      <c r="P8" s="7"/>
+      <c r="Q8" s="7"/>
+      <c r="R8" s="7"/>
+      <c r="S8" s="7"/>
+      <c r="T8" s="7"/>
     </row>
     <row r="9" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="8"/>
-      <c r="B9" s="8"/>
-      <c r="C9" s="8"/>
-      <c r="D9" s="8"/>
-      <c r="E9" s="8"/>
-      <c r="F9" s="8"/>
-      <c r="G9" s="8"/>
-      <c r="H9" s="8"/>
-      <c r="I9" s="8"/>
-      <c r="J9" s="8"/>
-      <c r="K9" s="8"/>
-      <c r="L9" s="8"/>
-      <c r="M9" s="8"/>
-      <c r="N9" s="8"/>
-      <c r="O9" s="8"/>
-      <c r="P9" s="8"/>
-      <c r="Q9" s="8"/>
-      <c r="R9" s="8"/>
-      <c r="S9" s="8"/>
-      <c r="T9" s="8"/>
+      <c r="A9" s="7"/>
+      <c r="B9" s="7"/>
+      <c r="C9" s="7"/>
+      <c r="D9" s="7"/>
+      <c r="E9" s="7"/>
+      <c r="F9" s="7"/>
+      <c r="G9" s="7"/>
+      <c r="H9" s="7"/>
+      <c r="I9" s="7"/>
+      <c r="J9" s="7"/>
+      <c r="K9" s="7"/>
+      <c r="L9" s="7"/>
+      <c r="M9" s="7"/>
+      <c r="N9" s="7"/>
+      <c r="O9" s="7"/>
+      <c r="P9" s="7"/>
+      <c r="Q9" s="7"/>
+      <c r="R9" s="7"/>
+      <c r="S9" s="7"/>
+      <c r="T9" s="7"/>
     </row>
     <row r="10" spans="1:20" ht="6" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="10"/>
-      <c r="B10" s="10"/>
-      <c r="C10" s="10"/>
-      <c r="D10" s="10"/>
-      <c r="E10" s="10"/>
-      <c r="F10" s="10"/>
-      <c r="G10" s="10"/>
-      <c r="H10" s="10"/>
-      <c r="I10" s="10"/>
-      <c r="J10" s="10"/>
-      <c r="K10" s="10"/>
-      <c r="L10" s="10"/>
-      <c r="M10" s="10"/>
-      <c r="N10" s="10"/>
-      <c r="O10" s="10"/>
-      <c r="P10" s="10"/>
-      <c r="Q10" s="10"/>
-      <c r="R10" s="10"/>
-      <c r="S10" s="10"/>
-      <c r="T10" s="10"/>
+      <c r="A10" s="8"/>
+      <c r="B10" s="8"/>
+      <c r="C10" s="8"/>
+      <c r="D10" s="8"/>
+      <c r="E10" s="8"/>
+      <c r="F10" s="8"/>
+      <c r="G10" s="8"/>
+      <c r="H10" s="8"/>
+      <c r="I10" s="8"/>
+      <c r="J10" s="8"/>
+      <c r="K10" s="8"/>
+      <c r="L10" s="8"/>
+      <c r="M10" s="8"/>
+      <c r="N10" s="8"/>
+      <c r="O10" s="8"/>
+      <c r="P10" s="8"/>
+      <c r="Q10" s="8"/>
+      <c r="R10" s="8"/>
+      <c r="S10" s="8"/>
+      <c r="T10" s="8"/>
     </row>
     <row r="11" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="11" t="s">
+      <c r="A11" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="B11" s="12"/>
-      <c r="C11" s="13" t="s">
+      <c r="B11" s="10"/>
+      <c r="C11" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D11" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="E11" s="14"/>
-      <c r="F11" s="14"/>
-      <c r="G11" s="14"/>
-      <c r="H11" s="15" t="s">
+      <c r="H11" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="I11" s="15"/>
-      <c r="J11" s="16"/>
-      <c r="K11" s="17" t="s">
+      <c r="I11" s="11"/>
+      <c r="J11" s="12"/>
+      <c r="K11" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="M11" s="13" t="s">
+      <c r="M11" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="N11" s="18" t="s">
+      <c r="N11" s="14" t="s">
         <v>33</v>
       </c>
-      <c r="S11" s="12"/>
-      <c r="T11" s="19"/>
+      <c r="S11" s="10"/>
+      <c r="T11" s="15"/>
     </row>
     <row r="12" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="20" t="s">
+      <c r="A12" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="B12" s="14"/>
-      <c r="C12" s="13" t="s">
+      <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D12" s="50"/>
+      <c r="D12" s="37"/>
       <c r="E12" s="1"/>
-      <c r="G12" s="14"/>
-      <c r="H12" s="21" t="s">
+      <c r="H12" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="I12" s="21"/>
-      <c r="J12" s="15"/>
-      <c r="K12" s="13" t="s">
+      <c r="I12" s="11"/>
+      <c r="J12" s="11"/>
+      <c r="K12" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="M12" s="13" t="s">
+      <c r="M12" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="N12" s="101" t="s">
+      <c r="N12" s="66" t="s">
         <v>36</v>
       </c>
-      <c r="O12" s="101"/>
-      <c r="P12" s="101"/>
-      <c r="Q12" s="101"/>
-      <c r="R12" s="101"/>
-      <c r="S12" s="101"/>
-      <c r="T12" s="22"/>
+      <c r="O12" s="66"/>
+      <c r="P12" s="66"/>
+      <c r="Q12" s="66"/>
+      <c r="R12" s="66"/>
+      <c r="S12" s="66"/>
+      <c r="T12" s="17"/>
     </row>
     <row r="13" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="20" t="s">
+      <c r="A13" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="B13" s="14"/>
-      <c r="C13" s="13" t="s">
+      <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D13" s="14"/>
-      <c r="E13" s="14"/>
-      <c r="F13" s="14"/>
-      <c r="G13" s="14"/>
-      <c r="H13" s="15" t="s">
+      <c r="H13" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="I13" s="15"/>
-      <c r="J13" s="15"/>
-      <c r="K13" s="13" t="s">
+      <c r="I13" s="11"/>
+      <c r="J13" s="11"/>
+      <c r="K13" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="M13" s="13" t="s">
+      <c r="M13" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="N13" s="24" t="s">
+      <c r="N13" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="S13" s="24"/>
-      <c r="T13" s="25"/>
+      <c r="T13" s="17"/>
     </row>
     <row r="14" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="20" t="s">
+      <c r="A14" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="B14" s="14"/>
-      <c r="C14" s="13" t="s">
+      <c r="C14" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D14" s="5"/>
       <c r="E14" s="1"/>
-      <c r="G14" s="14"/>
-      <c r="H14" s="14"/>
-      <c r="I14" s="14"/>
-      <c r="K14" s="102"/>
-      <c r="L14" s="103"/>
-      <c r="M14" s="103"/>
-      <c r="N14" s="103"/>
-      <c r="O14" s="13"/>
-      <c r="P14" s="26"/>
-      <c r="Q14" s="13"/>
-      <c r="R14" s="27"/>
-      <c r="S14" s="14"/>
-      <c r="T14" s="28"/>
+      <c r="K14" s="67"/>
+      <c r="L14" s="68"/>
+      <c r="M14" s="68"/>
+      <c r="N14" s="68"/>
+      <c r="O14" s="1"/>
+      <c r="P14" s="19"/>
+      <c r="Q14" s="1"/>
+      <c r="R14" s="1"/>
+      <c r="T14" s="17"/>
     </row>
     <row r="15" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A15" s="29" t="s">
+      <c r="A15" s="20" t="s">
         <v>7</v>
       </c>
-      <c r="B15" s="10"/>
-      <c r="C15" s="30" t="s">
+      <c r="B15" s="8"/>
+      <c r="C15" s="21" t="s">
         <v>8</v>
       </c>
-      <c r="D15" s="10" t="s">
+      <c r="D15" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="E15" s="31"/>
-      <c r="F15" s="31"/>
-      <c r="G15" s="31"/>
-      <c r="H15" s="10"/>
-      <c r="I15" s="10"/>
-      <c r="J15" s="10"/>
-      <c r="K15" s="10"/>
-      <c r="L15" s="32"/>
-      <c r="M15" s="10"/>
-      <c r="N15" s="89" t="s">
+      <c r="E15" s="22"/>
+      <c r="F15" s="22"/>
+      <c r="G15" s="22"/>
+      <c r="H15" s="8"/>
+      <c r="I15" s="8"/>
+      <c r="J15" s="8"/>
+      <c r="K15" s="8"/>
+      <c r="L15" s="23"/>
+      <c r="M15" s="8"/>
+      <c r="N15" s="83" t="s">
         <v>26</v>
       </c>
-      <c r="O15" s="89"/>
-      <c r="P15" s="89"/>
-      <c r="Q15" s="89"/>
-      <c r="R15" s="89"/>
-      <c r="S15" s="89"/>
-      <c r="T15" s="90"/>
+      <c r="O15" s="83"/>
+      <c r="P15" s="83"/>
+      <c r="Q15" s="83"/>
+      <c r="R15" s="83"/>
+      <c r="S15" s="83"/>
+      <c r="T15" s="84"/>
     </row>
     <row r="16" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="74"/>
-      <c r="B16" s="14"/>
-      <c r="C16" s="13"/>
-      <c r="D16" s="14"/>
-      <c r="E16" s="33"/>
-      <c r="F16" s="33"/>
-      <c r="G16" s="33"/>
-      <c r="H16" s="14"/>
-      <c r="I16" s="14"/>
-      <c r="J16" s="14"/>
-      <c r="K16" s="14"/>
-      <c r="L16" s="23"/>
-      <c r="M16" s="14"/>
-      <c r="N16" s="34"/>
-      <c r="O16" s="34"/>
-      <c r="P16" s="34"/>
-      <c r="Q16" s="34"/>
-      <c r="R16" s="34"/>
-      <c r="S16" s="34"/>
-      <c r="T16" s="34"/>
-    </row>
-    <row r="17" spans="1:21" s="35" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="85" t="s">
+      <c r="A16" s="54"/>
+      <c r="C16" s="1"/>
+      <c r="E16" s="24"/>
+      <c r="F16" s="24"/>
+      <c r="G16" s="24"/>
+      <c r="L16" s="18"/>
+      <c r="N16" s="7"/>
+      <c r="O16" s="7"/>
+      <c r="P16" s="7"/>
+      <c r="Q16" s="7"/>
+      <c r="R16" s="7"/>
+      <c r="S16" s="7"/>
+      <c r="T16" s="7"/>
+    </row>
+    <row r="17" spans="1:20" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="79" t="s">
         <v>0</v>
       </c>
-      <c r="B17" s="78"/>
-      <c r="C17" s="78" t="s">
+      <c r="B17" s="72"/>
+      <c r="C17" s="72" t="s">
         <v>18</v>
       </c>
-      <c r="D17" s="78"/>
-      <c r="E17" s="80" t="s">
+      <c r="D17" s="72"/>
+      <c r="E17" s="74" t="s">
         <v>1</v>
       </c>
-      <c r="F17" s="81"/>
-      <c r="G17" s="82"/>
-      <c r="H17" s="85" t="s">
+      <c r="F17" s="75"/>
+      <c r="G17" s="76"/>
+      <c r="H17" s="79" t="s">
         <v>20</v>
       </c>
-      <c r="I17" s="91"/>
-      <c r="J17" s="91"/>
-      <c r="K17" s="91"/>
-      <c r="L17" s="92"/>
-      <c r="M17" s="85" t="s">
+      <c r="I17" s="85"/>
+      <c r="J17" s="85"/>
+      <c r="K17" s="85"/>
+      <c r="L17" s="86"/>
+      <c r="M17" s="79" t="s">
         <v>2</v>
       </c>
-      <c r="N17" s="78"/>
-      <c r="O17" s="78"/>
-      <c r="P17" s="86"/>
-      <c r="Q17" s="85" t="s">
+      <c r="N17" s="72"/>
+      <c r="O17" s="72"/>
+      <c r="P17" s="80"/>
+      <c r="Q17" s="79" t="s">
         <v>11</v>
       </c>
-      <c r="R17" s="78"/>
-      <c r="S17" s="78"/>
-      <c r="T17" s="86"/>
-    </row>
-    <row r="18" spans="1:21" s="35" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="87"/>
-      <c r="B18" s="79"/>
-      <c r="C18" s="79"/>
-      <c r="D18" s="79"/>
-      <c r="E18" s="83"/>
-      <c r="F18" s="83"/>
-      <c r="G18" s="84"/>
-      <c r="H18" s="93"/>
-      <c r="I18" s="94"/>
-      <c r="J18" s="94"/>
-      <c r="K18" s="94"/>
-      <c r="L18" s="95"/>
-      <c r="M18" s="87"/>
-      <c r="N18" s="79"/>
-      <c r="O18" s="79"/>
-      <c r="P18" s="88"/>
-      <c r="Q18" s="87"/>
-      <c r="R18" s="79"/>
-      <c r="S18" s="79"/>
-      <c r="T18" s="88"/>
-    </row>
-    <row r="19" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="63"/>
-      <c r="B19" s="64"/>
-      <c r="C19" s="63"/>
-      <c r="D19" s="64"/>
-      <c r="E19" s="65"/>
-      <c r="F19" s="65"/>
-      <c r="G19" s="65"/>
-      <c r="H19" s="63"/>
-      <c r="I19" s="66"/>
-      <c r="J19" s="66"/>
-      <c r="K19" s="66"/>
-      <c r="L19" s="64"/>
-      <c r="M19" s="63"/>
-      <c r="N19" s="66"/>
-      <c r="O19" s="66"/>
-      <c r="P19" s="66"/>
-      <c r="Q19" s="63"/>
-      <c r="R19" s="66"/>
-      <c r="S19" s="66"/>
-      <c r="T19" s="64"/>
-    </row>
-    <row r="20" spans="1:21" s="39" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="96">
+      <c r="R17" s="72"/>
+      <c r="S17" s="72"/>
+      <c r="T17" s="80"/>
+    </row>
+    <row r="18" spans="1:20" s="25" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="81"/>
+      <c r="B18" s="73"/>
+      <c r="C18" s="73"/>
+      <c r="D18" s="73"/>
+      <c r="E18" s="77"/>
+      <c r="F18" s="77"/>
+      <c r="G18" s="78"/>
+      <c r="H18" s="87"/>
+      <c r="I18" s="88"/>
+      <c r="J18" s="88"/>
+      <c r="K18" s="88"/>
+      <c r="L18" s="89"/>
+      <c r="M18" s="81"/>
+      <c r="N18" s="73"/>
+      <c r="O18" s="73"/>
+      <c r="P18" s="82"/>
+      <c r="Q18" s="81"/>
+      <c r="R18" s="73"/>
+      <c r="S18" s="73"/>
+      <c r="T18" s="82"/>
+    </row>
+    <row r="19" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="47"/>
+      <c r="B19" s="48"/>
+      <c r="C19" s="47"/>
+      <c r="D19" s="48"/>
+      <c r="E19" s="49"/>
+      <c r="F19" s="49"/>
+      <c r="G19" s="49"/>
+      <c r="H19" s="47"/>
+      <c r="I19" s="50"/>
+      <c r="J19" s="50"/>
+      <c r="K19" s="50"/>
+      <c r="L19" s="48"/>
+      <c r="M19" s="47"/>
+      <c r="N19" s="50"/>
+      <c r="O19" s="50"/>
+      <c r="P19" s="50"/>
+      <c r="Q19" s="47"/>
+      <c r="R19" s="50"/>
+      <c r="S19" s="50"/>
+      <c r="T19" s="48"/>
+    </row>
+    <row r="20" spans="1:20" s="18" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="55">
         <v>1</v>
       </c>
-      <c r="B20" s="97"/>
-      <c r="C20" s="96">
+      <c r="B20" s="56"/>
+      <c r="C20" s="55">
         <v>1</v>
       </c>
-      <c r="D20" s="97"/>
-      <c r="E20" s="39" t="s">
+      <c r="D20" s="56"/>
+      <c r="E20" s="90" t="s">
         <v>38</v>
       </c>
-      <c r="F20" s="38"/>
-      <c r="G20" s="38"/>
-      <c r="H20" s="104">
+      <c r="F20" s="69"/>
+      <c r="G20" s="91"/>
+      <c r="H20" s="57">
         <v>8</v>
       </c>
-      <c r="I20" s="105"/>
-      <c r="J20" s="105"/>
-      <c r="K20" s="105"/>
-      <c r="L20" s="106"/>
-      <c r="M20" s="107">
+      <c r="I20" s="58"/>
+      <c r="J20" s="58"/>
+      <c r="K20" s="58"/>
+      <c r="L20" s="59"/>
+      <c r="M20" s="60">
         <v>480</v>
       </c>
-      <c r="N20" s="108"/>
-      <c r="O20" s="108"/>
-      <c r="P20" s="109"/>
-      <c r="Q20" s="107">
+      <c r="N20" s="61"/>
+      <c r="O20" s="61"/>
+      <c r="P20" s="62"/>
+      <c r="Q20" s="60">
         <f>M20*C20</f>
         <v>480</v>
       </c>
-      <c r="R20" s="108"/>
-      <c r="S20" s="108"/>
-      <c r="T20" s="109"/>
-      <c r="U20" s="69"/>
-    </row>
-    <row r="21" spans="1:21" s="39" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="36"/>
-      <c r="B21" s="37"/>
-      <c r="C21" s="96" t="s">
+      <c r="R20" s="61"/>
+      <c r="S20" s="61"/>
+      <c r="T20" s="62"/>
+    </row>
+    <row r="21" spans="1:20" s="18" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="26"/>
+      <c r="B21" s="27"/>
+      <c r="C21" s="55" t="s">
         <v>35</v>
       </c>
-      <c r="D21" s="97"/>
-      <c r="F21" s="38"/>
-      <c r="G21" s="38"/>
-      <c r="H21" s="104" t="s">
+      <c r="D21" s="56"/>
+      <c r="E21" s="90"/>
+      <c r="F21" s="69"/>
+      <c r="G21" s="91"/>
+      <c r="H21" s="57" t="s">
         <v>34</v>
       </c>
-      <c r="I21" s="105"/>
-      <c r="J21" s="105"/>
-      <c r="K21" s="105"/>
-      <c r="L21" s="106"/>
-      <c r="M21" s="67"/>
-      <c r="N21" s="67"/>
-      <c r="O21" s="67"/>
-      <c r="P21" s="68"/>
-      <c r="Q21" s="67"/>
-      <c r="R21" s="67"/>
-      <c r="S21" s="67"/>
-      <c r="T21" s="68"/>
-      <c r="U21" s="69"/>
-    </row>
-    <row r="22" spans="1:21" s="39" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="36"/>
-      <c r="B22" s="37"/>
-      <c r="C22" s="36"/>
-      <c r="D22" s="37"/>
-      <c r="F22" s="38"/>
-      <c r="G22" s="38"/>
-      <c r="H22" s="62"/>
-      <c r="I22" s="60"/>
-      <c r="J22" s="60"/>
-      <c r="K22" s="60"/>
-      <c r="L22" s="61"/>
-      <c r="M22" s="67"/>
-      <c r="N22" s="67"/>
-      <c r="O22" s="67"/>
-      <c r="P22" s="68"/>
-      <c r="Q22" s="67"/>
-      <c r="R22" s="67"/>
-      <c r="S22" s="67"/>
-      <c r="T22" s="68"/>
-      <c r="U22" s="69"/>
-    </row>
-    <row r="23" spans="1:21" s="39" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="36"/>
-      <c r="B23" s="37"/>
-      <c r="C23" s="36"/>
-      <c r="D23" s="37"/>
-      <c r="E23" s="59"/>
-      <c r="F23" s="49"/>
-      <c r="G23" s="54"/>
-      <c r="H23" s="36"/>
-      <c r="I23" s="60"/>
-      <c r="J23" s="60"/>
-      <c r="K23" s="60"/>
-      <c r="L23" s="61"/>
-      <c r="M23" s="67"/>
-      <c r="N23" s="67"/>
-      <c r="O23" s="67"/>
-      <c r="P23" s="68"/>
-      <c r="Q23" s="67"/>
-      <c r="R23" s="67"/>
-      <c r="S23" s="67"/>
-      <c r="T23" s="68"/>
-      <c r="U23" s="69"/>
-    </row>
-    <row r="24" spans="1:21" s="39" customFormat="1" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A24" s="51"/>
-      <c r="B24" s="52"/>
-      <c r="C24" s="52"/>
-      <c r="D24" s="52"/>
-      <c r="E24" s="52"/>
-      <c r="F24" s="52"/>
-      <c r="G24" s="52"/>
-      <c r="H24" s="53" t="s">
+      <c r="I21" s="58"/>
+      <c r="J21" s="58"/>
+      <c r="K21" s="58"/>
+      <c r="L21" s="59"/>
+      <c r="M21" s="55"/>
+      <c r="N21" s="63"/>
+      <c r="O21" s="63"/>
+      <c r="P21" s="56"/>
+      <c r="Q21" s="55"/>
+      <c r="R21" s="63"/>
+      <c r="S21" s="63"/>
+      <c r="T21" s="56"/>
+    </row>
+    <row r="22" spans="1:20" s="18" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="26"/>
+      <c r="B22" s="27"/>
+      <c r="C22" s="26"/>
+      <c r="D22" s="27"/>
+      <c r="E22" s="90"/>
+      <c r="F22" s="69"/>
+      <c r="G22" s="91"/>
+      <c r="H22" s="46"/>
+      <c r="I22" s="44"/>
+      <c r="J22" s="44"/>
+      <c r="K22" s="44"/>
+      <c r="L22" s="45"/>
+      <c r="M22" s="55"/>
+      <c r="N22" s="63"/>
+      <c r="O22" s="63"/>
+      <c r="P22" s="56"/>
+      <c r="Q22" s="55"/>
+      <c r="R22" s="63"/>
+      <c r="S22" s="63"/>
+      <c r="T22" s="56"/>
+    </row>
+    <row r="23" spans="1:20" s="18" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A23" s="26"/>
+      <c r="B23" s="27"/>
+      <c r="C23" s="26"/>
+      <c r="D23" s="27"/>
+      <c r="E23" s="92"/>
+      <c r="F23" s="93"/>
+      <c r="G23" s="94"/>
+      <c r="H23" s="26"/>
+      <c r="I23" s="44"/>
+      <c r="J23" s="44"/>
+      <c r="K23" s="44"/>
+      <c r="L23" s="45"/>
+      <c r="M23" s="95"/>
+      <c r="N23" s="96"/>
+      <c r="O23" s="96"/>
+      <c r="P23" s="97"/>
+      <c r="Q23" s="95"/>
+      <c r="R23" s="96"/>
+      <c r="S23" s="96"/>
+      <c r="T23" s="97"/>
+    </row>
+    <row r="24" spans="1:20" s="18" customFormat="1" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A24" s="38"/>
+      <c r="B24" s="39"/>
+      <c r="C24" s="39"/>
+      <c r="D24" s="39"/>
+      <c r="E24" s="39"/>
+      <c r="F24" s="39"/>
+      <c r="G24" s="39"/>
+      <c r="H24" s="40" t="s">
         <v>23</v>
       </c>
-      <c r="I24" s="52"/>
-      <c r="J24" s="53" t="s">
+      <c r="I24" s="39"/>
+      <c r="J24" s="40" t="s">
         <v>19</v>
       </c>
-      <c r="K24" s="52"/>
-      <c r="L24" s="52"/>
-      <c r="M24" s="70"/>
-      <c r="N24" s="70"/>
-      <c r="O24" s="70"/>
-      <c r="P24" s="71"/>
-      <c r="Q24" s="76">
+      <c r="K24" s="39"/>
+      <c r="L24" s="39"/>
+      <c r="M24" s="39"/>
+      <c r="N24" s="39"/>
+      <c r="O24" s="39"/>
+      <c r="P24" s="51"/>
+      <c r="Q24" s="70">
         <f>SUM(Q20:T23)</f>
         <v>480</v>
       </c>
-      <c r="R24" s="76"/>
-      <c r="S24" s="76"/>
-      <c r="T24" s="77"/>
-      <c r="U24" s="69"/>
-    </row>
-    <row r="25" spans="1:21" s="39" customFormat="1" ht="18" customHeight="1" thickTop="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="24"/>
-      <c r="B25" s="24"/>
-      <c r="C25" s="24"/>
-      <c r="D25" s="24"/>
-      <c r="E25" s="24"/>
-      <c r="F25" s="24"/>
-      <c r="G25" s="24"/>
-      <c r="H25" s="55"/>
-      <c r="I25" s="24"/>
-      <c r="J25" s="55"/>
-      <c r="K25" s="24"/>
-      <c r="L25" s="24"/>
-      <c r="M25" s="24"/>
-      <c r="N25" s="24"/>
-      <c r="O25" s="24"/>
-      <c r="P25" s="56"/>
-      <c r="Q25" s="57"/>
-      <c r="R25" s="57"/>
-      <c r="S25" s="57"/>
-      <c r="T25" s="57"/>
-    </row>
-    <row r="26" spans="1:21" s="39" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A26" s="41" t="s">
+      <c r="R24" s="70"/>
+      <c r="S24" s="70"/>
+      <c r="T24" s="71"/>
+    </row>
+    <row r="25" spans="1:20" s="18" customFormat="1" ht="18" customHeight="1" thickTop="1" x14ac:dyDescent="0.35">
+      <c r="A25" s="5"/>
+      <c r="B25" s="5"/>
+      <c r="C25" s="5"/>
+      <c r="D25" s="5"/>
+      <c r="E25" s="5"/>
+      <c r="F25" s="5"/>
+      <c r="G25" s="5"/>
+      <c r="I25" s="5"/>
+      <c r="K25" s="5"/>
+      <c r="L25" s="5"/>
+      <c r="M25" s="5"/>
+      <c r="N25" s="5"/>
+      <c r="O25" s="5"/>
+      <c r="P25" s="41"/>
+      <c r="Q25" s="42"/>
+      <c r="R25" s="42"/>
+      <c r="S25" s="42"/>
+      <c r="T25" s="42"/>
+    </row>
+    <row r="26" spans="1:20" s="18" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A26" s="29" t="s">
         <v>12</v>
       </c>
-      <c r="B26" s="12"/>
-      <c r="C26" s="12"/>
-      <c r="D26" s="12"/>
-      <c r="E26" s="12"/>
-      <c r="F26" s="17" t="s">
+      <c r="B26" s="10"/>
+      <c r="C26" s="10"/>
+      <c r="D26" s="10"/>
+      <c r="E26" s="10"/>
+      <c r="F26" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="G26" s="12" t="s">
+      <c r="G26" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="H26" s="12"/>
-      <c r="I26" s="12"/>
-      <c r="J26" s="12"/>
-      <c r="K26" s="12"/>
-      <c r="L26" s="12"/>
-      <c r="M26" s="12"/>
-      <c r="N26" s="12"/>
-      <c r="O26" s="12"/>
-      <c r="P26" s="12"/>
-      <c r="Q26" s="12"/>
-      <c r="R26" s="12"/>
-      <c r="S26" s="12"/>
-      <c r="T26" s="19"/>
-    </row>
-    <row r="27" spans="1:21" s="39" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A27" s="42" t="s">
+      <c r="H26" s="10"/>
+      <c r="I26" s="10"/>
+      <c r="J26" s="10"/>
+      <c r="K26" s="10"/>
+      <c r="L26" s="10"/>
+      <c r="M26" s="10"/>
+      <c r="N26" s="10"/>
+      <c r="O26" s="10"/>
+      <c r="P26" s="10"/>
+      <c r="Q26" s="10"/>
+      <c r="R26" s="10"/>
+      <c r="S26" s="10"/>
+      <c r="T26" s="15"/>
+    </row>
+    <row r="27" spans="1:20" s="18" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A27" s="30" t="s">
         <v>13</v>
       </c>
-      <c r="B27" s="6"/>
-      <c r="C27" s="6"/>
-      <c r="D27" s="6"/>
-      <c r="E27" s="6"/>
+      <c r="B27" s="5"/>
+      <c r="C27" s="5"/>
+      <c r="D27" s="5"/>
+      <c r="E27" s="5"/>
       <c r="F27" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="G27" s="6" t="s">
+      <c r="G27" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="H27" s="6"/>
-      <c r="I27" s="6"/>
-      <c r="J27" s="6"/>
-      <c r="K27" s="6"/>
-      <c r="L27" s="6"/>
-      <c r="M27" s="6"/>
-      <c r="N27" s="6"/>
-      <c r="O27" s="6"/>
-      <c r="P27" s="6"/>
-      <c r="Q27" s="6"/>
-      <c r="R27" s="6"/>
-      <c r="S27" s="6"/>
-      <c r="T27" s="28"/>
-    </row>
-    <row r="28" spans="1:21" s="39" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="42" t="s">
+      <c r="H27" s="5"/>
+      <c r="I27" s="5"/>
+      <c r="J27" s="5"/>
+      <c r="K27" s="5"/>
+      <c r="L27" s="5"/>
+      <c r="M27" s="5"/>
+      <c r="N27" s="5"/>
+      <c r="O27" s="5"/>
+      <c r="P27" s="5"/>
+      <c r="Q27" s="5"/>
+      <c r="R27" s="5"/>
+      <c r="S27" s="5"/>
+      <c r="T27" s="17"/>
+    </row>
+    <row r="28" spans="1:20" s="18" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A28" s="30" t="s">
         <v>14</v>
       </c>
-      <c r="B28" s="6"/>
-      <c r="C28" s="6"/>
-      <c r="D28" s="6"/>
-      <c r="E28" s="6"/>
+      <c r="B28" s="5"/>
+      <c r="C28" s="5"/>
+      <c r="D28" s="5"/>
+      <c r="E28" s="5"/>
       <c r="F28" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="G28" s="6" t="s">
+      <c r="G28" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="H28" s="6"/>
-      <c r="I28" s="6"/>
-      <c r="J28" s="6"/>
-      <c r="K28" s="6"/>
-      <c r="L28" s="6"/>
-      <c r="M28" s="6"/>
-      <c r="N28" s="6"/>
-      <c r="O28" s="6"/>
-      <c r="P28" s="6"/>
-      <c r="Q28" s="6"/>
-      <c r="R28" s="6"/>
-      <c r="S28" s="6"/>
-      <c r="T28" s="28"/>
-    </row>
-    <row r="29" spans="1:21" s="39" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="43" t="s">
+      <c r="H28" s="5"/>
+      <c r="I28" s="5"/>
+      <c r="J28" s="5"/>
+      <c r="K28" s="5"/>
+      <c r="L28" s="5"/>
+      <c r="M28" s="5"/>
+      <c r="N28" s="5"/>
+      <c r="O28" s="5"/>
+      <c r="P28" s="5"/>
+      <c r="Q28" s="5"/>
+      <c r="R28" s="5"/>
+      <c r="S28" s="5"/>
+      <c r="T28" s="17"/>
+    </row>
+    <row r="29" spans="1:20" s="18" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A29" s="31" t="s">
         <v>15</v>
       </c>
-      <c r="B29" s="10"/>
-      <c r="C29" s="10"/>
-      <c r="D29" s="10"/>
-      <c r="E29" s="10"/>
-      <c r="F29" s="30" t="s">
+      <c r="B29" s="8"/>
+      <c r="C29" s="8"/>
+      <c r="D29" s="8"/>
+      <c r="E29" s="8"/>
+      <c r="F29" s="21" t="s">
         <v>8</v>
       </c>
-      <c r="G29" s="10" t="s">
+      <c r="G29" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="H29" s="10"/>
-      <c r="I29" s="10"/>
-      <c r="J29" s="10"/>
-      <c r="K29" s="10"/>
-      <c r="L29" s="10"/>
-      <c r="M29" s="10"/>
-      <c r="N29" s="10"/>
-      <c r="O29" s="10"/>
-      <c r="P29" s="10"/>
-      <c r="Q29" s="10"/>
-      <c r="R29" s="10"/>
-      <c r="S29" s="10"/>
-      <c r="T29" s="44"/>
-    </row>
-    <row r="30" spans="1:21" s="39" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="6"/>
-      <c r="B30" s="6"/>
-      <c r="C30" s="6"/>
-      <c r="D30" s="6"/>
-      <c r="E30" s="6"/>
+      <c r="H29" s="8"/>
+      <c r="I29" s="8"/>
+      <c r="J29" s="8"/>
+      <c r="K29" s="8"/>
+      <c r="L29" s="8"/>
+      <c r="M29" s="8"/>
+      <c r="N29" s="8"/>
+      <c r="O29" s="8"/>
+      <c r="P29" s="8"/>
+      <c r="Q29" s="8"/>
+      <c r="R29" s="8"/>
+      <c r="S29" s="8"/>
+      <c r="T29" s="32"/>
+    </row>
+    <row r="30" spans="1:20" s="18" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A30" s="5"/>
+      <c r="B30" s="5"/>
+      <c r="C30" s="5"/>
+      <c r="D30" s="5"/>
+      <c r="E30" s="5"/>
       <c r="F30" s="1"/>
-      <c r="G30" s="6"/>
-      <c r="H30" s="6"/>
-      <c r="I30" s="6"/>
-      <c r="J30" s="6"/>
-      <c r="K30" s="6"/>
-      <c r="L30" s="6"/>
-      <c r="M30" s="6"/>
-      <c r="N30" s="6"/>
-      <c r="O30" s="6"/>
-      <c r="P30" s="6"/>
-      <c r="Q30" s="6"/>
-      <c r="R30" s="6"/>
-      <c r="S30" s="6"/>
-      <c r="T30" s="6"/>
-    </row>
-    <row r="31" spans="1:21" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A31" s="72" t="s">
+      <c r="G30" s="5"/>
+      <c r="H30" s="5"/>
+      <c r="I30" s="5"/>
+      <c r="J30" s="5"/>
+      <c r="K30" s="5"/>
+      <c r="L30" s="5"/>
+      <c r="M30" s="5"/>
+      <c r="N30" s="5"/>
+      <c r="O30" s="5"/>
+      <c r="P30" s="5"/>
+      <c r="Q30" s="5"/>
+      <c r="R30" s="5"/>
+      <c r="S30" s="5"/>
+      <c r="T30" s="5"/>
+    </row>
+    <row r="31" spans="1:20" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A31" s="52" t="s">
         <v>40</v>
       </c>
-      <c r="B31" s="72"/>
-      <c r="C31" s="72"/>
-      <c r="D31" s="72"/>
-      <c r="E31" s="72"/>
-      <c r="F31" s="72"/>
-      <c r="G31" s="72"/>
-      <c r="H31" s="72"/>
-      <c r="I31" s="72"/>
-      <c r="J31" s="72"/>
-    </row>
-    <row r="32" spans="1:21" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A32" s="72"/>
-      <c r="B32" s="72"/>
-      <c r="C32" s="72"/>
-      <c r="D32" s="72"/>
-      <c r="E32" s="72"/>
-      <c r="F32" s="72"/>
-      <c r="G32" s="72"/>
-      <c r="H32" s="72"/>
-      <c r="I32" s="72"/>
-      <c r="J32" s="72"/>
+      <c r="B31" s="52"/>
+      <c r="C31" s="52"/>
+      <c r="D31" s="52"/>
+      <c r="E31" s="52"/>
+      <c r="F31" s="52"/>
+      <c r="G31" s="52"/>
+      <c r="H31" s="52"/>
+      <c r="I31" s="52"/>
+      <c r="J31" s="52"/>
+    </row>
+    <row r="32" spans="1:20" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A32" s="52"/>
+      <c r="B32" s="52"/>
+      <c r="C32" s="52"/>
+      <c r="D32" s="52"/>
+      <c r="E32" s="52"/>
+      <c r="F32" s="52"/>
+      <c r="G32" s="52"/>
+      <c r="H32" s="52"/>
+      <c r="I32" s="52"/>
+      <c r="J32" s="52"/>
     </row>
     <row r="33" spans="1:20" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A33" s="73">
+      <c r="A33" s="53">
         <v>1</v>
       </c>
-      <c r="B33" s="72" t="s">
+      <c r="B33" s="52" t="s">
         <v>41</v>
       </c>
-      <c r="C33" s="72"/>
-      <c r="D33" s="72"/>
-      <c r="E33" s="72"/>
-      <c r="F33" s="72"/>
-      <c r="G33" s="72"/>
-      <c r="H33" s="72"/>
-      <c r="I33" s="72"/>
-      <c r="J33" s="72"/>
+      <c r="C33" s="52"/>
+      <c r="D33" s="52"/>
+      <c r="E33" s="52"/>
+      <c r="F33" s="52"/>
+      <c r="G33" s="52"/>
+      <c r="H33" s="52"/>
+      <c r="I33" s="52"/>
+      <c r="J33" s="52"/>
     </row>
     <row r="34" spans="1:20" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A34" s="73">
+      <c r="A34" s="53">
         <v>2</v>
       </c>
-      <c r="B34" s="72" t="s">
+      <c r="B34" s="52" t="s">
         <v>42</v>
       </c>
-      <c r="C34" s="72"/>
-      <c r="D34" s="72"/>
-      <c r="E34" s="72"/>
-      <c r="F34" s="72"/>
-      <c r="G34" s="72"/>
-      <c r="H34" s="72"/>
-      <c r="I34" s="72"/>
-      <c r="J34" s="72"/>
+      <c r="C34" s="52"/>
+      <c r="D34" s="52"/>
+      <c r="E34" s="52"/>
+      <c r="F34" s="52"/>
+      <c r="G34" s="52"/>
+      <c r="H34" s="52"/>
+      <c r="I34" s="52"/>
+      <c r="J34" s="52"/>
     </row>
     <row r="35" spans="1:20" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A35" s="73">
+      <c r="A35" s="53">
         <v>3</v>
       </c>
-      <c r="B35" s="72" t="s">
+      <c r="B35" s="52" t="s">
         <v>43</v>
       </c>
-      <c r="C35" s="72"/>
-      <c r="D35" s="72"/>
-      <c r="E35" s="72"/>
-      <c r="F35" s="72"/>
-      <c r="G35" s="72"/>
-      <c r="H35" s="72"/>
-      <c r="I35" s="72"/>
-      <c r="J35" s="72"/>
+      <c r="C35" s="52"/>
+      <c r="D35" s="52"/>
+      <c r="E35" s="52"/>
+      <c r="F35" s="52"/>
+      <c r="G35" s="52"/>
+      <c r="H35" s="52"/>
+      <c r="I35" s="52"/>
+      <c r="J35" s="52"/>
     </row>
     <row r="36" spans="1:20" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A36" s="72"/>
-      <c r="B36" s="72" t="s">
+      <c r="A36" s="52"/>
+      <c r="B36" s="52" t="s">
         <v>39</v>
       </c>
-      <c r="C36" s="72"/>
-      <c r="D36" s="72"/>
-      <c r="E36" s="72"/>
-      <c r="F36" s="72"/>
-      <c r="G36" s="72"/>
-      <c r="H36" s="72"/>
-      <c r="I36" s="72"/>
-      <c r="J36" s="72"/>
-    </row>
-    <row r="37" spans="1:20" s="39" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A37" s="6"/>
-      <c r="B37" s="6"/>
-      <c r="C37" s="6"/>
-      <c r="D37" s="6"/>
-      <c r="E37" s="6"/>
+      <c r="C36" s="52"/>
+      <c r="D36" s="52"/>
+      <c r="E36" s="52"/>
+      <c r="F36" s="52"/>
+      <c r="G36" s="52"/>
+      <c r="H36" s="52"/>
+      <c r="I36" s="52"/>
+      <c r="J36" s="52"/>
+    </row>
+    <row r="37" spans="1:20" s="18" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A37" s="5"/>
+      <c r="B37" s="5"/>
+      <c r="C37" s="5"/>
+      <c r="D37" s="5"/>
+      <c r="E37" s="5"/>
       <c r="F37" s="1"/>
-      <c r="G37" s="6"/>
-      <c r="H37" s="6"/>
-      <c r="I37" s="6"/>
-      <c r="J37" s="6"/>
-      <c r="K37" s="6"/>
-      <c r="L37" s="6"/>
-      <c r="M37" s="6"/>
-      <c r="N37" s="6"/>
-      <c r="O37" s="6"/>
-      <c r="P37" s="6"/>
-      <c r="Q37" s="6"/>
-      <c r="R37" s="6"/>
-      <c r="S37" s="6"/>
-      <c r="T37" s="6"/>
-    </row>
-    <row r="38" spans="1:20" s="39" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A38" s="6"/>
-      <c r="B38" s="6"/>
-      <c r="C38" s="6"/>
-      <c r="D38" s="6"/>
-      <c r="E38" s="6"/>
+      <c r="G37" s="5"/>
+      <c r="H37" s="5"/>
+      <c r="I37" s="5"/>
+      <c r="J37" s="5"/>
+      <c r="K37" s="5"/>
+      <c r="L37" s="5"/>
+      <c r="M37" s="5"/>
+      <c r="N37" s="5"/>
+      <c r="O37" s="5"/>
+      <c r="P37" s="5"/>
+      <c r="Q37" s="5"/>
+      <c r="R37" s="5"/>
+      <c r="S37" s="5"/>
+      <c r="T37" s="5"/>
+    </row>
+    <row r="38" spans="1:20" s="18" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A38" s="5"/>
+      <c r="B38" s="5"/>
+      <c r="C38" s="5"/>
+      <c r="D38" s="5"/>
+      <c r="E38" s="5"/>
       <c r="F38" s="1"/>
-      <c r="G38" s="6"/>
-      <c r="H38" s="6"/>
-      <c r="I38" s="6"/>
-      <c r="J38" s="6"/>
-      <c r="K38" s="6"/>
-      <c r="L38" s="6"/>
-      <c r="M38" s="6"/>
-      <c r="N38" s="6"/>
-      <c r="O38" s="6"/>
-      <c r="P38" s="6"/>
-      <c r="Q38" s="6"/>
-      <c r="R38" s="6"/>
-      <c r="S38" s="6"/>
-      <c r="T38" s="6"/>
-    </row>
-    <row r="39" spans="1:20" s="39" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A39" s="21" t="s">
+      <c r="G38" s="5"/>
+      <c r="H38" s="5"/>
+      <c r="I38" s="5"/>
+      <c r="J38" s="5"/>
+      <c r="K38" s="5"/>
+      <c r="L38" s="5"/>
+      <c r="M38" s="5"/>
+      <c r="N38" s="5"/>
+      <c r="O38" s="5"/>
+      <c r="P38" s="5"/>
+      <c r="Q38" s="5"/>
+      <c r="R38" s="5"/>
+      <c r="S38" s="5"/>
+      <c r="T38" s="5"/>
+    </row>
+    <row r="39" spans="1:20" s="18" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A39" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="B39" s="6"/>
-      <c r="C39" s="6"/>
-      <c r="D39" s="6"/>
-      <c r="E39" s="8"/>
-      <c r="F39" s="8"/>
-      <c r="G39" s="8"/>
-      <c r="H39" s="8"/>
-      <c r="I39" s="8"/>
-      <c r="J39" s="8"/>
-      <c r="K39" s="8"/>
-      <c r="L39" s="8"/>
-      <c r="M39" s="6"/>
-      <c r="N39" s="6"/>
-      <c r="O39" s="6"/>
-      <c r="P39" s="6"/>
-      <c r="Q39" s="6"/>
-      <c r="R39" s="6"/>
-      <c r="S39" s="6"/>
-      <c r="T39" s="6"/>
-    </row>
-    <row r="40" spans="1:20" s="39" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A40" s="6" t="s">
+      <c r="B39" s="5"/>
+      <c r="C39" s="5"/>
+      <c r="D39" s="5"/>
+      <c r="E39" s="7"/>
+      <c r="F39" s="7"/>
+      <c r="G39" s="7"/>
+      <c r="H39" s="7"/>
+      <c r="I39" s="7"/>
+      <c r="J39" s="7"/>
+      <c r="K39" s="7"/>
+      <c r="L39" s="7"/>
+      <c r="M39" s="5"/>
+      <c r="N39" s="5"/>
+      <c r="O39" s="5"/>
+      <c r="P39" s="5"/>
+      <c r="Q39" s="5"/>
+      <c r="R39" s="5"/>
+      <c r="S39" s="5"/>
+      <c r="T39" s="5"/>
+    </row>
+    <row r="40" spans="1:20" s="18" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A40" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="B40" s="6"/>
-      <c r="C40" s="6"/>
-      <c r="D40" s="6"/>
+      <c r="B40" s="5"/>
+      <c r="C40" s="5"/>
+      <c r="D40" s="5"/>
       <c r="E40" s="1"/>
       <c r="F40" s="1"/>
       <c r="G40" s="1"/>
@@ -2992,702 +2939,696 @@
       <c r="J40" s="1"/>
       <c r="K40" s="1"/>
       <c r="L40" s="1"/>
-      <c r="M40" s="6"/>
-      <c r="N40" s="6"/>
-      <c r="O40" s="6"/>
-      <c r="P40" s="6"/>
-      <c r="Q40" s="6"/>
-      <c r="R40" s="6"/>
-      <c r="S40" s="6"/>
-      <c r="T40" s="6"/>
-    </row>
-    <row r="41" spans="1:20" s="39" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A41" s="14"/>
-      <c r="B41" s="14"/>
-      <c r="C41" s="14"/>
-      <c r="D41" s="14"/>
-      <c r="E41" s="34"/>
-      <c r="F41" s="34"/>
-      <c r="G41" s="34"/>
-      <c r="H41" s="34"/>
-      <c r="I41" s="34"/>
-      <c r="J41" s="34"/>
-      <c r="K41" s="34"/>
-      <c r="L41" s="34"/>
-      <c r="M41" s="14"/>
-      <c r="N41" s="6"/>
-      <c r="O41" s="6"/>
-      <c r="P41" s="6"/>
-      <c r="Q41" s="6"/>
-      <c r="R41" s="6"/>
-      <c r="S41" s="6"/>
-      <c r="T41" s="6"/>
-    </row>
-    <row r="42" spans="1:20" s="39" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A42" s="58" t="s">
+      <c r="M40" s="5"/>
+      <c r="N40" s="5"/>
+      <c r="O40" s="5"/>
+      <c r="P40" s="5"/>
+      <c r="Q40" s="5"/>
+      <c r="R40" s="5"/>
+      <c r="S40" s="5"/>
+      <c r="T40" s="5"/>
+    </row>
+    <row r="41" spans="1:20" s="18" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A41" s="5"/>
+      <c r="B41" s="5"/>
+      <c r="C41" s="5"/>
+      <c r="D41" s="5"/>
+      <c r="E41" s="7"/>
+      <c r="F41" s="7"/>
+      <c r="G41" s="7"/>
+      <c r="H41" s="7"/>
+      <c r="I41" s="7"/>
+      <c r="J41" s="7"/>
+      <c r="K41" s="7"/>
+      <c r="L41" s="7"/>
+      <c r="M41" s="5"/>
+      <c r="N41" s="5"/>
+      <c r="O41" s="5"/>
+      <c r="P41" s="5"/>
+      <c r="Q41" s="5"/>
+      <c r="R41" s="5"/>
+      <c r="S41" s="5"/>
+      <c r="T41" s="5"/>
+    </row>
+    <row r="42" spans="1:20" s="18" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A42" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="B42" s="14"/>
-      <c r="C42" s="14"/>
-      <c r="D42" s="14"/>
-      <c r="E42" s="34"/>
-      <c r="F42" s="34"/>
-      <c r="G42" s="34"/>
-      <c r="H42" s="34"/>
-      <c r="I42" s="34"/>
-      <c r="J42" s="34"/>
-      <c r="K42" s="34"/>
-      <c r="L42" s="34"/>
-      <c r="M42" s="14"/>
-      <c r="N42" s="6"/>
-      <c r="O42" s="6"/>
-      <c r="P42" s="6"/>
-      <c r="Q42" s="6"/>
-      <c r="R42" s="6"/>
-      <c r="S42" s="6"/>
-      <c r="T42" s="6"/>
-    </row>
-    <row r="43" spans="1:20" s="39" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A43" s="14"/>
-      <c r="B43" s="14"/>
-      <c r="C43" s="14"/>
-      <c r="D43" s="14"/>
-      <c r="E43" s="14"/>
-      <c r="F43" s="14"/>
-      <c r="G43" s="14"/>
-      <c r="H43" s="14"/>
-      <c r="I43" s="14"/>
-      <c r="J43" s="14"/>
-      <c r="K43" s="14"/>
-      <c r="L43" s="14"/>
-      <c r="M43" s="14"/>
-      <c r="N43" s="6"/>
-      <c r="O43" s="6"/>
-      <c r="P43" s="6"/>
-      <c r="Q43" s="6"/>
-      <c r="R43" s="6"/>
-      <c r="S43" s="6"/>
-      <c r="T43" s="6"/>
-    </row>
-    <row r="44" spans="1:20" s="39" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A44" s="75" t="s">
+      <c r="B42" s="5"/>
+      <c r="C42" s="5"/>
+      <c r="D42" s="5"/>
+      <c r="E42" s="7"/>
+      <c r="F42" s="7"/>
+      <c r="G42" s="7"/>
+      <c r="H42" s="7"/>
+      <c r="I42" s="7"/>
+      <c r="J42" s="7"/>
+      <c r="K42" s="7"/>
+      <c r="L42" s="7"/>
+      <c r="M42" s="5"/>
+      <c r="N42" s="5"/>
+      <c r="O42" s="5"/>
+      <c r="P42" s="5"/>
+      <c r="Q42" s="5"/>
+      <c r="R42" s="5"/>
+      <c r="S42" s="5"/>
+      <c r="T42" s="5"/>
+    </row>
+    <row r="43" spans="1:20" s="18" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A43" s="5"/>
+      <c r="B43" s="5"/>
+      <c r="C43" s="5"/>
+      <c r="D43" s="5"/>
+      <c r="E43" s="5"/>
+      <c r="F43" s="5"/>
+      <c r="G43" s="5"/>
+      <c r="H43" s="5"/>
+      <c r="I43" s="5"/>
+      <c r="J43" s="5"/>
+      <c r="K43" s="5"/>
+      <c r="L43" s="5"/>
+      <c r="M43" s="5"/>
+      <c r="N43" s="5"/>
+      <c r="O43" s="5"/>
+      <c r="P43" s="5"/>
+      <c r="Q43" s="5"/>
+      <c r="R43" s="5"/>
+      <c r="S43" s="5"/>
+      <c r="T43" s="5"/>
+    </row>
+    <row r="44" spans="1:20" s="18" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A44" s="69" t="s">
         <v>31</v>
       </c>
-      <c r="B44" s="75"/>
-      <c r="C44" s="75"/>
-      <c r="D44" s="75"/>
-      <c r="E44" s="75"/>
-      <c r="F44" s="75"/>
-      <c r="G44" s="14"/>
-      <c r="H44" s="14"/>
-      <c r="I44" s="14"/>
-      <c r="J44" s="15"/>
-      <c r="K44" s="15"/>
-      <c r="L44" s="15"/>
-      <c r="M44" s="14"/>
-      <c r="N44" s="6"/>
-      <c r="O44" s="6"/>
-      <c r="P44" s="6"/>
-      <c r="Q44" s="6"/>
-      <c r="R44" s="6"/>
-      <c r="S44" s="6"/>
-      <c r="T44" s="6"/>
-    </row>
-    <row r="45" spans="1:20" s="39" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A45" s="45" t="s">
+      <c r="B44" s="69"/>
+      <c r="C44" s="69"/>
+      <c r="D44" s="69"/>
+      <c r="E44" s="69"/>
+      <c r="F44" s="69"/>
+      <c r="G44" s="5"/>
+      <c r="H44" s="5"/>
+      <c r="I44" s="5"/>
+      <c r="J44" s="11"/>
+      <c r="K44" s="11"/>
+      <c r="L44" s="11"/>
+      <c r="M44" s="5"/>
+      <c r="N44" s="5"/>
+      <c r="O44" s="5"/>
+      <c r="P44" s="5"/>
+      <c r="Q44" s="5"/>
+      <c r="R44" s="5"/>
+      <c r="S44" s="5"/>
+      <c r="T44" s="5"/>
+    </row>
+    <row r="45" spans="1:20" s="18" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A45" s="33" t="s">
         <v>25</v>
       </c>
-      <c r="B45" s="45"/>
-      <c r="C45" s="45"/>
-      <c r="D45" s="45"/>
-      <c r="E45" s="14"/>
-      <c r="F45" s="14"/>
-      <c r="G45" s="14"/>
-      <c r="H45" s="14"/>
-      <c r="I45" s="14"/>
-      <c r="J45" s="15"/>
-      <c r="K45" s="15"/>
-      <c r="L45" s="15"/>
-      <c r="M45" s="14"/>
-      <c r="N45" s="6"/>
-      <c r="O45" s="6"/>
-      <c r="P45" s="6"/>
-      <c r="Q45" s="6"/>
-      <c r="R45" s="6"/>
-      <c r="S45" s="6"/>
-      <c r="T45" s="6"/>
-    </row>
-    <row r="46" spans="1:20" s="39" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A46" s="6"/>
-      <c r="B46" s="6"/>
-      <c r="C46" s="6"/>
-      <c r="D46" s="6"/>
-      <c r="E46" s="6"/>
-      <c r="F46" s="6"/>
-      <c r="G46" s="6"/>
-      <c r="H46" s="6"/>
-      <c r="I46" s="6"/>
-      <c r="J46" s="6"/>
-      <c r="K46" s="6"/>
-      <c r="L46" s="6"/>
-      <c r="M46" s="6"/>
-      <c r="N46" s="6"/>
-      <c r="O46" s="6"/>
-      <c r="P46" s="6"/>
-      <c r="Q46" s="6"/>
-      <c r="R46" s="6"/>
-      <c r="S46" s="6"/>
-      <c r="T46" s="6"/>
-    </row>
-    <row r="47" spans="1:20" s="39" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A47" s="6"/>
-      <c r="B47" s="6"/>
-      <c r="C47" s="6"/>
-      <c r="D47" s="6"/>
-      <c r="E47" s="6"/>
-      <c r="F47" s="6"/>
-      <c r="G47" s="6"/>
-      <c r="H47" s="6"/>
-      <c r="I47" s="6"/>
-      <c r="J47" s="6"/>
-      <c r="K47" s="6"/>
-      <c r="L47" s="6"/>
-      <c r="M47" s="6"/>
-      <c r="N47" s="6"/>
-      <c r="O47" s="6"/>
-      <c r="P47" s="6"/>
-      <c r="Q47" s="6"/>
-      <c r="R47" s="6"/>
-      <c r="S47" s="6"/>
-      <c r="T47" s="6"/>
-    </row>
-    <row r="48" spans="1:20" s="39" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A48" s="6"/>
-      <c r="B48" s="6"/>
-      <c r="C48" s="14"/>
-      <c r="D48" s="14"/>
-      <c r="E48" s="14"/>
-      <c r="F48" s="14"/>
-      <c r="G48" s="6"/>
-      <c r="H48" s="6"/>
-      <c r="I48" s="6"/>
-      <c r="J48" s="6"/>
-      <c r="K48" s="6"/>
-      <c r="L48" s="6"/>
-      <c r="M48" s="6"/>
-      <c r="N48" s="6"/>
-      <c r="O48" s="6"/>
-      <c r="P48" s="6"/>
-      <c r="Q48" s="6"/>
-      <c r="R48" s="6"/>
-      <c r="S48" s="6"/>
-      <c r="T48" s="6"/>
-    </row>
-    <row r="49" spans="1:20" s="39" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A49" s="6"/>
-      <c r="B49" s="6"/>
-      <c r="C49" s="14"/>
-      <c r="D49" s="14"/>
-      <c r="E49" s="14"/>
-      <c r="F49" s="14"/>
-      <c r="G49" s="6"/>
-      <c r="H49" s="6"/>
-      <c r="I49" s="6"/>
-      <c r="J49" s="6"/>
-      <c r="K49" s="6"/>
-      <c r="L49" s="6"/>
-      <c r="M49" s="6"/>
-      <c r="N49" s="6"/>
-      <c r="O49" s="6"/>
-      <c r="P49" s="6"/>
-      <c r="Q49" s="6"/>
-      <c r="R49" s="6"/>
-      <c r="S49" s="6"/>
-      <c r="T49" s="6"/>
-    </row>
-    <row r="50" spans="1:20" s="39" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A50" s="6"/>
-      <c r="B50" s="6"/>
-      <c r="C50" s="14"/>
-      <c r="D50" s="14"/>
-      <c r="E50" s="48"/>
-      <c r="F50" s="48"/>
-      <c r="G50" s="6"/>
-      <c r="H50" s="6"/>
-      <c r="I50" s="6"/>
-      <c r="J50" s="6"/>
-      <c r="K50" s="6"/>
-      <c r="L50" s="6"/>
-      <c r="M50" s="6"/>
-      <c r="N50" s="6"/>
-      <c r="O50" s="6"/>
-      <c r="P50" s="6"/>
-      <c r="Q50" s="6"/>
-      <c r="R50" s="6"/>
-      <c r="S50" s="6"/>
-      <c r="T50" s="6"/>
-    </row>
-    <row r="51" spans="1:20" s="39" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A51" s="6"/>
-      <c r="B51" s="6"/>
-      <c r="C51" s="14"/>
-      <c r="D51" s="14"/>
-      <c r="E51" s="34"/>
-      <c r="F51" s="34"/>
-      <c r="G51" s="6"/>
-      <c r="H51" s="6"/>
-      <c r="I51" s="6"/>
-      <c r="J51" s="6"/>
-      <c r="K51" s="6"/>
-      <c r="L51" s="6"/>
-      <c r="M51" s="6"/>
-      <c r="N51" s="6"/>
-      <c r="O51" s="6"/>
-      <c r="P51" s="6"/>
-      <c r="Q51" s="6"/>
-      <c r="R51" s="6"/>
-      <c r="S51" s="6"/>
-      <c r="T51" s="6"/>
-    </row>
-    <row r="52" spans="1:20" s="39" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A52" s="6"/>
-      <c r="B52" s="6"/>
-      <c r="C52" s="14"/>
-      <c r="D52" s="14"/>
-      <c r="E52" s="45"/>
-      <c r="F52" s="45"/>
-      <c r="G52" s="6"/>
-      <c r="H52" s="6"/>
-      <c r="I52" s="6"/>
-      <c r="J52" s="6"/>
-      <c r="K52" s="6"/>
-      <c r="L52" s="6"/>
-      <c r="M52" s="6"/>
-      <c r="N52" s="6"/>
-      <c r="O52" s="6"/>
-      <c r="P52" s="6"/>
-      <c r="Q52" s="6"/>
-      <c r="R52" s="6"/>
-      <c r="S52" s="6"/>
-      <c r="T52" s="6"/>
-    </row>
-    <row r="53" spans="1:20" s="39" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A53" s="6"/>
-      <c r="B53" s="6"/>
-      <c r="C53" s="14"/>
-      <c r="D53" s="14"/>
-      <c r="E53" s="14"/>
-      <c r="F53" s="14"/>
-      <c r="G53" s="6"/>
-      <c r="H53" s="6"/>
-      <c r="I53" s="6"/>
-      <c r="J53" s="6"/>
-      <c r="K53" s="6"/>
-      <c r="L53" s="6"/>
-      <c r="M53" s="6"/>
-      <c r="N53" s="6"/>
-      <c r="O53" s="6"/>
-      <c r="P53" s="6"/>
-      <c r="Q53" s="6"/>
-      <c r="R53" s="6"/>
-      <c r="S53" s="6"/>
-      <c r="T53" s="6"/>
-    </row>
-    <row r="54" spans="1:20" s="39" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A54" s="6"/>
-      <c r="B54" s="6"/>
-      <c r="C54" s="6"/>
-      <c r="D54" s="6"/>
-      <c r="E54" s="6"/>
-      <c r="F54" s="6"/>
-      <c r="G54" s="6"/>
-      <c r="H54" s="6"/>
-      <c r="I54" s="6"/>
-      <c r="J54" s="6"/>
-      <c r="K54" s="6"/>
-      <c r="L54" s="6"/>
-      <c r="M54" s="6"/>
-      <c r="N54" s="6"/>
-      <c r="O54" s="6"/>
-      <c r="P54" s="6"/>
-      <c r="Q54" s="6"/>
-      <c r="R54" s="6"/>
-      <c r="S54" s="6"/>
-      <c r="T54" s="6"/>
-    </row>
-    <row r="55" spans="1:20" s="39" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A55" s="6"/>
-      <c r="B55" s="6"/>
-      <c r="C55" s="6"/>
-      <c r="D55" s="6"/>
-      <c r="E55" s="6"/>
-      <c r="F55" s="6"/>
-      <c r="G55" s="6"/>
-      <c r="H55" s="6"/>
-      <c r="I55" s="6"/>
-      <c r="J55" s="6"/>
-      <c r="K55" s="6"/>
-      <c r="L55" s="6"/>
-      <c r="M55" s="6"/>
-      <c r="N55" s="6"/>
-      <c r="O55" s="6"/>
-      <c r="P55" s="6"/>
-      <c r="Q55" s="6"/>
-      <c r="R55" s="6"/>
-      <c r="S55" s="6"/>
-      <c r="T55" s="6"/>
-    </row>
-    <row r="56" spans="1:20" s="39" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A56" s="6"/>
-      <c r="B56" s="6"/>
-      <c r="C56" s="6"/>
-      <c r="D56" s="6"/>
-      <c r="E56" s="6"/>
-      <c r="F56" s="6"/>
-      <c r="G56" s="6"/>
-      <c r="H56" s="6"/>
-      <c r="I56" s="6"/>
-      <c r="J56" s="6"/>
-      <c r="K56" s="6"/>
-      <c r="L56" s="6"/>
-      <c r="M56" s="6"/>
-      <c r="N56" s="6"/>
-      <c r="O56" s="6"/>
-      <c r="P56" s="6"/>
-      <c r="Q56" s="6"/>
-      <c r="R56" s="6"/>
-      <c r="S56" s="6"/>
-      <c r="T56" s="6"/>
-    </row>
-    <row r="57" spans="1:20" s="39" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A57" s="6"/>
-      <c r="B57" s="6"/>
-      <c r="C57" s="6"/>
-      <c r="D57" s="6"/>
-      <c r="E57" s="6"/>
-      <c r="F57" s="6"/>
-      <c r="G57" s="6"/>
-      <c r="H57" s="6"/>
-      <c r="I57" s="6"/>
-      <c r="J57" s="6"/>
-      <c r="K57" s="6"/>
-      <c r="L57" s="6"/>
-      <c r="M57" s="6"/>
-      <c r="N57" s="6"/>
-      <c r="O57" s="6"/>
-      <c r="P57" s="6"/>
-      <c r="Q57" s="6"/>
-      <c r="R57" s="6"/>
-      <c r="S57" s="6"/>
-      <c r="T57" s="6"/>
-    </row>
-    <row r="59" spans="1:20" s="40" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A59" s="6"/>
-      <c r="B59" s="6"/>
-      <c r="C59" s="6"/>
-      <c r="D59" s="6"/>
-      <c r="E59" s="6"/>
-      <c r="F59" s="6"/>
-      <c r="G59" s="6"/>
-      <c r="H59" s="6"/>
-      <c r="I59" s="6"/>
-      <c r="J59" s="6"/>
-      <c r="K59" s="6"/>
-      <c r="L59" s="6"/>
-      <c r="M59" s="6"/>
-      <c r="N59" s="6"/>
-      <c r="O59" s="6"/>
-      <c r="P59" s="6"/>
-      <c r="Q59" s="6"/>
-      <c r="R59" s="6"/>
-      <c r="S59" s="6"/>
-      <c r="T59" s="6"/>
-    </row>
-    <row r="60" spans="1:20" s="40" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A60" s="6"/>
-      <c r="B60" s="6"/>
-      <c r="C60" s="6"/>
-      <c r="D60" s="6"/>
-      <c r="E60" s="6"/>
-      <c r="F60" s="6"/>
-      <c r="G60" s="6"/>
-      <c r="H60" s="6"/>
-      <c r="I60" s="6"/>
-      <c r="J60" s="6"/>
-      <c r="K60" s="6"/>
-      <c r="L60" s="6"/>
-      <c r="M60" s="6"/>
-      <c r="N60" s="6"/>
-      <c r="O60" s="6"/>
-      <c r="P60" s="6"/>
-      <c r="Q60" s="6"/>
-      <c r="R60" s="6"/>
-      <c r="S60" s="6"/>
-      <c r="T60" s="6"/>
-    </row>
-    <row r="61" spans="1:20" s="40" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A61" s="6"/>
-      <c r="B61" s="6"/>
-      <c r="C61" s="6"/>
-      <c r="D61" s="6"/>
-      <c r="E61" s="6"/>
-      <c r="F61" s="6"/>
-      <c r="G61" s="6"/>
-      <c r="H61" s="6"/>
-      <c r="I61" s="6"/>
-      <c r="J61" s="6"/>
-      <c r="K61" s="6"/>
-      <c r="L61" s="6"/>
-      <c r="M61" s="6"/>
-      <c r="N61" s="6"/>
-      <c r="O61" s="6"/>
-      <c r="P61" s="6"/>
-      <c r="Q61" s="6"/>
-      <c r="R61" s="6"/>
-      <c r="S61" s="6"/>
-      <c r="T61" s="6"/>
-    </row>
-    <row r="62" spans="1:20" s="40" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A62" s="6"/>
-      <c r="B62" s="6"/>
-      <c r="C62" s="6"/>
-      <c r="D62" s="6"/>
-      <c r="E62" s="6"/>
-      <c r="F62" s="6"/>
-      <c r="G62" s="6"/>
-      <c r="H62" s="6"/>
-      <c r="I62" s="6"/>
-      <c r="J62" s="6"/>
-      <c r="K62" s="6"/>
-      <c r="L62" s="6"/>
-      <c r="M62" s="6"/>
-      <c r="N62" s="6"/>
-      <c r="O62" s="6"/>
-      <c r="P62" s="6"/>
-      <c r="Q62" s="6"/>
-      <c r="R62" s="6"/>
-      <c r="S62" s="6"/>
-      <c r="T62" s="6"/>
-    </row>
-    <row r="63" spans="1:20" s="40" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A63" s="6"/>
-      <c r="B63" s="6"/>
-      <c r="C63" s="6"/>
-      <c r="D63" s="6"/>
-      <c r="E63" s="6"/>
-      <c r="F63" s="6"/>
-      <c r="G63" s="6"/>
-      <c r="H63" s="6"/>
-      <c r="I63" s="6"/>
-      <c r="J63" s="6"/>
-      <c r="K63" s="6"/>
-      <c r="L63" s="6"/>
-      <c r="M63" s="6"/>
-      <c r="N63" s="6"/>
-      <c r="O63" s="6"/>
-      <c r="P63" s="6"/>
-      <c r="Q63" s="6"/>
-      <c r="R63" s="6"/>
-      <c r="S63" s="6"/>
-      <c r="T63" s="6"/>
-    </row>
-    <row r="64" spans="1:20" s="40" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A64" s="6"/>
-      <c r="B64" s="6"/>
-      <c r="C64" s="6"/>
-      <c r="D64" s="6"/>
-      <c r="E64" s="6"/>
-      <c r="F64" s="6"/>
-      <c r="G64" s="6"/>
-      <c r="H64" s="6"/>
-      <c r="I64" s="6"/>
-      <c r="J64" s="6"/>
-      <c r="K64" s="6"/>
-      <c r="L64" s="6"/>
-      <c r="M64" s="6"/>
-      <c r="N64" s="6"/>
-      <c r="O64" s="6"/>
-      <c r="P64" s="6"/>
-      <c r="Q64" s="6"/>
-      <c r="R64" s="6"/>
-      <c r="S64" s="6"/>
-      <c r="T64" s="6"/>
-    </row>
-    <row r="65" spans="1:23" s="40" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A65" s="6"/>
-      <c r="B65" s="6"/>
-      <c r="C65" s="6"/>
-      <c r="D65" s="6"/>
-      <c r="E65" s="6"/>
-      <c r="F65" s="6"/>
-      <c r="G65" s="6"/>
-      <c r="H65" s="6"/>
-      <c r="I65" s="6"/>
-      <c r="J65" s="6"/>
-      <c r="K65" s="6"/>
-      <c r="L65" s="6"/>
-      <c r="M65" s="6"/>
-      <c r="N65" s="6"/>
-      <c r="O65" s="6"/>
-      <c r="P65" s="6"/>
-      <c r="Q65" s="6"/>
-      <c r="R65" s="6"/>
-      <c r="S65" s="6"/>
-      <c r="T65" s="6"/>
-    </row>
-    <row r="66" spans="1:23" s="40" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A66" s="6"/>
-      <c r="B66" s="6"/>
-      <c r="C66" s="6"/>
-      <c r="D66" s="6"/>
-      <c r="E66" s="6"/>
-      <c r="F66" s="6"/>
-      <c r="G66" s="6"/>
-      <c r="H66" s="6"/>
-      <c r="I66" s="6"/>
-      <c r="J66" s="6"/>
-      <c r="K66" s="6"/>
-      <c r="L66" s="6"/>
-      <c r="M66" s="6"/>
-      <c r="N66" s="6"/>
-      <c r="O66" s="6"/>
-      <c r="P66" s="6"/>
-      <c r="Q66" s="6"/>
-      <c r="R66" s="6"/>
-      <c r="S66" s="6"/>
-      <c r="T66" s="6"/>
-    </row>
-    <row r="67" spans="1:23" s="40" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A67" s="6"/>
-      <c r="B67" s="6"/>
-      <c r="C67" s="6"/>
-      <c r="D67" s="6"/>
-      <c r="E67" s="6"/>
-      <c r="F67" s="6"/>
-      <c r="G67" s="6"/>
-      <c r="H67" s="6"/>
-      <c r="I67" s="6"/>
-      <c r="J67" s="6"/>
-      <c r="K67" s="6"/>
-      <c r="L67" s="6"/>
-      <c r="M67" s="6"/>
-      <c r="N67" s="6"/>
-      <c r="O67" s="6"/>
-      <c r="P67" s="6"/>
-      <c r="Q67" s="6"/>
-      <c r="R67" s="6"/>
-      <c r="S67" s="6"/>
-      <c r="T67" s="6"/>
-    </row>
-    <row r="70" spans="1:23" s="40" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A70" s="6"/>
-      <c r="B70" s="6"/>
-      <c r="C70" s="6"/>
-      <c r="D70" s="6"/>
-      <c r="E70" s="6"/>
-      <c r="F70" s="6"/>
-      <c r="G70" s="6"/>
-      <c r="H70" s="6"/>
-      <c r="I70" s="6"/>
-      <c r="J70" s="6"/>
-      <c r="K70" s="6"/>
-      <c r="L70" s="6"/>
-      <c r="M70" s="6"/>
-      <c r="N70" s="6"/>
-      <c r="O70" s="6"/>
-      <c r="P70" s="6"/>
-      <c r="Q70" s="6"/>
-      <c r="R70" s="6"/>
-      <c r="S70" s="6"/>
-      <c r="T70" s="6"/>
-    </row>
-    <row r="71" spans="1:23" s="40" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A71" s="6"/>
-      <c r="B71" s="6"/>
-      <c r="C71" s="6"/>
-      <c r="D71" s="6"/>
-      <c r="E71" s="6"/>
-      <c r="F71" s="6"/>
-      <c r="G71" s="6"/>
-      <c r="H71" s="6"/>
-      <c r="I71" s="6"/>
-      <c r="J71" s="6"/>
-      <c r="K71" s="6"/>
-      <c r="L71" s="6"/>
-      <c r="M71" s="6"/>
-      <c r="N71" s="6"/>
-      <c r="O71" s="6"/>
-      <c r="P71" s="6"/>
-      <c r="Q71" s="6"/>
-      <c r="R71" s="6"/>
-      <c r="S71" s="6"/>
-      <c r="T71" s="6"/>
-    </row>
-    <row r="72" spans="1:23" s="40" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A72" s="6"/>
-      <c r="B72" s="6"/>
-      <c r="C72" s="6"/>
-      <c r="D72" s="6"/>
-      <c r="E72" s="6"/>
-      <c r="F72" s="6"/>
-      <c r="G72" s="6"/>
-      <c r="H72" s="6"/>
-      <c r="I72" s="6"/>
-      <c r="J72" s="6"/>
-      <c r="K72" s="6"/>
-      <c r="L72" s="6"/>
-      <c r="M72" s="6"/>
-      <c r="N72" s="6"/>
-      <c r="O72" s="6"/>
-      <c r="P72" s="6"/>
-      <c r="Q72" s="6"/>
-      <c r="R72" s="6"/>
-      <c r="S72" s="6"/>
-      <c r="T72" s="6"/>
-    </row>
-    <row r="75" spans="1:23" s="35" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A75" s="6"/>
-      <c r="B75" s="6"/>
-      <c r="C75" s="6"/>
-      <c r="D75" s="6"/>
-      <c r="E75" s="6"/>
-      <c r="F75" s="6"/>
-      <c r="G75" s="6"/>
-      <c r="H75" s="6"/>
-      <c r="I75" s="6"/>
-      <c r="J75" s="6"/>
-      <c r="K75" s="6"/>
-      <c r="L75" s="6"/>
-      <c r="M75" s="6"/>
-      <c r="N75" s="6"/>
-      <c r="O75" s="6"/>
-      <c r="P75" s="6"/>
-      <c r="Q75" s="6"/>
-      <c r="R75" s="6"/>
-      <c r="S75" s="6"/>
-      <c r="T75" s="6"/>
-      <c r="U75" s="46"/>
-      <c r="V75" s="46"/>
-      <c r="W75" s="46"/>
+      <c r="B45" s="33"/>
+      <c r="C45" s="33"/>
+      <c r="D45" s="33"/>
+      <c r="E45" s="5"/>
+      <c r="F45" s="5"/>
+      <c r="G45" s="5"/>
+      <c r="H45" s="5"/>
+      <c r="I45" s="5"/>
+      <c r="J45" s="11"/>
+      <c r="K45" s="11"/>
+      <c r="L45" s="11"/>
+      <c r="M45" s="5"/>
+      <c r="N45" s="5"/>
+      <c r="O45" s="5"/>
+      <c r="P45" s="5"/>
+      <c r="Q45" s="5"/>
+      <c r="R45" s="5"/>
+      <c r="S45" s="5"/>
+      <c r="T45" s="5"/>
+    </row>
+    <row r="46" spans="1:20" s="18" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A46" s="5"/>
+      <c r="B46" s="5"/>
+      <c r="C46" s="5"/>
+      <c r="D46" s="5"/>
+      <c r="E46" s="5"/>
+      <c r="F46" s="5"/>
+      <c r="G46" s="5"/>
+      <c r="H46" s="5"/>
+      <c r="I46" s="5"/>
+      <c r="J46" s="5"/>
+      <c r="K46" s="5"/>
+      <c r="L46" s="5"/>
+      <c r="M46" s="5"/>
+      <c r="N46" s="5"/>
+      <c r="O46" s="5"/>
+      <c r="P46" s="5"/>
+      <c r="Q46" s="5"/>
+      <c r="R46" s="5"/>
+      <c r="S46" s="5"/>
+      <c r="T46" s="5"/>
+    </row>
+    <row r="47" spans="1:20" s="18" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A47" s="5"/>
+      <c r="B47" s="5"/>
+      <c r="C47" s="5"/>
+      <c r="D47" s="5"/>
+      <c r="E47" s="5"/>
+      <c r="F47" s="5"/>
+      <c r="G47" s="5"/>
+      <c r="H47" s="5"/>
+      <c r="I47" s="5"/>
+      <c r="J47" s="5"/>
+      <c r="K47" s="5"/>
+      <c r="L47" s="5"/>
+      <c r="M47" s="5"/>
+      <c r="N47" s="5"/>
+      <c r="O47" s="5"/>
+      <c r="P47" s="5"/>
+      <c r="Q47" s="5"/>
+      <c r="R47" s="5"/>
+      <c r="S47" s="5"/>
+      <c r="T47" s="5"/>
+    </row>
+    <row r="48" spans="1:20" s="18" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A48" s="5"/>
+      <c r="B48" s="5"/>
+      <c r="C48" s="5"/>
+      <c r="D48" s="5"/>
+      <c r="E48" s="5"/>
+      <c r="F48" s="5"/>
+      <c r="G48" s="5"/>
+      <c r="H48" s="5"/>
+      <c r="I48" s="5"/>
+      <c r="J48" s="5"/>
+      <c r="K48" s="5"/>
+      <c r="L48" s="5"/>
+      <c r="M48" s="5"/>
+      <c r="N48" s="5"/>
+      <c r="O48" s="5"/>
+      <c r="P48" s="5"/>
+      <c r="Q48" s="5"/>
+      <c r="R48" s="5"/>
+      <c r="S48" s="5"/>
+      <c r="T48" s="5"/>
+    </row>
+    <row r="49" spans="1:20" s="18" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A49" s="5"/>
+      <c r="B49" s="5"/>
+      <c r="C49" s="5"/>
+      <c r="D49" s="5"/>
+      <c r="E49" s="5"/>
+      <c r="F49" s="5"/>
+      <c r="G49" s="5"/>
+      <c r="H49" s="5"/>
+      <c r="I49" s="5"/>
+      <c r="J49" s="5"/>
+      <c r="K49" s="5"/>
+      <c r="L49" s="5"/>
+      <c r="M49" s="5"/>
+      <c r="N49" s="5"/>
+      <c r="O49" s="5"/>
+      <c r="P49" s="5"/>
+      <c r="Q49" s="5"/>
+      <c r="R49" s="5"/>
+      <c r="S49" s="5"/>
+      <c r="T49" s="5"/>
+    </row>
+    <row r="50" spans="1:20" s="18" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A50" s="5"/>
+      <c r="B50" s="5"/>
+      <c r="C50" s="5"/>
+      <c r="D50" s="5"/>
+      <c r="E50" s="36"/>
+      <c r="F50" s="36"/>
+      <c r="G50" s="5"/>
+      <c r="H50" s="5"/>
+      <c r="I50" s="5"/>
+      <c r="J50" s="5"/>
+      <c r="K50" s="5"/>
+      <c r="L50" s="5"/>
+      <c r="M50" s="5"/>
+      <c r="N50" s="5"/>
+      <c r="O50" s="5"/>
+      <c r="P50" s="5"/>
+      <c r="Q50" s="5"/>
+      <c r="R50" s="5"/>
+      <c r="S50" s="5"/>
+      <c r="T50" s="5"/>
+    </row>
+    <row r="51" spans="1:20" s="18" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A51" s="5"/>
+      <c r="B51" s="5"/>
+      <c r="C51" s="5"/>
+      <c r="D51" s="5"/>
+      <c r="E51" s="7"/>
+      <c r="F51" s="7"/>
+      <c r="G51" s="5"/>
+      <c r="H51" s="5"/>
+      <c r="I51" s="5"/>
+      <c r="J51" s="5"/>
+      <c r="K51" s="5"/>
+      <c r="L51" s="5"/>
+      <c r="M51" s="5"/>
+      <c r="N51" s="5"/>
+      <c r="O51" s="5"/>
+      <c r="P51" s="5"/>
+      <c r="Q51" s="5"/>
+      <c r="R51" s="5"/>
+      <c r="S51" s="5"/>
+      <c r="T51" s="5"/>
+    </row>
+    <row r="52" spans="1:20" s="18" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A52" s="5"/>
+      <c r="B52" s="5"/>
+      <c r="C52" s="5"/>
+      <c r="D52" s="5"/>
+      <c r="E52" s="33"/>
+      <c r="F52" s="33"/>
+      <c r="G52" s="5"/>
+      <c r="H52" s="5"/>
+      <c r="I52" s="5"/>
+      <c r="J52" s="5"/>
+      <c r="K52" s="5"/>
+      <c r="L52" s="5"/>
+      <c r="M52" s="5"/>
+      <c r="N52" s="5"/>
+      <c r="O52" s="5"/>
+      <c r="P52" s="5"/>
+      <c r="Q52" s="5"/>
+      <c r="R52" s="5"/>
+      <c r="S52" s="5"/>
+      <c r="T52" s="5"/>
+    </row>
+    <row r="53" spans="1:20" s="18" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A53" s="5"/>
+      <c r="B53" s="5"/>
+      <c r="C53" s="5"/>
+      <c r="D53" s="5"/>
+      <c r="E53" s="5"/>
+      <c r="F53" s="5"/>
+      <c r="G53" s="5"/>
+      <c r="H53" s="5"/>
+      <c r="I53" s="5"/>
+      <c r="J53" s="5"/>
+      <c r="K53" s="5"/>
+      <c r="L53" s="5"/>
+      <c r="M53" s="5"/>
+      <c r="N53" s="5"/>
+      <c r="O53" s="5"/>
+      <c r="P53" s="5"/>
+      <c r="Q53" s="5"/>
+      <c r="R53" s="5"/>
+      <c r="S53" s="5"/>
+      <c r="T53" s="5"/>
+    </row>
+    <row r="54" spans="1:20" s="18" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A54" s="5"/>
+      <c r="B54" s="5"/>
+      <c r="C54" s="5"/>
+      <c r="D54" s="5"/>
+      <c r="E54" s="5"/>
+      <c r="F54" s="5"/>
+      <c r="G54" s="5"/>
+      <c r="H54" s="5"/>
+      <c r="I54" s="5"/>
+      <c r="J54" s="5"/>
+      <c r="K54" s="5"/>
+      <c r="L54" s="5"/>
+      <c r="M54" s="5"/>
+      <c r="N54" s="5"/>
+      <c r="O54" s="5"/>
+      <c r="P54" s="5"/>
+      <c r="Q54" s="5"/>
+      <c r="R54" s="5"/>
+      <c r="S54" s="5"/>
+      <c r="T54" s="5"/>
+    </row>
+    <row r="55" spans="1:20" s="18" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A55" s="5"/>
+      <c r="B55" s="5"/>
+      <c r="C55" s="5"/>
+      <c r="D55" s="5"/>
+      <c r="E55" s="5"/>
+      <c r="F55" s="5"/>
+      <c r="G55" s="5"/>
+      <c r="H55" s="5"/>
+      <c r="I55" s="5"/>
+      <c r="J55" s="5"/>
+      <c r="K55" s="5"/>
+      <c r="L55" s="5"/>
+      <c r="M55" s="5"/>
+      <c r="N55" s="5"/>
+      <c r="O55" s="5"/>
+      <c r="P55" s="5"/>
+      <c r="Q55" s="5"/>
+      <c r="R55" s="5"/>
+      <c r="S55" s="5"/>
+      <c r="T55" s="5"/>
+    </row>
+    <row r="56" spans="1:20" s="18" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A56" s="5"/>
+      <c r="B56" s="5"/>
+      <c r="C56" s="5"/>
+      <c r="D56" s="5"/>
+      <c r="E56" s="5"/>
+      <c r="F56" s="5"/>
+      <c r="G56" s="5"/>
+      <c r="H56" s="5"/>
+      <c r="I56" s="5"/>
+      <c r="J56" s="5"/>
+      <c r="K56" s="5"/>
+      <c r="L56" s="5"/>
+      <c r="M56" s="5"/>
+      <c r="N56" s="5"/>
+      <c r="O56" s="5"/>
+      <c r="P56" s="5"/>
+      <c r="Q56" s="5"/>
+      <c r="R56" s="5"/>
+      <c r="S56" s="5"/>
+      <c r="T56" s="5"/>
+    </row>
+    <row r="57" spans="1:20" s="18" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A57" s="5"/>
+      <c r="B57" s="5"/>
+      <c r="C57" s="5"/>
+      <c r="D57" s="5"/>
+      <c r="E57" s="5"/>
+      <c r="F57" s="5"/>
+      <c r="G57" s="5"/>
+      <c r="H57" s="5"/>
+      <c r="I57" s="5"/>
+      <c r="J57" s="5"/>
+      <c r="K57" s="5"/>
+      <c r="L57" s="5"/>
+      <c r="M57" s="5"/>
+      <c r="N57" s="5"/>
+      <c r="O57" s="5"/>
+      <c r="P57" s="5"/>
+      <c r="Q57" s="5"/>
+      <c r="R57" s="5"/>
+      <c r="S57" s="5"/>
+      <c r="T57" s="5"/>
+    </row>
+    <row r="59" spans="1:20" s="28" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A59" s="5"/>
+      <c r="B59" s="5"/>
+      <c r="C59" s="5"/>
+      <c r="D59" s="5"/>
+      <c r="E59" s="5"/>
+      <c r="F59" s="5"/>
+      <c r="G59" s="5"/>
+      <c r="H59" s="5"/>
+      <c r="I59" s="5"/>
+      <c r="J59" s="5"/>
+      <c r="K59" s="5"/>
+      <c r="L59" s="5"/>
+      <c r="M59" s="5"/>
+      <c r="N59" s="5"/>
+      <c r="O59" s="5"/>
+      <c r="P59" s="5"/>
+      <c r="Q59" s="5"/>
+      <c r="R59" s="5"/>
+      <c r="S59" s="5"/>
+      <c r="T59" s="5"/>
+    </row>
+    <row r="60" spans="1:20" s="28" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A60" s="5"/>
+      <c r="B60" s="5"/>
+      <c r="C60" s="5"/>
+      <c r="D60" s="5"/>
+      <c r="E60" s="5"/>
+      <c r="F60" s="5"/>
+      <c r="G60" s="5"/>
+      <c r="H60" s="5"/>
+      <c r="I60" s="5"/>
+      <c r="J60" s="5"/>
+      <c r="K60" s="5"/>
+      <c r="L60" s="5"/>
+      <c r="M60" s="5"/>
+      <c r="N60" s="5"/>
+      <c r="O60" s="5"/>
+      <c r="P60" s="5"/>
+      <c r="Q60" s="5"/>
+      <c r="R60" s="5"/>
+      <c r="S60" s="5"/>
+      <c r="T60" s="5"/>
+    </row>
+    <row r="61" spans="1:20" s="28" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A61" s="5"/>
+      <c r="B61" s="5"/>
+      <c r="C61" s="5"/>
+      <c r="D61" s="5"/>
+      <c r="E61" s="5"/>
+      <c r="F61" s="5"/>
+      <c r="G61" s="5"/>
+      <c r="H61" s="5"/>
+      <c r="I61" s="5"/>
+      <c r="J61" s="5"/>
+      <c r="K61" s="5"/>
+      <c r="L61" s="5"/>
+      <c r="M61" s="5"/>
+      <c r="N61" s="5"/>
+      <c r="O61" s="5"/>
+      <c r="P61" s="5"/>
+      <c r="Q61" s="5"/>
+      <c r="R61" s="5"/>
+      <c r="S61" s="5"/>
+      <c r="T61" s="5"/>
+    </row>
+    <row r="62" spans="1:20" s="28" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A62" s="5"/>
+      <c r="B62" s="5"/>
+      <c r="C62" s="5"/>
+      <c r="D62" s="5"/>
+      <c r="E62" s="5"/>
+      <c r="F62" s="5"/>
+      <c r="G62" s="5"/>
+      <c r="H62" s="5"/>
+      <c r="I62" s="5"/>
+      <c r="J62" s="5"/>
+      <c r="K62" s="5"/>
+      <c r="L62" s="5"/>
+      <c r="M62" s="5"/>
+      <c r="N62" s="5"/>
+      <c r="O62" s="5"/>
+      <c r="P62" s="5"/>
+      <c r="Q62" s="5"/>
+      <c r="R62" s="5"/>
+      <c r="S62" s="5"/>
+      <c r="T62" s="5"/>
+    </row>
+    <row r="63" spans="1:20" s="28" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A63" s="5"/>
+      <c r="B63" s="5"/>
+      <c r="C63" s="5"/>
+      <c r="D63" s="5"/>
+      <c r="E63" s="5"/>
+      <c r="F63" s="5"/>
+      <c r="G63" s="5"/>
+      <c r="H63" s="5"/>
+      <c r="I63" s="5"/>
+      <c r="J63" s="5"/>
+      <c r="K63" s="5"/>
+      <c r="L63" s="5"/>
+      <c r="M63" s="5"/>
+      <c r="N63" s="5"/>
+      <c r="O63" s="5"/>
+      <c r="P63" s="5"/>
+      <c r="Q63" s="5"/>
+      <c r="R63" s="5"/>
+      <c r="S63" s="5"/>
+      <c r="T63" s="5"/>
+    </row>
+    <row r="64" spans="1:20" s="28" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A64" s="5"/>
+      <c r="B64" s="5"/>
+      <c r="C64" s="5"/>
+      <c r="D64" s="5"/>
+      <c r="E64" s="5"/>
+      <c r="F64" s="5"/>
+      <c r="G64" s="5"/>
+      <c r="H64" s="5"/>
+      <c r="I64" s="5"/>
+      <c r="J64" s="5"/>
+      <c r="K64" s="5"/>
+      <c r="L64" s="5"/>
+      <c r="M64" s="5"/>
+      <c r="N64" s="5"/>
+      <c r="O64" s="5"/>
+      <c r="P64" s="5"/>
+      <c r="Q64" s="5"/>
+      <c r="R64" s="5"/>
+      <c r="S64" s="5"/>
+      <c r="T64" s="5"/>
+    </row>
+    <row r="65" spans="1:23" s="28" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A65" s="5"/>
+      <c r="B65" s="5"/>
+      <c r="C65" s="5"/>
+      <c r="D65" s="5"/>
+      <c r="E65" s="5"/>
+      <c r="F65" s="5"/>
+      <c r="G65" s="5"/>
+      <c r="H65" s="5"/>
+      <c r="I65" s="5"/>
+      <c r="J65" s="5"/>
+      <c r="K65" s="5"/>
+      <c r="L65" s="5"/>
+      <c r="M65" s="5"/>
+      <c r="N65" s="5"/>
+      <c r="O65" s="5"/>
+      <c r="P65" s="5"/>
+      <c r="Q65" s="5"/>
+      <c r="R65" s="5"/>
+      <c r="S65" s="5"/>
+      <c r="T65" s="5"/>
+    </row>
+    <row r="66" spans="1:23" s="28" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A66" s="5"/>
+      <c r="B66" s="5"/>
+      <c r="C66" s="5"/>
+      <c r="D66" s="5"/>
+      <c r="E66" s="5"/>
+      <c r="F66" s="5"/>
+      <c r="G66" s="5"/>
+      <c r="H66" s="5"/>
+      <c r="I66" s="5"/>
+      <c r="J66" s="5"/>
+      <c r="K66" s="5"/>
+      <c r="L66" s="5"/>
+      <c r="M66" s="5"/>
+      <c r="N66" s="5"/>
+      <c r="O66" s="5"/>
+      <c r="P66" s="5"/>
+      <c r="Q66" s="5"/>
+      <c r="R66" s="5"/>
+      <c r="S66" s="5"/>
+      <c r="T66" s="5"/>
+    </row>
+    <row r="67" spans="1:23" s="28" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A67" s="5"/>
+      <c r="B67" s="5"/>
+      <c r="C67" s="5"/>
+      <c r="D67" s="5"/>
+      <c r="E67" s="5"/>
+      <c r="F67" s="5"/>
+      <c r="G67" s="5"/>
+      <c r="H67" s="5"/>
+      <c r="I67" s="5"/>
+      <c r="J67" s="5"/>
+      <c r="K67" s="5"/>
+      <c r="L67" s="5"/>
+      <c r="M67" s="5"/>
+      <c r="N67" s="5"/>
+      <c r="O67" s="5"/>
+      <c r="P67" s="5"/>
+      <c r="Q67" s="5"/>
+      <c r="R67" s="5"/>
+      <c r="S67" s="5"/>
+      <c r="T67" s="5"/>
+    </row>
+    <row r="70" spans="1:23" s="28" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A70" s="5"/>
+      <c r="B70" s="5"/>
+      <c r="C70" s="5"/>
+      <c r="D70" s="5"/>
+      <c r="E70" s="5"/>
+      <c r="F70" s="5"/>
+      <c r="G70" s="5"/>
+      <c r="H70" s="5"/>
+      <c r="I70" s="5"/>
+      <c r="J70" s="5"/>
+      <c r="K70" s="5"/>
+      <c r="L70" s="5"/>
+      <c r="M70" s="5"/>
+      <c r="N70" s="5"/>
+      <c r="O70" s="5"/>
+      <c r="P70" s="5"/>
+      <c r="Q70" s="5"/>
+      <c r="R70" s="5"/>
+      <c r="S70" s="5"/>
+      <c r="T70" s="5"/>
+    </row>
+    <row r="71" spans="1:23" s="28" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A71" s="5"/>
+      <c r="B71" s="5"/>
+      <c r="C71" s="5"/>
+      <c r="D71" s="5"/>
+      <c r="E71" s="5"/>
+      <c r="F71" s="5"/>
+      <c r="G71" s="5"/>
+      <c r="H71" s="5"/>
+      <c r="I71" s="5"/>
+      <c r="J71" s="5"/>
+      <c r="K71" s="5"/>
+      <c r="L71" s="5"/>
+      <c r="M71" s="5"/>
+      <c r="N71" s="5"/>
+      <c r="O71" s="5"/>
+      <c r="P71" s="5"/>
+      <c r="Q71" s="5"/>
+      <c r="R71" s="5"/>
+      <c r="S71" s="5"/>
+      <c r="T71" s="5"/>
+    </row>
+    <row r="72" spans="1:23" s="28" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A72" s="5"/>
+      <c r="B72" s="5"/>
+      <c r="C72" s="5"/>
+      <c r="D72" s="5"/>
+      <c r="E72" s="5"/>
+      <c r="F72" s="5"/>
+      <c r="G72" s="5"/>
+      <c r="H72" s="5"/>
+      <c r="I72" s="5"/>
+      <c r="J72" s="5"/>
+      <c r="K72" s="5"/>
+      <c r="L72" s="5"/>
+      <c r="M72" s="5"/>
+      <c r="N72" s="5"/>
+      <c r="O72" s="5"/>
+      <c r="P72" s="5"/>
+      <c r="Q72" s="5"/>
+      <c r="R72" s="5"/>
+      <c r="S72" s="5"/>
+      <c r="T72" s="5"/>
+    </row>
+    <row r="75" spans="1:23" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A75" s="5"/>
+      <c r="B75" s="5"/>
+      <c r="C75" s="5"/>
+      <c r="D75" s="5"/>
+      <c r="E75" s="5"/>
+      <c r="F75" s="5"/>
+      <c r="G75" s="5"/>
+      <c r="H75" s="5"/>
+      <c r="I75" s="5"/>
+      <c r="J75" s="5"/>
+      <c r="K75" s="5"/>
+      <c r="L75" s="5"/>
+      <c r="M75" s="5"/>
+      <c r="N75" s="5"/>
+      <c r="O75" s="5"/>
+      <c r="P75" s="5"/>
+      <c r="Q75" s="5"/>
+      <c r="R75" s="5"/>
+      <c r="S75" s="5"/>
+      <c r="T75" s="5"/>
+      <c r="U75" s="34"/>
+      <c r="V75" s="34"/>
+      <c r="W75" s="34"/>
     </row>
     <row r="76" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="U76" s="47"/>
-      <c r="V76" s="47"/>
-      <c r="W76" s="47"/>
+      <c r="U76" s="35"/>
+      <c r="V76" s="35"/>
+      <c r="W76" s="35"/>
     </row>
   </sheetData>
-  <mergeCells count="22">
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="H20:L20"/>
-    <mergeCell ref="M20:P20"/>
-    <mergeCell ref="Q20:T20"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="H21:L21"/>
-    <mergeCell ref="A3:T3"/>
-    <mergeCell ref="A4:T4"/>
-    <mergeCell ref="A5:T5"/>
-    <mergeCell ref="A6:T6"/>
-    <mergeCell ref="N12:S12"/>
+  <mergeCells count="32">
+    <mergeCell ref="M22:P22"/>
+    <mergeCell ref="M23:P23"/>
+    <mergeCell ref="Q21:T21"/>
+    <mergeCell ref="Q22:T22"/>
+    <mergeCell ref="Q23:T23"/>
     <mergeCell ref="K14:N14"/>
     <mergeCell ref="A44:F44"/>
     <mergeCell ref="Q24:T24"/>
@@ -3699,6 +3640,22 @@
     <mergeCell ref="Q17:T18"/>
     <mergeCell ref="H17:L18"/>
     <mergeCell ref="A20:B20"/>
+    <mergeCell ref="E20:G20"/>
+    <mergeCell ref="E21:G21"/>
+    <mergeCell ref="E22:G22"/>
+    <mergeCell ref="E23:G23"/>
+    <mergeCell ref="M21:P21"/>
+    <mergeCell ref="A3:T3"/>
+    <mergeCell ref="A4:T4"/>
+    <mergeCell ref="A5:T5"/>
+    <mergeCell ref="A6:T6"/>
+    <mergeCell ref="N12:S12"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="H20:L20"/>
+    <mergeCell ref="M20:P20"/>
+    <mergeCell ref="Q20:T20"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="H21:L21"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <printOptions horizontalCentered="1"/>

--- a/RFQ Generator Beta Version/Templates/DE TEMPLATE.xlsx
+++ b/RFQ Generator Beta Version/Templates/DE TEMPLATE.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\RFQ PROJECT\RFQ TEMPLATE\PRICED\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40C5827C-AF09-4AE1-8537-7DD3EB9EAE19}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D62D8B0-408C-4803-8EFE-A9DC31EC2A2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{02CCD737-9343-44DD-A110-541534088332}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="PRICED" sheetId="27" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">PRICED!$A$2:$T$45</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">PRICED!$A$2:$T$47</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">PRICED!$2:$18</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="52">
   <si>
     <t>ITEM</t>
   </si>
@@ -111,24 +111,12 @@
     <t>TOTAL</t>
   </si>
   <si>
-    <t>60 DAYS</t>
-  </si>
-  <si>
     <t>Operation Executive</t>
   </si>
   <si>
     <t>PRICED</t>
   </si>
   <si>
-    <t>DDP</t>
-  </si>
-  <si>
-    <t>ABF</t>
-  </si>
-  <si>
-    <t>ASEAN BINTULU FERTILIZER SDN BHD</t>
-  </si>
-  <si>
     <t>30 DAYS</t>
   </si>
   <si>
@@ -138,24 +126,6 @@
     <t>kamarul</t>
   </si>
   <si>
-    <t>27/10/2022</t>
-  </si>
-  <si>
-    <t>WEEKS</t>
-  </si>
-  <si>
-    <t>PC</t>
-  </si>
-  <si>
-    <t>RFP-000000046846</t>
-  </si>
-  <si>
-    <t>DEJSB/105932/271022</t>
-  </si>
-  <si>
-    <t>ELBOW,PIP,90DEG,3/4",NPT,SS F316,ASTM</t>
-  </si>
-  <si>
     <t xml:space="preserve"> if it is prevented in performing those obligations by an event of force majeure.</t>
   </si>
   <si>
@@ -169,6 +139,60 @@
   </si>
   <si>
     <t xml:space="preserve">Force Majeure- Neither party is responsible for any failure to perform its obligations under this contract, </t>
+  </si>
+  <si>
+    <t>total_price</t>
+  </si>
+  <si>
+    <t>SUB TOTAL</t>
+  </si>
+  <si>
+    <t>DISCOUNT</t>
+  </si>
+  <si>
+    <t>sub_total</t>
+  </si>
+  <si>
+    <t>_discount</t>
+  </si>
+  <si>
+    <t>client_name</t>
+  </si>
+  <si>
+    <t>_date</t>
+  </si>
+  <si>
+    <t>rfq_code</t>
+  </si>
+  <si>
+    <t>quote_code</t>
+  </si>
+  <si>
+    <t>_num</t>
+  </si>
+  <si>
+    <t>_qty</t>
+  </si>
+  <si>
+    <t>_desc</t>
+  </si>
+  <si>
+    <t>delivery_time</t>
+  </si>
+  <si>
+    <t>unit_price</t>
+  </si>
+  <si>
+    <t>summary_total_price</t>
+  </si>
+  <si>
+    <t>_validity</t>
+  </si>
+  <si>
+    <t>delivery_term</t>
+  </si>
+  <si>
+    <t>delivery_point</t>
   </si>
 </sst>
 </file>
@@ -253,7 +277,7 @@
       <sz val="11"/>
       <color indexed="8"/>
       <name val="Franklin Gothic Book"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
@@ -368,13 +392,22 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color indexed="64"/>
       </left>
       <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
+      <top/>
       <bottom style="thick">
         <color indexed="64"/>
       </bottom>
@@ -383,9 +416,7 @@
     <border>
       <left/>
       <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
+      <top/>
       <bottom style="thick">
         <color indexed="64"/>
       </bottom>
@@ -396,21 +427,8 @@
       <right style="thin">
         <color indexed="64"/>
       </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
+      <top/>
       <bottom style="thick">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
@@ -470,12 +488,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -496,46 +508,151 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="39" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="4" fontId="5" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="5" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -546,6 +663,12 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="4" fontId="5" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -553,111 +676,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="4" fontId="5" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="4" fontId="5" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="5" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1626,13 +1644,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>39</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>152400</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
       <xdr:colOff>754380</xdr:colOff>
-      <xdr:row>43</xdr:row>
+      <xdr:row>45</xdr:row>
       <xdr:rowOff>99060</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -2047,7 +2065,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{457F1634-390D-461A-B4FA-B698C0706EE9}">
-  <dimension ref="A2:W76"/>
+  <dimension ref="A2:W78"/>
   <sheetFormatPr defaultColWidth="3.6640625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="2" width="3.6640625" style="5" customWidth="1"/>
@@ -2083,92 +2101,92 @@
       <c r="T2" s="6"/>
     </row>
     <row r="3" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="63"/>
-      <c r="B3" s="63"/>
-      <c r="C3" s="63"/>
-      <c r="D3" s="63"/>
-      <c r="E3" s="63"/>
-      <c r="F3" s="63"/>
-      <c r="G3" s="63"/>
-      <c r="H3" s="63"/>
-      <c r="I3" s="63"/>
-      <c r="J3" s="63"/>
-      <c r="K3" s="63"/>
-      <c r="L3" s="63"/>
-      <c r="M3" s="63"/>
-      <c r="N3" s="63"/>
-      <c r="O3" s="63"/>
-      <c r="P3" s="63"/>
-      <c r="Q3" s="63"/>
-      <c r="R3" s="63"/>
-      <c r="S3" s="63"/>
-      <c r="T3" s="63"/>
+      <c r="A3" s="49"/>
+      <c r="B3" s="49"/>
+      <c r="C3" s="49"/>
+      <c r="D3" s="49"/>
+      <c r="E3" s="49"/>
+      <c r="F3" s="49"/>
+      <c r="G3" s="49"/>
+      <c r="H3" s="49"/>
+      <c r="I3" s="49"/>
+      <c r="J3" s="49"/>
+      <c r="K3" s="49"/>
+      <c r="L3" s="49"/>
+      <c r="M3" s="49"/>
+      <c r="N3" s="49"/>
+      <c r="O3" s="49"/>
+      <c r="P3" s="49"/>
+      <c r="Q3" s="49"/>
+      <c r="R3" s="49"/>
+      <c r="S3" s="49"/>
+      <c r="T3" s="49"/>
     </row>
     <row r="4" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="64"/>
-      <c r="B4" s="64"/>
-      <c r="C4" s="64"/>
-      <c r="D4" s="64"/>
-      <c r="E4" s="64"/>
-      <c r="F4" s="64"/>
-      <c r="G4" s="64"/>
-      <c r="H4" s="64"/>
-      <c r="I4" s="64"/>
-      <c r="J4" s="64"/>
-      <c r="K4" s="64"/>
-      <c r="L4" s="64"/>
-      <c r="M4" s="64"/>
-      <c r="N4" s="64"/>
-      <c r="O4" s="64"/>
-      <c r="P4" s="64"/>
-      <c r="Q4" s="64"/>
-      <c r="R4" s="64"/>
-      <c r="S4" s="64"/>
-      <c r="T4" s="64"/>
+      <c r="A4" s="80"/>
+      <c r="B4" s="80"/>
+      <c r="C4" s="80"/>
+      <c r="D4" s="80"/>
+      <c r="E4" s="80"/>
+      <c r="F4" s="80"/>
+      <c r="G4" s="80"/>
+      <c r="H4" s="80"/>
+      <c r="I4" s="80"/>
+      <c r="J4" s="80"/>
+      <c r="K4" s="80"/>
+      <c r="L4" s="80"/>
+      <c r="M4" s="80"/>
+      <c r="N4" s="80"/>
+      <c r="O4" s="80"/>
+      <c r="P4" s="80"/>
+      <c r="Q4" s="80"/>
+      <c r="R4" s="80"/>
+      <c r="S4" s="80"/>
+      <c r="T4" s="80"/>
     </row>
     <row r="5" spans="1:20" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="65"/>
-      <c r="B5" s="65"/>
-      <c r="C5" s="65"/>
-      <c r="D5" s="65"/>
-      <c r="E5" s="65"/>
-      <c r="F5" s="65"/>
-      <c r="G5" s="65"/>
-      <c r="H5" s="65"/>
-      <c r="I5" s="65"/>
-      <c r="J5" s="65"/>
-      <c r="K5" s="65"/>
-      <c r="L5" s="65"/>
-      <c r="M5" s="65"/>
-      <c r="N5" s="65"/>
-      <c r="O5" s="65"/>
-      <c r="P5" s="65"/>
-      <c r="Q5" s="65"/>
-      <c r="R5" s="65"/>
-      <c r="S5" s="65"/>
-      <c r="T5" s="65"/>
+      <c r="A5" s="81"/>
+      <c r="B5" s="81"/>
+      <c r="C5" s="81"/>
+      <c r="D5" s="81"/>
+      <c r="E5" s="81"/>
+      <c r="F5" s="81"/>
+      <c r="G5" s="81"/>
+      <c r="H5" s="81"/>
+      <c r="I5" s="81"/>
+      <c r="J5" s="81"/>
+      <c r="K5" s="81"/>
+      <c r="L5" s="81"/>
+      <c r="M5" s="81"/>
+      <c r="N5" s="81"/>
+      <c r="O5" s="81"/>
+      <c r="P5" s="81"/>
+      <c r="Q5" s="81"/>
+      <c r="R5" s="81"/>
+      <c r="S5" s="81"/>
+      <c r="T5" s="81"/>
     </row>
     <row r="6" spans="1:20" ht="30.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="63"/>
-      <c r="B6" s="63"/>
-      <c r="C6" s="63"/>
-      <c r="D6" s="63"/>
-      <c r="E6" s="63"/>
-      <c r="F6" s="63"/>
-      <c r="G6" s="63"/>
-      <c r="H6" s="63"/>
-      <c r="I6" s="63"/>
-      <c r="J6" s="63"/>
-      <c r="K6" s="63"/>
-      <c r="L6" s="63"/>
-      <c r="M6" s="63"/>
-      <c r="N6" s="63"/>
-      <c r="O6" s="63"/>
-      <c r="P6" s="63"/>
-      <c r="Q6" s="63"/>
-      <c r="R6" s="63"/>
-      <c r="S6" s="63"/>
-      <c r="T6" s="63"/>
+      <c r="A6" s="49"/>
+      <c r="B6" s="49"/>
+      <c r="C6" s="49"/>
+      <c r="D6" s="49"/>
+      <c r="E6" s="49"/>
+      <c r="F6" s="49"/>
+      <c r="G6" s="49"/>
+      <c r="H6" s="49"/>
+      <c r="I6" s="49"/>
+      <c r="J6" s="49"/>
+      <c r="K6" s="49"/>
+      <c r="L6" s="49"/>
+      <c r="M6" s="49"/>
+      <c r="N6" s="49"/>
+      <c r="O6" s="49"/>
+      <c r="P6" s="49"/>
+      <c r="Q6" s="49"/>
+      <c r="R6" s="49"/>
+      <c r="S6" s="49"/>
+      <c r="T6" s="49"/>
     </row>
     <row r="7" spans="1:20" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="7"/>
@@ -2267,7 +2285,7 @@
         <v>8</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="H11" s="11" t="s">
         <v>9</v>
@@ -2281,7 +2299,7 @@
         <v>8</v>
       </c>
       <c r="N11" s="14" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="S11" s="10"/>
       <c r="T11" s="15"/>
@@ -2293,7 +2311,7 @@
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D12" s="37"/>
+      <c r="D12" s="35"/>
       <c r="E12" s="1"/>
       <c r="H12" s="11" t="s">
         <v>16</v>
@@ -2306,14 +2324,14 @@
       <c r="M12" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="N12" s="66" t="s">
-        <v>36</v>
-      </c>
-      <c r="O12" s="66"/>
-      <c r="P12" s="66"/>
-      <c r="Q12" s="66"/>
-      <c r="R12" s="66"/>
-      <c r="S12" s="66"/>
+      <c r="N12" s="82" t="s">
+        <v>41</v>
+      </c>
+      <c r="O12" s="82"/>
+      <c r="P12" s="82"/>
+      <c r="Q12" s="82"/>
+      <c r="R12" s="82"/>
+      <c r="S12" s="82"/>
       <c r="T12" s="17"/>
     </row>
     <row r="13" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -2335,7 +2353,7 @@
         <v>8</v>
       </c>
       <c r="N13" s="5" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="T13" s="17"/>
     </row>
@@ -2347,10 +2365,10 @@
         <v>8</v>
       </c>
       <c r="E14" s="1"/>
-      <c r="K14" s="67"/>
-      <c r="L14" s="68"/>
-      <c r="M14" s="68"/>
-      <c r="N14" s="68"/>
+      <c r="K14" s="51"/>
+      <c r="L14" s="52"/>
+      <c r="M14" s="52"/>
+      <c r="N14" s="52"/>
       <c r="O14" s="1"/>
       <c r="P14" s="19"/>
       <c r="Q14" s="1"/>
@@ -2377,18 +2395,18 @@
       <c r="K15" s="8"/>
       <c r="L15" s="23"/>
       <c r="M15" s="8"/>
-      <c r="N15" s="83" t="s">
-        <v>26</v>
-      </c>
-      <c r="O15" s="83"/>
-      <c r="P15" s="83"/>
-      <c r="Q15" s="83"/>
-      <c r="R15" s="83"/>
-      <c r="S15" s="83"/>
-      <c r="T15" s="84"/>
+      <c r="N15" s="67" t="s">
+        <v>25</v>
+      </c>
+      <c r="O15" s="67"/>
+      <c r="P15" s="67"/>
+      <c r="Q15" s="67"/>
+      <c r="R15" s="67"/>
+      <c r="S15" s="67"/>
+      <c r="T15" s="68"/>
     </row>
     <row r="16" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="54"/>
+      <c r="A16" s="41"/>
       <c r="C16" s="1"/>
       <c r="E16" s="24"/>
       <c r="F16" s="24"/>
@@ -2403,357 +2421,353 @@
       <c r="T16" s="7"/>
     </row>
     <row r="17" spans="1:20" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="79" t="s">
+      <c r="A17" s="63" t="s">
         <v>0</v>
       </c>
-      <c r="B17" s="72"/>
-      <c r="C17" s="72" t="s">
+      <c r="B17" s="56"/>
+      <c r="C17" s="56" t="s">
         <v>18</v>
       </c>
-      <c r="D17" s="72"/>
-      <c r="E17" s="74" t="s">
+      <c r="D17" s="56"/>
+      <c r="E17" s="58" t="s">
         <v>1</v>
       </c>
-      <c r="F17" s="75"/>
-      <c r="G17" s="76"/>
-      <c r="H17" s="79" t="s">
+      <c r="F17" s="59"/>
+      <c r="G17" s="60"/>
+      <c r="H17" s="63" t="s">
         <v>20</v>
       </c>
-      <c r="I17" s="85"/>
-      <c r="J17" s="85"/>
-      <c r="K17" s="85"/>
-      <c r="L17" s="86"/>
-      <c r="M17" s="79" t="s">
+      <c r="I17" s="69"/>
+      <c r="J17" s="69"/>
+      <c r="K17" s="69"/>
+      <c r="L17" s="70"/>
+      <c r="M17" s="63" t="s">
         <v>2</v>
       </c>
-      <c r="N17" s="72"/>
-      <c r="O17" s="72"/>
-      <c r="P17" s="80"/>
-      <c r="Q17" s="79" t="s">
+      <c r="N17" s="56"/>
+      <c r="O17" s="56"/>
+      <c r="P17" s="64"/>
+      <c r="Q17" s="63" t="s">
         <v>11</v>
       </c>
-      <c r="R17" s="72"/>
-      <c r="S17" s="72"/>
-      <c r="T17" s="80"/>
+      <c r="R17" s="56"/>
+      <c r="S17" s="56"/>
+      <c r="T17" s="64"/>
     </row>
     <row r="18" spans="1:20" s="25" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="81"/>
-      <c r="B18" s="73"/>
-      <c r="C18" s="73"/>
-      <c r="D18" s="73"/>
-      <c r="E18" s="77"/>
-      <c r="F18" s="77"/>
-      <c r="G18" s="78"/>
-      <c r="H18" s="87"/>
-      <c r="I18" s="88"/>
-      <c r="J18" s="88"/>
-      <c r="K18" s="88"/>
-      <c r="L18" s="89"/>
-      <c r="M18" s="81"/>
-      <c r="N18" s="73"/>
-      <c r="O18" s="73"/>
-      <c r="P18" s="82"/>
-      <c r="Q18" s="81"/>
-      <c r="R18" s="73"/>
-      <c r="S18" s="73"/>
-      <c r="T18" s="82"/>
+      <c r="A18" s="65"/>
+      <c r="B18" s="57"/>
+      <c r="C18" s="57"/>
+      <c r="D18" s="57"/>
+      <c r="E18" s="61"/>
+      <c r="F18" s="61"/>
+      <c r="G18" s="62"/>
+      <c r="H18" s="71"/>
+      <c r="I18" s="72"/>
+      <c r="J18" s="72"/>
+      <c r="K18" s="72"/>
+      <c r="L18" s="73"/>
+      <c r="M18" s="65"/>
+      <c r="N18" s="57"/>
+      <c r="O18" s="57"/>
+      <c r="P18" s="66"/>
+      <c r="Q18" s="65"/>
+      <c r="R18" s="57"/>
+      <c r="S18" s="57"/>
+      <c r="T18" s="66"/>
     </row>
     <row r="19" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="47"/>
-      <c r="B19" s="48"/>
-      <c r="C19" s="47"/>
-      <c r="D19" s="48"/>
-      <c r="E19" s="49"/>
-      <c r="F19" s="49"/>
-      <c r="G19" s="49"/>
-      <c r="H19" s="47"/>
-      <c r="I19" s="50"/>
-      <c r="J19" s="50"/>
-      <c r="K19" s="50"/>
-      <c r="L19" s="48"/>
-      <c r="M19" s="47"/>
-      <c r="N19" s="50"/>
-      <c r="O19" s="50"/>
-      <c r="P19" s="50"/>
-      <c r="Q19" s="47"/>
-      <c r="R19" s="50"/>
-      <c r="S19" s="50"/>
-      <c r="T19" s="48"/>
+      <c r="A19" s="88"/>
+      <c r="B19" s="89"/>
+      <c r="C19" s="88"/>
+      <c r="D19" s="89"/>
+      <c r="E19" s="83"/>
+      <c r="F19" s="84"/>
+      <c r="G19" s="85"/>
+      <c r="H19" s="88"/>
+      <c r="I19" s="94"/>
+      <c r="J19" s="94"/>
+      <c r="K19" s="94"/>
+      <c r="L19" s="89"/>
+      <c r="M19" s="88"/>
+      <c r="N19" s="94"/>
+      <c r="O19" s="94"/>
+      <c r="P19" s="89"/>
+      <c r="Q19" s="88"/>
+      <c r="R19" s="94"/>
+      <c r="S19" s="94"/>
+      <c r="T19" s="89"/>
     </row>
     <row r="20" spans="1:20" s="18" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="55">
-        <v>1</v>
-      </c>
-      <c r="B20" s="56"/>
-      <c r="C20" s="55">
-        <v>1</v>
-      </c>
-      <c r="D20" s="56"/>
-      <c r="E20" s="90" t="s">
+      <c r="A20" s="74" t="s">
+        <v>43</v>
+      </c>
+      <c r="B20" s="50"/>
+      <c r="C20" s="74" t="s">
+        <v>44</v>
+      </c>
+      <c r="D20" s="50"/>
+      <c r="E20" s="75" t="s">
+        <v>45</v>
+      </c>
+      <c r="F20" s="53"/>
+      <c r="G20" s="76"/>
+      <c r="H20" s="90" t="s">
+        <v>46</v>
+      </c>
+      <c r="I20" s="91"/>
+      <c r="J20" s="91"/>
+      <c r="K20" s="91"/>
+      <c r="L20" s="92"/>
+      <c r="M20" s="95" t="s">
+        <v>47</v>
+      </c>
+      <c r="N20" s="96"/>
+      <c r="O20" s="96"/>
+      <c r="P20" s="97"/>
+      <c r="Q20" s="95" t="s">
+        <v>34</v>
+      </c>
+      <c r="R20" s="96"/>
+      <c r="S20" s="96"/>
+      <c r="T20" s="97"/>
+    </row>
+    <row r="21" spans="1:20" s="18" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="74"/>
+      <c r="B21" s="50"/>
+      <c r="C21" s="74"/>
+      <c r="D21" s="50"/>
+      <c r="E21" s="75"/>
+      <c r="F21" s="53"/>
+      <c r="G21" s="76"/>
+      <c r="H21" s="90"/>
+      <c r="I21" s="91"/>
+      <c r="J21" s="91"/>
+      <c r="K21" s="91"/>
+      <c r="L21" s="92"/>
+      <c r="M21" s="74"/>
+      <c r="N21" s="49"/>
+      <c r="O21" s="49"/>
+      <c r="P21" s="50"/>
+      <c r="Q21" s="74"/>
+      <c r="R21" s="49"/>
+      <c r="S21" s="49"/>
+      <c r="T21" s="50"/>
+    </row>
+    <row r="22" spans="1:20" s="18" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="74"/>
+      <c r="B22" s="50"/>
+      <c r="C22" s="74"/>
+      <c r="D22" s="50"/>
+      <c r="E22" s="75"/>
+      <c r="F22" s="53"/>
+      <c r="G22" s="76"/>
+      <c r="H22" s="90"/>
+      <c r="I22" s="91"/>
+      <c r="J22" s="91"/>
+      <c r="K22" s="91"/>
+      <c r="L22" s="92"/>
+      <c r="M22" s="74"/>
+      <c r="N22" s="49"/>
+      <c r="O22" s="49"/>
+      <c r="P22" s="50"/>
+      <c r="Q22" s="74"/>
+      <c r="R22" s="49"/>
+      <c r="S22" s="49"/>
+      <c r="T22" s="50"/>
+    </row>
+    <row r="23" spans="1:20" s="18" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A23" s="86"/>
+      <c r="B23" s="87"/>
+      <c r="C23" s="86"/>
+      <c r="D23" s="87"/>
+      <c r="E23" s="77"/>
+      <c r="F23" s="78"/>
+      <c r="G23" s="79"/>
+      <c r="H23" s="86"/>
+      <c r="I23" s="93"/>
+      <c r="J23" s="93"/>
+      <c r="K23" s="93"/>
+      <c r="L23" s="87"/>
+      <c r="M23" s="86"/>
+      <c r="N23" s="93"/>
+      <c r="O23" s="93"/>
+      <c r="P23" s="87"/>
+      <c r="Q23" s="86"/>
+      <c r="R23" s="93"/>
+      <c r="S23" s="93"/>
+      <c r="T23" s="87"/>
+    </row>
+    <row r="24" spans="1:20" s="18" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A24" s="7"/>
+      <c r="B24" s="7"/>
+      <c r="C24" s="7"/>
+      <c r="D24" s="7"/>
+      <c r="E24" s="42"/>
+      <c r="F24" s="42"/>
+      <c r="G24" s="42"/>
+      <c r="H24" s="31" t="s">
+        <v>35</v>
+      </c>
+      <c r="I24" s="7"/>
+      <c r="J24" s="7"/>
+      <c r="K24" s="7"/>
+      <c r="L24" s="7"/>
+      <c r="M24" s="7"/>
+      <c r="N24" s="7"/>
+      <c r="O24" s="7"/>
+      <c r="P24" s="7"/>
+      <c r="Q24" s="47" t="s">
+        <v>37</v>
+      </c>
+      <c r="R24" s="47"/>
+      <c r="S24" s="47"/>
+      <c r="T24" s="48"/>
+    </row>
+    <row r="25" spans="1:20" s="18" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A25" s="7"/>
+      <c r="B25" s="7"/>
+      <c r="C25" s="7"/>
+      <c r="D25" s="7"/>
+      <c r="E25" s="42"/>
+      <c r="F25" s="42"/>
+      <c r="G25" s="42"/>
+      <c r="H25" s="31" t="s">
+        <v>36</v>
+      </c>
+      <c r="I25" s="7"/>
+      <c r="J25" s="7"/>
+      <c r="K25" s="7"/>
+      <c r="L25" s="7"/>
+      <c r="M25" s="7"/>
+      <c r="N25" s="7"/>
+      <c r="O25" s="7"/>
+      <c r="P25" s="7"/>
+      <c r="Q25" s="49" t="s">
         <v>38</v>
       </c>
-      <c r="F20" s="69"/>
-      <c r="G20" s="91"/>
-      <c r="H20" s="57">
-        <v>8</v>
-      </c>
-      <c r="I20" s="58"/>
-      <c r="J20" s="58"/>
-      <c r="K20" s="58"/>
-      <c r="L20" s="59"/>
-      <c r="M20" s="60">
-        <v>480</v>
-      </c>
-      <c r="N20" s="61"/>
-      <c r="O20" s="61"/>
-      <c r="P20" s="62"/>
-      <c r="Q20" s="60">
-        <f>M20*C20</f>
-        <v>480</v>
-      </c>
-      <c r="R20" s="61"/>
-      <c r="S20" s="61"/>
-      <c r="T20" s="62"/>
-    </row>
-    <row r="21" spans="1:20" s="18" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="26"/>
-      <c r="B21" s="27"/>
-      <c r="C21" s="55" t="s">
-        <v>35</v>
-      </c>
-      <c r="D21" s="56"/>
-      <c r="E21" s="90"/>
-      <c r="F21" s="69"/>
-      <c r="G21" s="91"/>
-      <c r="H21" s="57" t="s">
-        <v>34</v>
-      </c>
-      <c r="I21" s="58"/>
-      <c r="J21" s="58"/>
-      <c r="K21" s="58"/>
-      <c r="L21" s="59"/>
-      <c r="M21" s="55"/>
-      <c r="N21" s="63"/>
-      <c r="O21" s="63"/>
-      <c r="P21" s="56"/>
-      <c r="Q21" s="55"/>
-      <c r="R21" s="63"/>
-      <c r="S21" s="63"/>
-      <c r="T21" s="56"/>
-    </row>
-    <row r="22" spans="1:20" s="18" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="26"/>
-      <c r="B22" s="27"/>
-      <c r="C22" s="26"/>
-      <c r="D22" s="27"/>
-      <c r="E22" s="90"/>
-      <c r="F22" s="69"/>
-      <c r="G22" s="91"/>
-      <c r="H22" s="46"/>
-      <c r="I22" s="44"/>
-      <c r="J22" s="44"/>
-      <c r="K22" s="44"/>
-      <c r="L22" s="45"/>
-      <c r="M22" s="55"/>
-      <c r="N22" s="63"/>
-      <c r="O22" s="63"/>
-      <c r="P22" s="56"/>
-      <c r="Q22" s="55"/>
-      <c r="R22" s="63"/>
-      <c r="S22" s="63"/>
-      <c r="T22" s="56"/>
-    </row>
-    <row r="23" spans="1:20" s="18" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="26"/>
-      <c r="B23" s="27"/>
-      <c r="C23" s="26"/>
-      <c r="D23" s="27"/>
-      <c r="E23" s="92"/>
-      <c r="F23" s="93"/>
-      <c r="G23" s="94"/>
-      <c r="H23" s="26"/>
-      <c r="I23" s="44"/>
-      <c r="J23" s="44"/>
-      <c r="K23" s="44"/>
-      <c r="L23" s="45"/>
-      <c r="M23" s="95"/>
-      <c r="N23" s="96"/>
-      <c r="O23" s="96"/>
-      <c r="P23" s="97"/>
-      <c r="Q23" s="95"/>
-      <c r="R23" s="96"/>
-      <c r="S23" s="96"/>
-      <c r="T23" s="97"/>
-    </row>
-    <row r="24" spans="1:20" s="18" customFormat="1" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A24" s="38"/>
-      <c r="B24" s="39"/>
-      <c r="C24" s="39"/>
-      <c r="D24" s="39"/>
-      <c r="E24" s="39"/>
-      <c r="F24" s="39"/>
-      <c r="G24" s="39"/>
-      <c r="H24" s="40" t="s">
+      <c r="R25" s="49"/>
+      <c r="S25" s="49"/>
+      <c r="T25" s="50"/>
+    </row>
+    <row r="26" spans="1:20" s="18" customFormat="1" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A26" s="43"/>
+      <c r="B26" s="44"/>
+      <c r="C26" s="44"/>
+      <c r="D26" s="44"/>
+      <c r="E26" s="44"/>
+      <c r="F26" s="44"/>
+      <c r="G26" s="44"/>
+      <c r="H26" s="45" t="s">
         <v>23</v>
       </c>
-      <c r="I24" s="39"/>
-      <c r="J24" s="40" t="s">
+      <c r="I26" s="44"/>
+      <c r="J26" s="45" t="s">
         <v>19</v>
       </c>
-      <c r="K24" s="39"/>
-      <c r="L24" s="39"/>
-      <c r="M24" s="39"/>
-      <c r="N24" s="39"/>
-      <c r="O24" s="39"/>
-      <c r="P24" s="51"/>
-      <c r="Q24" s="70">
-        <f>SUM(Q20:T23)</f>
-        <v>480</v>
-      </c>
-      <c r="R24" s="70"/>
-      <c r="S24" s="70"/>
-      <c r="T24" s="71"/>
-    </row>
-    <row r="25" spans="1:20" s="18" customFormat="1" ht="18" customHeight="1" thickTop="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="5"/>
-      <c r="B25" s="5"/>
-      <c r="C25" s="5"/>
-      <c r="D25" s="5"/>
-      <c r="E25" s="5"/>
-      <c r="F25" s="5"/>
-      <c r="G25" s="5"/>
-      <c r="I25" s="5"/>
-      <c r="K25" s="5"/>
-      <c r="L25" s="5"/>
-      <c r="M25" s="5"/>
-      <c r="N25" s="5"/>
-      <c r="O25" s="5"/>
-      <c r="P25" s="41"/>
-      <c r="Q25" s="42"/>
-      <c r="R25" s="42"/>
-      <c r="S25" s="42"/>
-      <c r="T25" s="42"/>
-    </row>
-    <row r="26" spans="1:20" s="18" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A26" s="29" t="s">
-        <v>12</v>
-      </c>
-      <c r="B26" s="10"/>
-      <c r="C26" s="10"/>
-      <c r="D26" s="10"/>
-      <c r="E26" s="10"/>
-      <c r="F26" s="13" t="s">
-        <v>8</v>
-      </c>
-      <c r="G26" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="H26" s="10"/>
-      <c r="I26" s="10"/>
-      <c r="J26" s="10"/>
-      <c r="K26" s="10"/>
-      <c r="L26" s="10"/>
-      <c r="M26" s="10"/>
-      <c r="N26" s="10"/>
-      <c r="O26" s="10"/>
-      <c r="P26" s="10"/>
-      <c r="Q26" s="10"/>
-      <c r="R26" s="10"/>
-      <c r="S26" s="10"/>
-      <c r="T26" s="15"/>
-    </row>
-    <row r="27" spans="1:20" s="18" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A27" s="30" t="s">
-        <v>13</v>
-      </c>
+      <c r="K26" s="44"/>
+      <c r="L26" s="44"/>
+      <c r="M26" s="44"/>
+      <c r="N26" s="44"/>
+      <c r="O26" s="44"/>
+      <c r="P26" s="46"/>
+      <c r="Q26" s="54" t="s">
+        <v>48</v>
+      </c>
+      <c r="R26" s="54"/>
+      <c r="S26" s="54"/>
+      <c r="T26" s="55"/>
+    </row>
+    <row r="27" spans="1:20" s="18" customFormat="1" ht="18" customHeight="1" thickTop="1" x14ac:dyDescent="0.35">
+      <c r="A27" s="5"/>
       <c r="B27" s="5"/>
       <c r="C27" s="5"/>
       <c r="D27" s="5"/>
       <c r="E27" s="5"/>
-      <c r="F27" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="G27" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="H27" s="5"/>
+      <c r="F27" s="5"/>
+      <c r="G27" s="5"/>
       <c r="I27" s="5"/>
-      <c r="J27" s="5"/>
       <c r="K27" s="5"/>
       <c r="L27" s="5"/>
       <c r="M27" s="5"/>
       <c r="N27" s="5"/>
       <c r="O27" s="5"/>
-      <c r="P27" s="5"/>
-      <c r="Q27" s="5"/>
-      <c r="R27" s="5"/>
-      <c r="S27" s="5"/>
-      <c r="T27" s="17"/>
+      <c r="P27" s="36"/>
+      <c r="Q27" s="37"/>
+      <c r="R27" s="37"/>
+      <c r="S27" s="37"/>
+      <c r="T27" s="37"/>
     </row>
     <row r="28" spans="1:20" s="18" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="30" t="s">
+      <c r="A28" s="27" t="s">
+        <v>12</v>
+      </c>
+      <c r="B28" s="10"/>
+      <c r="C28" s="10"/>
+      <c r="D28" s="10"/>
+      <c r="E28" s="10"/>
+      <c r="F28" s="13" t="s">
+        <v>8</v>
+      </c>
+      <c r="G28" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="H28" s="10"/>
+      <c r="I28" s="10"/>
+      <c r="J28" s="10"/>
+      <c r="K28" s="10"/>
+      <c r="L28" s="10"/>
+      <c r="M28" s="10"/>
+      <c r="N28" s="10"/>
+      <c r="O28" s="10"/>
+      <c r="P28" s="10"/>
+      <c r="Q28" s="10"/>
+      <c r="R28" s="10"/>
+      <c r="S28" s="10"/>
+      <c r="T28" s="15"/>
+    </row>
+    <row r="29" spans="1:20" s="18" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A29" s="28" t="s">
+        <v>13</v>
+      </c>
+      <c r="B29" s="5"/>
+      <c r="C29" s="5"/>
+      <c r="D29" s="5"/>
+      <c r="E29" s="5"/>
+      <c r="F29" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G29" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="H29" s="5"/>
+      <c r="I29" s="5"/>
+      <c r="J29" s="5"/>
+      <c r="K29" s="5"/>
+      <c r="L29" s="5"/>
+      <c r="M29" s="5"/>
+      <c r="N29" s="5"/>
+      <c r="O29" s="5"/>
+      <c r="P29" s="5"/>
+      <c r="Q29" s="5"/>
+      <c r="R29" s="5"/>
+      <c r="S29" s="5"/>
+      <c r="T29" s="17"/>
+    </row>
+    <row r="30" spans="1:20" s="18" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A30" s="28" t="s">
         <v>14</v>
       </c>
-      <c r="B28" s="5"/>
-      <c r="C28" s="5"/>
-      <c r="D28" s="5"/>
-      <c r="E28" s="5"/>
-      <c r="F28" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="G28" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="H28" s="5"/>
-      <c r="I28" s="5"/>
-      <c r="J28" s="5"/>
-      <c r="K28" s="5"/>
-      <c r="L28" s="5"/>
-      <c r="M28" s="5"/>
-      <c r="N28" s="5"/>
-      <c r="O28" s="5"/>
-      <c r="P28" s="5"/>
-      <c r="Q28" s="5"/>
-      <c r="R28" s="5"/>
-      <c r="S28" s="5"/>
-      <c r="T28" s="17"/>
-    </row>
-    <row r="29" spans="1:20" s="18" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="31" t="s">
-        <v>15</v>
-      </c>
-      <c r="B29" s="8"/>
-      <c r="C29" s="8"/>
-      <c r="D29" s="8"/>
-      <c r="E29" s="8"/>
-      <c r="F29" s="21" t="s">
-        <v>8</v>
-      </c>
-      <c r="G29" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="H29" s="8"/>
-      <c r="I29" s="8"/>
-      <c r="J29" s="8"/>
-      <c r="K29" s="8"/>
-      <c r="L29" s="8"/>
-      <c r="M29" s="8"/>
-      <c r="N29" s="8"/>
-      <c r="O29" s="8"/>
-      <c r="P29" s="8"/>
-      <c r="Q29" s="8"/>
-      <c r="R29" s="8"/>
-      <c r="S29" s="8"/>
-      <c r="T29" s="32"/>
-    </row>
-    <row r="30" spans="1:20" s="18" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="5"/>
       <c r="B30" s="5"/>
       <c r="C30" s="5"/>
       <c r="D30" s="5"/>
       <c r="E30" s="5"/>
-      <c r="F30" s="1"/>
-      <c r="G30" s="5"/>
+      <c r="F30" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G30" s="5" t="s">
+        <v>50</v>
+      </c>
       <c r="H30" s="5"/>
       <c r="I30" s="5"/>
       <c r="J30" s="5"/>
@@ -2766,155 +2780,159 @@
       <c r="Q30" s="5"/>
       <c r="R30" s="5"/>
       <c r="S30" s="5"/>
-      <c r="T30" s="5"/>
-    </row>
-    <row r="31" spans="1:20" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A31" s="52" t="s">
-        <v>40</v>
-      </c>
-      <c r="B31" s="52"/>
-      <c r="C31" s="52"/>
-      <c r="D31" s="52"/>
-      <c r="E31" s="52"/>
-      <c r="F31" s="52"/>
-      <c r="G31" s="52"/>
-      <c r="H31" s="52"/>
-      <c r="I31" s="52"/>
-      <c r="J31" s="52"/>
-    </row>
-    <row r="32" spans="1:20" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A32" s="52"/>
-      <c r="B32" s="52"/>
-      <c r="C32" s="52"/>
-      <c r="D32" s="52"/>
-      <c r="E32" s="52"/>
-      <c r="F32" s="52"/>
-      <c r="G32" s="52"/>
-      <c r="H32" s="52"/>
-      <c r="I32" s="52"/>
-      <c r="J32" s="52"/>
+      <c r="T30" s="17"/>
+    </row>
+    <row r="31" spans="1:20" s="18" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A31" s="29" t="s">
+        <v>15</v>
+      </c>
+      <c r="B31" s="8"/>
+      <c r="C31" s="8"/>
+      <c r="D31" s="8"/>
+      <c r="E31" s="8"/>
+      <c r="F31" s="21" t="s">
+        <v>8</v>
+      </c>
+      <c r="G31" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="H31" s="8"/>
+      <c r="I31" s="8"/>
+      <c r="J31" s="8"/>
+      <c r="K31" s="8"/>
+      <c r="L31" s="8"/>
+      <c r="M31" s="8"/>
+      <c r="N31" s="8"/>
+      <c r="O31" s="8"/>
+      <c r="P31" s="8"/>
+      <c r="Q31" s="8"/>
+      <c r="R31" s="8"/>
+      <c r="S31" s="8"/>
+      <c r="T31" s="30"/>
+    </row>
+    <row r="32" spans="1:20" s="18" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A32" s="5"/>
+      <c r="B32" s="5"/>
+      <c r="C32" s="5"/>
+      <c r="D32" s="5"/>
+      <c r="E32" s="5"/>
+      <c r="F32" s="1"/>
+      <c r="G32" s="5"/>
+      <c r="H32" s="5"/>
+      <c r="I32" s="5"/>
+      <c r="J32" s="5"/>
+      <c r="K32" s="5"/>
+      <c r="L32" s="5"/>
+      <c r="M32" s="5"/>
+      <c r="N32" s="5"/>
+      <c r="O32" s="5"/>
+      <c r="P32" s="5"/>
+      <c r="Q32" s="5"/>
+      <c r="R32" s="5"/>
+      <c r="S32" s="5"/>
+      <c r="T32" s="5"/>
     </row>
     <row r="33" spans="1:20" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A33" s="53">
+      <c r="A33" s="39" t="s">
+        <v>30</v>
+      </c>
+      <c r="B33" s="39"/>
+      <c r="C33" s="39"/>
+      <c r="D33" s="39"/>
+      <c r="E33" s="39"/>
+      <c r="F33" s="39"/>
+      <c r="G33" s="39"/>
+      <c r="H33" s="39"/>
+      <c r="I33" s="39"/>
+      <c r="J33" s="39"/>
+    </row>
+    <row r="34" spans="1:20" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A34" s="39"/>
+      <c r="B34" s="39"/>
+      <c r="C34" s="39"/>
+      <c r="D34" s="39"/>
+      <c r="E34" s="39"/>
+      <c r="F34" s="39"/>
+      <c r="G34" s="39"/>
+      <c r="H34" s="39"/>
+      <c r="I34" s="39"/>
+      <c r="J34" s="39"/>
+    </row>
+    <row r="35" spans="1:20" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A35" s="40">
         <v>1</v>
       </c>
-      <c r="B33" s="52" t="s">
-        <v>41</v>
-      </c>
-      <c r="C33" s="52"/>
-      <c r="D33" s="52"/>
-      <c r="E33" s="52"/>
-      <c r="F33" s="52"/>
-      <c r="G33" s="52"/>
-      <c r="H33" s="52"/>
-      <c r="I33" s="52"/>
-      <c r="J33" s="52"/>
-    </row>
-    <row r="34" spans="1:20" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A34" s="53">
+      <c r="B35" s="39" t="s">
+        <v>31</v>
+      </c>
+      <c r="C35" s="39"/>
+      <c r="D35" s="39"/>
+      <c r="E35" s="39"/>
+      <c r="F35" s="39"/>
+      <c r="G35" s="39"/>
+      <c r="H35" s="39"/>
+      <c r="I35" s="39"/>
+      <c r="J35" s="39"/>
+    </row>
+    <row r="36" spans="1:20" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A36" s="40">
         <v>2</v>
       </c>
-      <c r="B34" s="52" t="s">
-        <v>42</v>
-      </c>
-      <c r="C34" s="52"/>
-      <c r="D34" s="52"/>
-      <c r="E34" s="52"/>
-      <c r="F34" s="52"/>
-      <c r="G34" s="52"/>
-      <c r="H34" s="52"/>
-      <c r="I34" s="52"/>
-      <c r="J34" s="52"/>
-    </row>
-    <row r="35" spans="1:20" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A35" s="53">
+      <c r="B36" s="39" t="s">
+        <v>32</v>
+      </c>
+      <c r="C36" s="39"/>
+      <c r="D36" s="39"/>
+      <c r="E36" s="39"/>
+      <c r="F36" s="39"/>
+      <c r="G36" s="39"/>
+      <c r="H36" s="39"/>
+      <c r="I36" s="39"/>
+      <c r="J36" s="39"/>
+    </row>
+    <row r="37" spans="1:20" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A37" s="40">
         <v>3</v>
       </c>
-      <c r="B35" s="52" t="s">
-        <v>43</v>
-      </c>
-      <c r="C35" s="52"/>
-      <c r="D35" s="52"/>
-      <c r="E35" s="52"/>
-      <c r="F35" s="52"/>
-      <c r="G35" s="52"/>
-      <c r="H35" s="52"/>
-      <c r="I35" s="52"/>
-      <c r="J35" s="52"/>
-    </row>
-    <row r="36" spans="1:20" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A36" s="52"/>
-      <c r="B36" s="52" t="s">
-        <v>39</v>
-      </c>
-      <c r="C36" s="52"/>
-      <c r="D36" s="52"/>
-      <c r="E36" s="52"/>
-      <c r="F36" s="52"/>
-      <c r="G36" s="52"/>
-      <c r="H36" s="52"/>
-      <c r="I36" s="52"/>
-      <c r="J36" s="52"/>
-    </row>
-    <row r="37" spans="1:20" s="18" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A37" s="5"/>
-      <c r="B37" s="5"/>
-      <c r="C37" s="5"/>
-      <c r="D37" s="5"/>
-      <c r="E37" s="5"/>
-      <c r="F37" s="1"/>
-      <c r="G37" s="5"/>
-      <c r="H37" s="5"/>
-      <c r="I37" s="5"/>
-      <c r="J37" s="5"/>
-      <c r="K37" s="5"/>
-      <c r="L37" s="5"/>
-      <c r="M37" s="5"/>
-      <c r="N37" s="5"/>
-      <c r="O37" s="5"/>
-      <c r="P37" s="5"/>
-      <c r="Q37" s="5"/>
-      <c r="R37" s="5"/>
-      <c r="S37" s="5"/>
-      <c r="T37" s="5"/>
-    </row>
-    <row r="38" spans="1:20" s="18" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A38" s="5"/>
-      <c r="B38" s="5"/>
-      <c r="C38" s="5"/>
-      <c r="D38" s="5"/>
-      <c r="E38" s="5"/>
-      <c r="F38" s="1"/>
-      <c r="G38" s="5"/>
-      <c r="H38" s="5"/>
-      <c r="I38" s="5"/>
-      <c r="J38" s="5"/>
-      <c r="K38" s="5"/>
-      <c r="L38" s="5"/>
-      <c r="M38" s="5"/>
-      <c r="N38" s="5"/>
-      <c r="O38" s="5"/>
-      <c r="P38" s="5"/>
-      <c r="Q38" s="5"/>
-      <c r="R38" s="5"/>
-      <c r="S38" s="5"/>
-      <c r="T38" s="5"/>
+      <c r="B37" s="39" t="s">
+        <v>33</v>
+      </c>
+      <c r="C37" s="39"/>
+      <c r="D37" s="39"/>
+      <c r="E37" s="39"/>
+      <c r="F37" s="39"/>
+      <c r="G37" s="39"/>
+      <c r="H37" s="39"/>
+      <c r="I37" s="39"/>
+      <c r="J37" s="39"/>
+    </row>
+    <row r="38" spans="1:20" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A38" s="39"/>
+      <c r="B38" s="39" t="s">
+        <v>29</v>
+      </c>
+      <c r="C38" s="39"/>
+      <c r="D38" s="39"/>
+      <c r="E38" s="39"/>
+      <c r="F38" s="39"/>
+      <c r="G38" s="39"/>
+      <c r="H38" s="39"/>
+      <c r="I38" s="39"/>
+      <c r="J38" s="39"/>
     </row>
     <row r="39" spans="1:20" s="18" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A39" s="11" t="s">
-        <v>21</v>
-      </c>
+      <c r="A39" s="5"/>
       <c r="B39" s="5"/>
       <c r="C39" s="5"/>
       <c r="D39" s="5"/>
-      <c r="E39" s="7"/>
-      <c r="F39" s="7"/>
-      <c r="G39" s="7"/>
-      <c r="H39" s="7"/>
-      <c r="I39" s="7"/>
-      <c r="J39" s="7"/>
-      <c r="K39" s="7"/>
-      <c r="L39" s="7"/>
+      <c r="E39" s="5"/>
+      <c r="F39" s="1"/>
+      <c r="G39" s="5"/>
+      <c r="H39" s="5"/>
+      <c r="I39" s="5"/>
+      <c r="J39" s="5"/>
+      <c r="K39" s="5"/>
+      <c r="L39" s="5"/>
       <c r="M39" s="5"/>
       <c r="N39" s="5"/>
       <c r="O39" s="5"/>
@@ -2925,20 +2943,18 @@
       <c r="T39" s="5"/>
     </row>
     <row r="40" spans="1:20" s="18" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A40" s="5" t="s">
-        <v>22</v>
-      </c>
+      <c r="A40" s="5"/>
       <c r="B40" s="5"/>
       <c r="C40" s="5"/>
       <c r="D40" s="5"/>
-      <c r="E40" s="1"/>
+      <c r="E40" s="5"/>
       <c r="F40" s="1"/>
-      <c r="G40" s="1"/>
-      <c r="H40" s="1"/>
-      <c r="I40" s="1"/>
-      <c r="J40" s="1"/>
-      <c r="K40" s="1"/>
-      <c r="L40" s="1"/>
+      <c r="G40" s="5"/>
+      <c r="H40" s="5"/>
+      <c r="I40" s="5"/>
+      <c r="J40" s="5"/>
+      <c r="K40" s="5"/>
+      <c r="L40" s="5"/>
       <c r="M40" s="5"/>
       <c r="N40" s="5"/>
       <c r="O40" s="5"/>
@@ -2949,7 +2965,9 @@
       <c r="T40" s="5"/>
     </row>
     <row r="41" spans="1:20" s="18" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A41" s="5"/>
+      <c r="A41" s="11" t="s">
+        <v>21</v>
+      </c>
       <c r="B41" s="5"/>
       <c r="C41" s="5"/>
       <c r="D41" s="5"/>
@@ -2971,20 +2989,20 @@
       <c r="T41" s="5"/>
     </row>
     <row r="42" spans="1:20" s="18" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A42" s="43" t="s">
-        <v>32</v>
+      <c r="A42" s="5" t="s">
+        <v>22</v>
       </c>
       <c r="B42" s="5"/>
       <c r="C42" s="5"/>
       <c r="D42" s="5"/>
-      <c r="E42" s="7"/>
-      <c r="F42" s="7"/>
-      <c r="G42" s="7"/>
-      <c r="H42" s="7"/>
-      <c r="I42" s="7"/>
-      <c r="J42" s="7"/>
-      <c r="K42" s="7"/>
-      <c r="L42" s="7"/>
+      <c r="E42" s="1"/>
+      <c r="F42" s="1"/>
+      <c r="G42" s="1"/>
+      <c r="H42" s="1"/>
+      <c r="I42" s="1"/>
+      <c r="J42" s="1"/>
+      <c r="K42" s="1"/>
+      <c r="L42" s="1"/>
       <c r="M42" s="5"/>
       <c r="N42" s="5"/>
       <c r="O42" s="5"/>
@@ -2999,14 +3017,14 @@
       <c r="B43" s="5"/>
       <c r="C43" s="5"/>
       <c r="D43" s="5"/>
-      <c r="E43" s="5"/>
-      <c r="F43" s="5"/>
-      <c r="G43" s="5"/>
-      <c r="H43" s="5"/>
-      <c r="I43" s="5"/>
-      <c r="J43" s="5"/>
-      <c r="K43" s="5"/>
-      <c r="L43" s="5"/>
+      <c r="E43" s="7"/>
+      <c r="F43" s="7"/>
+      <c r="G43" s="7"/>
+      <c r="H43" s="7"/>
+      <c r="I43" s="7"/>
+      <c r="J43" s="7"/>
+      <c r="K43" s="7"/>
+      <c r="L43" s="7"/>
       <c r="M43" s="5"/>
       <c r="N43" s="5"/>
       <c r="O43" s="5"/>
@@ -3017,20 +3035,20 @@
       <c r="T43" s="5"/>
     </row>
     <row r="44" spans="1:20" s="18" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A44" s="69" t="s">
-        <v>31</v>
-      </c>
-      <c r="B44" s="69"/>
-      <c r="C44" s="69"/>
-      <c r="D44" s="69"/>
-      <c r="E44" s="69"/>
-      <c r="F44" s="69"/>
-      <c r="G44" s="5"/>
-      <c r="H44" s="5"/>
-      <c r="I44" s="5"/>
-      <c r="J44" s="11"/>
-      <c r="K44" s="11"/>
-      <c r="L44" s="11"/>
+      <c r="A44" s="38" t="s">
+        <v>28</v>
+      </c>
+      <c r="B44" s="5"/>
+      <c r="C44" s="5"/>
+      <c r="D44" s="5"/>
+      <c r="E44" s="7"/>
+      <c r="F44" s="7"/>
+      <c r="G44" s="7"/>
+      <c r="H44" s="7"/>
+      <c r="I44" s="7"/>
+      <c r="J44" s="7"/>
+      <c r="K44" s="7"/>
+      <c r="L44" s="7"/>
       <c r="M44" s="5"/>
       <c r="N44" s="5"/>
       <c r="O44" s="5"/>
@@ -3041,20 +3059,18 @@
       <c r="T44" s="5"/>
     </row>
     <row r="45" spans="1:20" s="18" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A45" s="33" t="s">
-        <v>25</v>
-      </c>
-      <c r="B45" s="33"/>
-      <c r="C45" s="33"/>
-      <c r="D45" s="33"/>
+      <c r="A45" s="5"/>
+      <c r="B45" s="5"/>
+      <c r="C45" s="5"/>
+      <c r="D45" s="5"/>
       <c r="E45" s="5"/>
       <c r="F45" s="5"/>
       <c r="G45" s="5"/>
       <c r="H45" s="5"/>
       <c r="I45" s="5"/>
-      <c r="J45" s="11"/>
-      <c r="K45" s="11"/>
-      <c r="L45" s="11"/>
+      <c r="J45" s="5"/>
+      <c r="K45" s="5"/>
+      <c r="L45" s="5"/>
       <c r="M45" s="5"/>
       <c r="N45" s="5"/>
       <c r="O45" s="5"/>
@@ -3065,18 +3081,20 @@
       <c r="T45" s="5"/>
     </row>
     <row r="46" spans="1:20" s="18" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A46" s="5"/>
-      <c r="B46" s="5"/>
-      <c r="C46" s="5"/>
-      <c r="D46" s="5"/>
-      <c r="E46" s="5"/>
-      <c r="F46" s="5"/>
+      <c r="A46" s="53" t="s">
+        <v>27</v>
+      </c>
+      <c r="B46" s="53"/>
+      <c r="C46" s="53"/>
+      <c r="D46" s="53"/>
+      <c r="E46" s="53"/>
+      <c r="F46" s="53"/>
       <c r="G46" s="5"/>
       <c r="H46" s="5"/>
       <c r="I46" s="5"/>
-      <c r="J46" s="5"/>
-      <c r="K46" s="5"/>
-      <c r="L46" s="5"/>
+      <c r="J46" s="11"/>
+      <c r="K46" s="11"/>
+      <c r="L46" s="11"/>
       <c r="M46" s="5"/>
       <c r="N46" s="5"/>
       <c r="O46" s="5"/>
@@ -3087,18 +3105,20 @@
       <c r="T46" s="5"/>
     </row>
     <row r="47" spans="1:20" s="18" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A47" s="5"/>
-      <c r="B47" s="5"/>
-      <c r="C47" s="5"/>
-      <c r="D47" s="5"/>
+      <c r="A47" s="31" t="s">
+        <v>24</v>
+      </c>
+      <c r="B47" s="31"/>
+      <c r="C47" s="31"/>
+      <c r="D47" s="31"/>
       <c r="E47" s="5"/>
       <c r="F47" s="5"/>
       <c r="G47" s="5"/>
       <c r="H47" s="5"/>
       <c r="I47" s="5"/>
-      <c r="J47" s="5"/>
-      <c r="K47" s="5"/>
-      <c r="L47" s="5"/>
+      <c r="J47" s="11"/>
+      <c r="K47" s="11"/>
+      <c r="L47" s="11"/>
       <c r="M47" s="5"/>
       <c r="N47" s="5"/>
       <c r="O47" s="5"/>
@@ -3157,8 +3177,8 @@
       <c r="B50" s="5"/>
       <c r="C50" s="5"/>
       <c r="D50" s="5"/>
-      <c r="E50" s="36"/>
-      <c r="F50" s="36"/>
+      <c r="E50" s="5"/>
+      <c r="F50" s="5"/>
       <c r="G50" s="5"/>
       <c r="H50" s="5"/>
       <c r="I50" s="5"/>
@@ -3179,8 +3199,8 @@
       <c r="B51" s="5"/>
       <c r="C51" s="5"/>
       <c r="D51" s="5"/>
-      <c r="E51" s="7"/>
-      <c r="F51" s="7"/>
+      <c r="E51" s="5"/>
+      <c r="F51" s="5"/>
       <c r="G51" s="5"/>
       <c r="H51" s="5"/>
       <c r="I51" s="5"/>
@@ -3201,8 +3221,8 @@
       <c r="B52" s="5"/>
       <c r="C52" s="5"/>
       <c r="D52" s="5"/>
-      <c r="E52" s="33"/>
-      <c r="F52" s="33"/>
+      <c r="E52" s="34"/>
+      <c r="F52" s="34"/>
       <c r="G52" s="5"/>
       <c r="H52" s="5"/>
       <c r="I52" s="5"/>
@@ -3223,8 +3243,8 @@
       <c r="B53" s="5"/>
       <c r="C53" s="5"/>
       <c r="D53" s="5"/>
-      <c r="E53" s="5"/>
-      <c r="F53" s="5"/>
+      <c r="E53" s="7"/>
+      <c r="F53" s="7"/>
       <c r="G53" s="5"/>
       <c r="H53" s="5"/>
       <c r="I53" s="5"/>
@@ -3245,8 +3265,8 @@
       <c r="B54" s="5"/>
       <c r="C54" s="5"/>
       <c r="D54" s="5"/>
-      <c r="E54" s="5"/>
-      <c r="F54" s="5"/>
+      <c r="E54" s="31"/>
+      <c r="F54" s="31"/>
       <c r="G54" s="5"/>
       <c r="H54" s="5"/>
       <c r="I54" s="5"/>
@@ -3328,7 +3348,29 @@
       <c r="S57" s="5"/>
       <c r="T57" s="5"/>
     </row>
-    <row r="59" spans="1:20" s="28" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:20" s="18" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A58" s="5"/>
+      <c r="B58" s="5"/>
+      <c r="C58" s="5"/>
+      <c r="D58" s="5"/>
+      <c r="E58" s="5"/>
+      <c r="F58" s="5"/>
+      <c r="G58" s="5"/>
+      <c r="H58" s="5"/>
+      <c r="I58" s="5"/>
+      <c r="J58" s="5"/>
+      <c r="K58" s="5"/>
+      <c r="L58" s="5"/>
+      <c r="M58" s="5"/>
+      <c r="N58" s="5"/>
+      <c r="O58" s="5"/>
+      <c r="P58" s="5"/>
+      <c r="Q58" s="5"/>
+      <c r="R58" s="5"/>
+      <c r="S58" s="5"/>
+      <c r="T58" s="5"/>
+    </row>
+    <row r="59" spans="1:20" s="18" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A59" s="5"/>
       <c r="B59" s="5"/>
       <c r="C59" s="5"/>
@@ -3350,29 +3392,7 @@
       <c r="S59" s="5"/>
       <c r="T59" s="5"/>
     </row>
-    <row r="60" spans="1:20" s="28" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A60" s="5"/>
-      <c r="B60" s="5"/>
-      <c r="C60" s="5"/>
-      <c r="D60" s="5"/>
-      <c r="E60" s="5"/>
-      <c r="F60" s="5"/>
-      <c r="G60" s="5"/>
-      <c r="H60" s="5"/>
-      <c r="I60" s="5"/>
-      <c r="J60" s="5"/>
-      <c r="K60" s="5"/>
-      <c r="L60" s="5"/>
-      <c r="M60" s="5"/>
-      <c r="N60" s="5"/>
-      <c r="O60" s="5"/>
-      <c r="P60" s="5"/>
-      <c r="Q60" s="5"/>
-      <c r="R60" s="5"/>
-      <c r="S60" s="5"/>
-      <c r="T60" s="5"/>
-    </row>
-    <row r="61" spans="1:20" s="28" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:20" s="26" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A61" s="5"/>
       <c r="B61" s="5"/>
       <c r="C61" s="5"/>
@@ -3394,7 +3414,7 @@
       <c r="S61" s="5"/>
       <c r="T61" s="5"/>
     </row>
-    <row r="62" spans="1:20" s="28" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:20" s="26" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A62" s="5"/>
       <c r="B62" s="5"/>
       <c r="C62" s="5"/>
@@ -3416,7 +3436,7 @@
       <c r="S62" s="5"/>
       <c r="T62" s="5"/>
     </row>
-    <row r="63" spans="1:20" s="28" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:20" s="26" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A63" s="5"/>
       <c r="B63" s="5"/>
       <c r="C63" s="5"/>
@@ -3438,7 +3458,7 @@
       <c r="S63" s="5"/>
       <c r="T63" s="5"/>
     </row>
-    <row r="64" spans="1:20" s="28" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:20" s="26" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A64" s="5"/>
       <c r="B64" s="5"/>
       <c r="C64" s="5"/>
@@ -3460,7 +3480,7 @@
       <c r="S64" s="5"/>
       <c r="T64" s="5"/>
     </row>
-    <row r="65" spans="1:23" s="28" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:23" s="26" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A65" s="5"/>
       <c r="B65" s="5"/>
       <c r="C65" s="5"/>
@@ -3482,7 +3502,7 @@
       <c r="S65" s="5"/>
       <c r="T65" s="5"/>
     </row>
-    <row r="66" spans="1:23" s="28" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:23" s="26" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A66" s="5"/>
       <c r="B66" s="5"/>
       <c r="C66" s="5"/>
@@ -3504,7 +3524,7 @@
       <c r="S66" s="5"/>
       <c r="T66" s="5"/>
     </row>
-    <row r="67" spans="1:23" s="28" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:23" s="26" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A67" s="5"/>
       <c r="B67" s="5"/>
       <c r="C67" s="5"/>
@@ -3526,51 +3546,51 @@
       <c r="S67" s="5"/>
       <c r="T67" s="5"/>
     </row>
-    <row r="70" spans="1:23" s="28" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A70" s="5"/>
-      <c r="B70" s="5"/>
-      <c r="C70" s="5"/>
-      <c r="D70" s="5"/>
-      <c r="E70" s="5"/>
-      <c r="F70" s="5"/>
-      <c r="G70" s="5"/>
-      <c r="H70" s="5"/>
-      <c r="I70" s="5"/>
-      <c r="J70" s="5"/>
-      <c r="K70" s="5"/>
-      <c r="L70" s="5"/>
-      <c r="M70" s="5"/>
-      <c r="N70" s="5"/>
-      <c r="O70" s="5"/>
-      <c r="P70" s="5"/>
-      <c r="Q70" s="5"/>
-      <c r="R70" s="5"/>
-      <c r="S70" s="5"/>
-      <c r="T70" s="5"/>
-    </row>
-    <row r="71" spans="1:23" s="28" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A71" s="5"/>
-      <c r="B71" s="5"/>
-      <c r="C71" s="5"/>
-      <c r="D71" s="5"/>
-      <c r="E71" s="5"/>
-      <c r="F71" s="5"/>
-      <c r="G71" s="5"/>
-      <c r="H71" s="5"/>
-      <c r="I71" s="5"/>
-      <c r="J71" s="5"/>
-      <c r="K71" s="5"/>
-      <c r="L71" s="5"/>
-      <c r="M71" s="5"/>
-      <c r="N71" s="5"/>
-      <c r="O71" s="5"/>
-      <c r="P71" s="5"/>
-      <c r="Q71" s="5"/>
-      <c r="R71" s="5"/>
-      <c r="S71" s="5"/>
-      <c r="T71" s="5"/>
-    </row>
-    <row r="72" spans="1:23" s="28" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:23" s="26" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A68" s="5"/>
+      <c r="B68" s="5"/>
+      <c r="C68" s="5"/>
+      <c r="D68" s="5"/>
+      <c r="E68" s="5"/>
+      <c r="F68" s="5"/>
+      <c r="G68" s="5"/>
+      <c r="H68" s="5"/>
+      <c r="I68" s="5"/>
+      <c r="J68" s="5"/>
+      <c r="K68" s="5"/>
+      <c r="L68" s="5"/>
+      <c r="M68" s="5"/>
+      <c r="N68" s="5"/>
+      <c r="O68" s="5"/>
+      <c r="P68" s="5"/>
+      <c r="Q68" s="5"/>
+      <c r="R68" s="5"/>
+      <c r="S68" s="5"/>
+      <c r="T68" s="5"/>
+    </row>
+    <row r="69" spans="1:23" s="26" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A69" s="5"/>
+      <c r="B69" s="5"/>
+      <c r="C69" s="5"/>
+      <c r="D69" s="5"/>
+      <c r="E69" s="5"/>
+      <c r="F69" s="5"/>
+      <c r="G69" s="5"/>
+      <c r="H69" s="5"/>
+      <c r="I69" s="5"/>
+      <c r="J69" s="5"/>
+      <c r="K69" s="5"/>
+      <c r="L69" s="5"/>
+      <c r="M69" s="5"/>
+      <c r="N69" s="5"/>
+      <c r="O69" s="5"/>
+      <c r="P69" s="5"/>
+      <c r="Q69" s="5"/>
+      <c r="R69" s="5"/>
+      <c r="S69" s="5"/>
+      <c r="T69" s="5"/>
+    </row>
+    <row r="72" spans="1:23" s="26" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A72" s="5"/>
       <c r="B72" s="5"/>
       <c r="C72" s="5"/>
@@ -3592,46 +3612,118 @@
       <c r="S72" s="5"/>
       <c r="T72" s="5"/>
     </row>
-    <row r="75" spans="1:23" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A75" s="5"/>
-      <c r="B75" s="5"/>
-      <c r="C75" s="5"/>
-      <c r="D75" s="5"/>
-      <c r="E75" s="5"/>
-      <c r="F75" s="5"/>
-      <c r="G75" s="5"/>
-      <c r="H75" s="5"/>
-      <c r="I75" s="5"/>
-      <c r="J75" s="5"/>
-      <c r="K75" s="5"/>
-      <c r="L75" s="5"/>
-      <c r="M75" s="5"/>
-      <c r="N75" s="5"/>
-      <c r="O75" s="5"/>
-      <c r="P75" s="5"/>
-      <c r="Q75" s="5"/>
-      <c r="R75" s="5"/>
-      <c r="S75" s="5"/>
-      <c r="T75" s="5"/>
-      <c r="U75" s="34"/>
-      <c r="V75" s="34"/>
-      <c r="W75" s="34"/>
-    </row>
-    <row r="76" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="U76" s="35"/>
-      <c r="V76" s="35"/>
-      <c r="W76" s="35"/>
+    <row r="73" spans="1:23" s="26" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A73" s="5"/>
+      <c r="B73" s="5"/>
+      <c r="C73" s="5"/>
+      <c r="D73" s="5"/>
+      <c r="E73" s="5"/>
+      <c r="F73" s="5"/>
+      <c r="G73" s="5"/>
+      <c r="H73" s="5"/>
+      <c r="I73" s="5"/>
+      <c r="J73" s="5"/>
+      <c r="K73" s="5"/>
+      <c r="L73" s="5"/>
+      <c r="M73" s="5"/>
+      <c r="N73" s="5"/>
+      <c r="O73" s="5"/>
+      <c r="P73" s="5"/>
+      <c r="Q73" s="5"/>
+      <c r="R73" s="5"/>
+      <c r="S73" s="5"/>
+      <c r="T73" s="5"/>
+    </row>
+    <row r="74" spans="1:23" s="26" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A74" s="5"/>
+      <c r="B74" s="5"/>
+      <c r="C74" s="5"/>
+      <c r="D74" s="5"/>
+      <c r="E74" s="5"/>
+      <c r="F74" s="5"/>
+      <c r="G74" s="5"/>
+      <c r="H74" s="5"/>
+      <c r="I74" s="5"/>
+      <c r="J74" s="5"/>
+      <c r="K74" s="5"/>
+      <c r="L74" s="5"/>
+      <c r="M74" s="5"/>
+      <c r="N74" s="5"/>
+      <c r="O74" s="5"/>
+      <c r="P74" s="5"/>
+      <c r="Q74" s="5"/>
+      <c r="R74" s="5"/>
+      <c r="S74" s="5"/>
+      <c r="T74" s="5"/>
+    </row>
+    <row r="77" spans="1:23" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A77" s="5"/>
+      <c r="B77" s="5"/>
+      <c r="C77" s="5"/>
+      <c r="D77" s="5"/>
+      <c r="E77" s="5"/>
+      <c r="F77" s="5"/>
+      <c r="G77" s="5"/>
+      <c r="H77" s="5"/>
+      <c r="I77" s="5"/>
+      <c r="J77" s="5"/>
+      <c r="K77" s="5"/>
+      <c r="L77" s="5"/>
+      <c r="M77" s="5"/>
+      <c r="N77" s="5"/>
+      <c r="O77" s="5"/>
+      <c r="P77" s="5"/>
+      <c r="Q77" s="5"/>
+      <c r="R77" s="5"/>
+      <c r="S77" s="5"/>
+      <c r="T77" s="5"/>
+      <c r="U77" s="32"/>
+      <c r="V77" s="32"/>
+      <c r="W77" s="32"/>
+    </row>
+    <row r="78" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="U78" s="33"/>
+      <c r="V78" s="33"/>
+      <c r="W78" s="33"/>
     </row>
   </sheetData>
-  <mergeCells count="32">
+  <mergeCells count="47">
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="H22:L22"/>
+    <mergeCell ref="H23:L23"/>
+    <mergeCell ref="Q19:T19"/>
+    <mergeCell ref="M19:P19"/>
+    <mergeCell ref="H19:L19"/>
+    <mergeCell ref="H20:L20"/>
+    <mergeCell ref="M20:P20"/>
+    <mergeCell ref="Q20:T20"/>
+    <mergeCell ref="H21:L21"/>
     <mergeCell ref="M22:P22"/>
     <mergeCell ref="M23:P23"/>
     <mergeCell ref="Q21:T21"/>
     <mergeCell ref="Q22:T22"/>
     <mergeCell ref="Q23:T23"/>
+    <mergeCell ref="E23:G23"/>
+    <mergeCell ref="M21:P21"/>
+    <mergeCell ref="A3:T3"/>
+    <mergeCell ref="A4:T4"/>
+    <mergeCell ref="A5:T5"/>
+    <mergeCell ref="A6:T6"/>
+    <mergeCell ref="N12:S12"/>
+    <mergeCell ref="E19:G19"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="A23:B23"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="Q24:T24"/>
+    <mergeCell ref="Q25:T25"/>
     <mergeCell ref="K14:N14"/>
-    <mergeCell ref="A44:F44"/>
-    <mergeCell ref="Q24:T24"/>
+    <mergeCell ref="A46:F46"/>
+    <mergeCell ref="Q26:T26"/>
     <mergeCell ref="C17:D18"/>
     <mergeCell ref="E17:G18"/>
     <mergeCell ref="M17:P18"/>
@@ -3643,19 +3735,6 @@
     <mergeCell ref="E20:G20"/>
     <mergeCell ref="E21:G21"/>
     <mergeCell ref="E22:G22"/>
-    <mergeCell ref="E23:G23"/>
-    <mergeCell ref="M21:P21"/>
-    <mergeCell ref="A3:T3"/>
-    <mergeCell ref="A4:T4"/>
-    <mergeCell ref="A5:T5"/>
-    <mergeCell ref="A6:T6"/>
-    <mergeCell ref="N12:S12"/>
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="H20:L20"/>
-    <mergeCell ref="M20:P20"/>
-    <mergeCell ref="Q20:T20"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="H21:L21"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <printOptions horizontalCentered="1"/>

--- a/RFQ Generator Beta Version/Templates/DE TEMPLATE.xlsx
+++ b/RFQ Generator Beta Version/Templates/DE TEMPLATE.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\source\repos\RFQ Generator Beta Version\RFQ Generator Beta Version\bin\Debug\Templates\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\source\repos\RFQ Generator Beta Version\RFQ Generator Beta Version\Templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1530A2F-8E46-4C75-BE15-81A29237B701}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0EF364E6-594C-43C3-812F-068C5F37803E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{02CCD737-9343-44DD-A110-541534088332}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="51">
   <si>
     <t>ITEM</t>
   </si>
@@ -94,9 +94,6 @@
   </si>
   <si>
     <t xml:space="preserve">QTY </t>
-  </si>
-  <si>
-    <t>TOTAL RFQ VALUE</t>
   </si>
   <si>
     <t>DELIVERY</t>
@@ -303,7 +300,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="15">
+  <borders count="16">
     <border>
       <left/>
       <right/>
@@ -453,13 +450,24 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thick">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="165" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="100">
+  <cellXfs count="102">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -528,181 +536,197 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="39" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="5" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="5" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="4" fontId="5" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="5" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="39" fontId="5" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="4" fontId="5" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="5" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="5" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="5" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -2127,92 +2151,92 @@
       <c r="T2" s="6"/>
     </row>
     <row r="3" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="51"/>
-      <c r="B3" s="51"/>
-      <c r="C3" s="51"/>
-      <c r="D3" s="51"/>
-      <c r="E3" s="51"/>
-      <c r="F3" s="51"/>
-      <c r="G3" s="51"/>
-      <c r="H3" s="51"/>
-      <c r="I3" s="51"/>
-      <c r="J3" s="51"/>
-      <c r="K3" s="51"/>
-      <c r="L3" s="51"/>
-      <c r="M3" s="51"/>
-      <c r="N3" s="51"/>
-      <c r="O3" s="51"/>
-      <c r="P3" s="51"/>
-      <c r="Q3" s="51"/>
-      <c r="R3" s="51"/>
-      <c r="S3" s="51"/>
-      <c r="T3" s="51"/>
+      <c r="A3" s="55"/>
+      <c r="B3" s="55"/>
+      <c r="C3" s="55"/>
+      <c r="D3" s="55"/>
+      <c r="E3" s="55"/>
+      <c r="F3" s="55"/>
+      <c r="G3" s="55"/>
+      <c r="H3" s="55"/>
+      <c r="I3" s="55"/>
+      <c r="J3" s="55"/>
+      <c r="K3" s="55"/>
+      <c r="L3" s="55"/>
+      <c r="M3" s="55"/>
+      <c r="N3" s="55"/>
+      <c r="O3" s="55"/>
+      <c r="P3" s="55"/>
+      <c r="Q3" s="55"/>
+      <c r="R3" s="55"/>
+      <c r="S3" s="55"/>
+      <c r="T3" s="55"/>
     </row>
     <row r="4" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="83"/>
-      <c r="B4" s="83"/>
-      <c r="C4" s="83"/>
-      <c r="D4" s="83"/>
-      <c r="E4" s="83"/>
-      <c r="F4" s="83"/>
-      <c r="G4" s="83"/>
-      <c r="H4" s="83"/>
-      <c r="I4" s="83"/>
-      <c r="J4" s="83"/>
-      <c r="K4" s="83"/>
-      <c r="L4" s="83"/>
-      <c r="M4" s="83"/>
-      <c r="N4" s="83"/>
-      <c r="O4" s="83"/>
-      <c r="P4" s="83"/>
-      <c r="Q4" s="83"/>
-      <c r="R4" s="83"/>
-      <c r="S4" s="83"/>
-      <c r="T4" s="83"/>
+      <c r="A4" s="56"/>
+      <c r="B4" s="56"/>
+      <c r="C4" s="56"/>
+      <c r="D4" s="56"/>
+      <c r="E4" s="56"/>
+      <c r="F4" s="56"/>
+      <c r="G4" s="56"/>
+      <c r="H4" s="56"/>
+      <c r="I4" s="56"/>
+      <c r="J4" s="56"/>
+      <c r="K4" s="56"/>
+      <c r="L4" s="56"/>
+      <c r="M4" s="56"/>
+      <c r="N4" s="56"/>
+      <c r="O4" s="56"/>
+      <c r="P4" s="56"/>
+      <c r="Q4" s="56"/>
+      <c r="R4" s="56"/>
+      <c r="S4" s="56"/>
+      <c r="T4" s="56"/>
     </row>
     <row r="5" spans="1:20" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="84"/>
-      <c r="B5" s="84"/>
-      <c r="C5" s="84"/>
-      <c r="D5" s="84"/>
-      <c r="E5" s="84"/>
-      <c r="F5" s="84"/>
-      <c r="G5" s="84"/>
-      <c r="H5" s="84"/>
-      <c r="I5" s="84"/>
-      <c r="J5" s="84"/>
-      <c r="K5" s="84"/>
-      <c r="L5" s="84"/>
-      <c r="M5" s="84"/>
-      <c r="N5" s="84"/>
-      <c r="O5" s="84"/>
-      <c r="P5" s="84"/>
-      <c r="Q5" s="84"/>
-      <c r="R5" s="84"/>
-      <c r="S5" s="84"/>
-      <c r="T5" s="84"/>
+      <c r="A5" s="57"/>
+      <c r="B5" s="57"/>
+      <c r="C5" s="57"/>
+      <c r="D5" s="57"/>
+      <c r="E5" s="57"/>
+      <c r="F5" s="57"/>
+      <c r="G5" s="57"/>
+      <c r="H5" s="57"/>
+      <c r="I5" s="57"/>
+      <c r="J5" s="57"/>
+      <c r="K5" s="57"/>
+      <c r="L5" s="57"/>
+      <c r="M5" s="57"/>
+      <c r="N5" s="57"/>
+      <c r="O5" s="57"/>
+      <c r="P5" s="57"/>
+      <c r="Q5" s="57"/>
+      <c r="R5" s="57"/>
+      <c r="S5" s="57"/>
+      <c r="T5" s="57"/>
     </row>
     <row r="6" spans="1:20" ht="30.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="51"/>
-      <c r="B6" s="51"/>
-      <c r="C6" s="51"/>
-      <c r="D6" s="51"/>
-      <c r="E6" s="51"/>
-      <c r="F6" s="51"/>
-      <c r="G6" s="51"/>
-      <c r="H6" s="51"/>
-      <c r="I6" s="51"/>
-      <c r="J6" s="51"/>
-      <c r="K6" s="51"/>
-      <c r="L6" s="51"/>
-      <c r="M6" s="51"/>
-      <c r="N6" s="51"/>
-      <c r="O6" s="51"/>
-      <c r="P6" s="51"/>
-      <c r="Q6" s="51"/>
-      <c r="R6" s="51"/>
-      <c r="S6" s="51"/>
-      <c r="T6" s="51"/>
+      <c r="A6" s="55"/>
+      <c r="B6" s="55"/>
+      <c r="C6" s="55"/>
+      <c r="D6" s="55"/>
+      <c r="E6" s="55"/>
+      <c r="F6" s="55"/>
+      <c r="G6" s="55"/>
+      <c r="H6" s="55"/>
+      <c r="I6" s="55"/>
+      <c r="J6" s="55"/>
+      <c r="K6" s="55"/>
+      <c r="L6" s="55"/>
+      <c r="M6" s="55"/>
+      <c r="N6" s="55"/>
+      <c r="O6" s="55"/>
+      <c r="P6" s="55"/>
+      <c r="Q6" s="55"/>
+      <c r="R6" s="55"/>
+      <c r="S6" s="55"/>
+      <c r="T6" s="55"/>
     </row>
     <row r="7" spans="1:20" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="7"/>
@@ -2311,7 +2335,7 @@
         <v>8</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="H11" s="11" t="s">
         <v>9</v>
@@ -2325,7 +2349,7 @@
         <v>8</v>
       </c>
       <c r="N11" s="14" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="S11" s="10"/>
       <c r="T11" s="15"/>
@@ -2350,14 +2374,14 @@
       <c r="M12" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="N12" s="85" t="s">
-        <v>41</v>
-      </c>
-      <c r="O12" s="85"/>
-      <c r="P12" s="85"/>
-      <c r="Q12" s="85"/>
-      <c r="R12" s="85"/>
-      <c r="S12" s="85"/>
+      <c r="N12" s="58" t="s">
+        <v>40</v>
+      </c>
+      <c r="O12" s="58"/>
+      <c r="P12" s="58"/>
+      <c r="Q12" s="58"/>
+      <c r="R12" s="58"/>
+      <c r="S12" s="58"/>
       <c r="T12" s="17"/>
     </row>
     <row r="13" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -2379,7 +2403,7 @@
         <v>8</v>
       </c>
       <c r="N13" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="T13" s="17"/>
     </row>
@@ -2391,10 +2415,10 @@
         <v>8</v>
       </c>
       <c r="E14" s="1"/>
-      <c r="K14" s="53"/>
-      <c r="L14" s="54"/>
-      <c r="M14" s="54"/>
-      <c r="N14" s="54"/>
+      <c r="K14" s="66"/>
+      <c r="L14" s="67"/>
+      <c r="M14" s="67"/>
+      <c r="N14" s="67"/>
       <c r="O14" s="1"/>
       <c r="P14" s="19"/>
       <c r="Q14" s="1"/>
@@ -2421,18 +2445,18 @@
       <c r="K15" s="8"/>
       <c r="L15" s="23"/>
       <c r="M15" s="8"/>
-      <c r="N15" s="69" t="s">
-        <v>25</v>
-      </c>
-      <c r="O15" s="69"/>
-      <c r="P15" s="69"/>
-      <c r="Q15" s="69"/>
-      <c r="R15" s="69"/>
-      <c r="S15" s="69"/>
-      <c r="T15" s="70"/>
+      <c r="N15" s="82" t="s">
+        <v>24</v>
+      </c>
+      <c r="O15" s="82"/>
+      <c r="P15" s="82"/>
+      <c r="Q15" s="82"/>
+      <c r="R15" s="82"/>
+      <c r="S15" s="82"/>
+      <c r="T15" s="83"/>
     </row>
     <row r="16" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="41"/>
+      <c r="A16" s="39"/>
       <c r="C16" s="1"/>
       <c r="E16" s="24"/>
       <c r="F16" s="24"/>
@@ -2447,238 +2471,238 @@
       <c r="T16" s="7"/>
     </row>
     <row r="17" spans="1:20" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="65" t="s">
+      <c r="A17" s="78" t="s">
         <v>0</v>
       </c>
-      <c r="B17" s="58"/>
-      <c r="C17" s="58" t="s">
+      <c r="B17" s="71"/>
+      <c r="C17" s="71" t="s">
         <v>18</v>
       </c>
-      <c r="D17" s="58"/>
-      <c r="E17" s="60" t="s">
+      <c r="D17" s="71"/>
+      <c r="E17" s="73" t="s">
         <v>1</v>
       </c>
-      <c r="F17" s="61"/>
-      <c r="G17" s="62"/>
-      <c r="H17" s="65" t="s">
-        <v>20</v>
-      </c>
-      <c r="I17" s="71"/>
-      <c r="J17" s="71"/>
-      <c r="K17" s="71"/>
-      <c r="L17" s="72"/>
-      <c r="M17" s="65" t="s">
+      <c r="F17" s="74"/>
+      <c r="G17" s="75"/>
+      <c r="H17" s="78" t="s">
+        <v>19</v>
+      </c>
+      <c r="I17" s="84"/>
+      <c r="J17" s="84"/>
+      <c r="K17" s="84"/>
+      <c r="L17" s="85"/>
+      <c r="M17" s="78" t="s">
         <v>2</v>
       </c>
-      <c r="N17" s="58"/>
-      <c r="O17" s="58"/>
-      <c r="P17" s="66"/>
-      <c r="Q17" s="65" t="s">
+      <c r="N17" s="71"/>
+      <c r="O17" s="71"/>
+      <c r="P17" s="79"/>
+      <c r="Q17" s="78" t="s">
         <v>11</v>
       </c>
-      <c r="R17" s="58"/>
-      <c r="S17" s="58"/>
-      <c r="T17" s="66"/>
+      <c r="R17" s="71"/>
+      <c r="S17" s="71"/>
+      <c r="T17" s="79"/>
     </row>
     <row r="18" spans="1:20" s="25" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="67"/>
-      <c r="B18" s="59"/>
-      <c r="C18" s="59"/>
-      <c r="D18" s="59"/>
-      <c r="E18" s="63"/>
-      <c r="F18" s="63"/>
-      <c r="G18" s="64"/>
-      <c r="H18" s="73"/>
-      <c r="I18" s="74"/>
-      <c r="J18" s="74"/>
-      <c r="K18" s="74"/>
-      <c r="L18" s="75"/>
-      <c r="M18" s="67"/>
-      <c r="N18" s="59"/>
-      <c r="O18" s="59"/>
-      <c r="P18" s="68"/>
-      <c r="Q18" s="67"/>
-      <c r="R18" s="59"/>
-      <c r="S18" s="59"/>
-      <c r="T18" s="68"/>
+      <c r="A18" s="80"/>
+      <c r="B18" s="72"/>
+      <c r="C18" s="72"/>
+      <c r="D18" s="72"/>
+      <c r="E18" s="76"/>
+      <c r="F18" s="76"/>
+      <c r="G18" s="77"/>
+      <c r="H18" s="86"/>
+      <c r="I18" s="87"/>
+      <c r="J18" s="87"/>
+      <c r="K18" s="87"/>
+      <c r="L18" s="88"/>
+      <c r="M18" s="80"/>
+      <c r="N18" s="72"/>
+      <c r="O18" s="72"/>
+      <c r="P18" s="81"/>
+      <c r="Q18" s="80"/>
+      <c r="R18" s="72"/>
+      <c r="S18" s="72"/>
+      <c r="T18" s="81"/>
     </row>
     <row r="19" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="81"/>
-      <c r="B19" s="82"/>
-      <c r="C19" s="81"/>
-      <c r="D19" s="82"/>
-      <c r="E19" s="86"/>
-      <c r="F19" s="87"/>
-      <c r="G19" s="88"/>
-      <c r="H19" s="81"/>
-      <c r="I19" s="93"/>
-      <c r="J19" s="93"/>
-      <c r="K19" s="93"/>
-      <c r="L19" s="82"/>
-      <c r="M19" s="81"/>
-      <c r="N19" s="93"/>
-      <c r="O19" s="93"/>
-      <c r="P19" s="82"/>
-      <c r="Q19" s="81"/>
-      <c r="R19" s="93"/>
-      <c r="S19" s="93"/>
-      <c r="T19" s="82"/>
+      <c r="A19" s="46"/>
+      <c r="B19" s="48"/>
+      <c r="C19" s="46"/>
+      <c r="D19" s="48"/>
+      <c r="E19" s="59"/>
+      <c r="F19" s="60"/>
+      <c r="G19" s="61"/>
+      <c r="H19" s="46"/>
+      <c r="I19" s="47"/>
+      <c r="J19" s="47"/>
+      <c r="K19" s="47"/>
+      <c r="L19" s="48"/>
+      <c r="M19" s="46"/>
+      <c r="N19" s="47"/>
+      <c r="O19" s="47"/>
+      <c r="P19" s="48"/>
+      <c r="Q19" s="46"/>
+      <c r="R19" s="47"/>
+      <c r="S19" s="47"/>
+      <c r="T19" s="48"/>
     </row>
     <row r="20" spans="1:20" s="18" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="76" t="s">
+      <c r="A20" s="62" t="s">
+        <v>42</v>
+      </c>
+      <c r="B20" s="63"/>
+      <c r="C20" s="62" t="s">
         <v>43</v>
       </c>
-      <c r="B20" s="52"/>
-      <c r="C20" s="76" t="s">
+      <c r="D20" s="63"/>
+      <c r="E20" s="89" t="s">
         <v>44</v>
       </c>
-      <c r="D20" s="52"/>
-      <c r="E20" s="77" t="s">
+      <c r="F20" s="68"/>
+      <c r="G20" s="90"/>
+      <c r="H20" s="49" t="s">
         <v>45</v>
       </c>
-      <c r="F20" s="55"/>
-      <c r="G20" s="78"/>
-      <c r="H20" s="89" t="s">
+      <c r="I20" s="50"/>
+      <c r="J20" s="50"/>
+      <c r="K20" s="50"/>
+      <c r="L20" s="51"/>
+      <c r="M20" s="52" t="s">
         <v>46</v>
       </c>
-      <c r="I20" s="90"/>
-      <c r="J20" s="90"/>
-      <c r="K20" s="90"/>
-      <c r="L20" s="91"/>
-      <c r="M20" s="94" t="s">
+      <c r="N20" s="53"/>
+      <c r="O20" s="53"/>
+      <c r="P20" s="54"/>
+      <c r="Q20" s="52" t="s">
+        <v>33</v>
+      </c>
+      <c r="R20" s="53"/>
+      <c r="S20" s="53"/>
+      <c r="T20" s="54"/>
+    </row>
+    <row r="21" spans="1:20" s="18" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="43"/>
+      <c r="B21" s="45"/>
+      <c r="C21" s="43"/>
+      <c r="D21" s="45"/>
+      <c r="E21" s="40"/>
+      <c r="F21" s="41"/>
+      <c r="G21" s="42"/>
+      <c r="H21" s="43"/>
+      <c r="I21" s="44"/>
+      <c r="J21" s="44"/>
+      <c r="K21" s="44"/>
+      <c r="L21" s="45"/>
+      <c r="M21" s="43"/>
+      <c r="N21" s="44"/>
+      <c r="O21" s="44"/>
+      <c r="P21" s="45"/>
+      <c r="Q21" s="43"/>
+      <c r="R21" s="44"/>
+      <c r="S21" s="44"/>
+      <c r="T21" s="45"/>
+    </row>
+    <row r="22" spans="1:20" s="18" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="93"/>
+      <c r="B22" s="64"/>
+      <c r="C22" s="64"/>
+      <c r="D22" s="64"/>
+      <c r="E22" s="92"/>
+      <c r="F22" s="92"/>
+      <c r="G22" s="92"/>
+      <c r="H22" s="64" t="s">
+        <v>34</v>
+      </c>
+      <c r="I22" s="64"/>
+      <c r="J22" s="64"/>
+      <c r="K22" s="64"/>
+      <c r="L22" s="64"/>
+      <c r="M22" s="64"/>
+      <c r="N22" s="64"/>
+      <c r="O22" s="64"/>
+      <c r="P22" s="64"/>
+      <c r="Q22" s="64" t="s">
+        <v>36</v>
+      </c>
+      <c r="R22" s="64"/>
+      <c r="S22" s="64"/>
+      <c r="T22" s="65"/>
+    </row>
+    <row r="23" spans="1:20" s="18" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A23" s="97"/>
+      <c r="B23" s="98"/>
+      <c r="C23" s="55"/>
+      <c r="D23" s="55"/>
+      <c r="E23" s="91"/>
+      <c r="F23" s="91"/>
+      <c r="G23" s="91"/>
+      <c r="H23" s="55" t="s">
+        <v>35</v>
+      </c>
+      <c r="I23" s="55"/>
+      <c r="J23" s="55"/>
+      <c r="K23" s="55"/>
+      <c r="L23" s="55"/>
+      <c r="M23" s="55"/>
+      <c r="N23" s="55"/>
+      <c r="O23" s="55"/>
+      <c r="P23" s="55"/>
+      <c r="Q23" s="55" t="s">
+        <v>37</v>
+      </c>
+      <c r="R23" s="55"/>
+      <c r="S23" s="55"/>
+      <c r="T23" s="63"/>
+    </row>
+    <row r="24" spans="1:20" s="18" customFormat="1" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A24" s="96"/>
+      <c r="B24" s="94"/>
+      <c r="C24" s="94"/>
+      <c r="D24" s="94"/>
+      <c r="E24" s="94"/>
+      <c r="F24" s="94"/>
+      <c r="G24" s="94"/>
+      <c r="H24" s="95" t="s">
+        <v>22</v>
+      </c>
+      <c r="I24" s="95"/>
+      <c r="J24" s="95"/>
+      <c r="K24" s="95"/>
+      <c r="L24" s="95"/>
+      <c r="M24" s="94"/>
+      <c r="N24" s="94"/>
+      <c r="O24" s="94"/>
+      <c r="P24" s="94"/>
+      <c r="Q24" s="69" t="s">
         <v>47</v>
       </c>
-      <c r="N20" s="95"/>
-      <c r="O20" s="95"/>
-      <c r="P20" s="96"/>
-      <c r="Q20" s="94" t="s">
-        <v>34</v>
-      </c>
-      <c r="R20" s="95"/>
-      <c r="S20" s="95"/>
-      <c r="T20" s="96"/>
-    </row>
-    <row r="21" spans="1:20" s="18" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="79"/>
-      <c r="B21" s="80"/>
-      <c r="C21" s="79"/>
-      <c r="D21" s="80"/>
-      <c r="E21" s="97"/>
-      <c r="F21" s="98"/>
-      <c r="G21" s="99"/>
-      <c r="H21" s="79"/>
-      <c r="I21" s="92"/>
-      <c r="J21" s="92"/>
-      <c r="K21" s="92"/>
-      <c r="L21" s="80"/>
-      <c r="M21" s="79"/>
-      <c r="N21" s="92"/>
-      <c r="O21" s="92"/>
-      <c r="P21" s="80"/>
-      <c r="Q21" s="79"/>
-      <c r="R21" s="92"/>
-      <c r="S21" s="92"/>
-      <c r="T21" s="80"/>
-    </row>
-    <row r="22" spans="1:20" s="18" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="46"/>
-      <c r="B22" s="7"/>
-      <c r="C22" s="7"/>
-      <c r="D22" s="7"/>
-      <c r="E22" s="42"/>
-      <c r="F22" s="42"/>
-      <c r="G22" s="42"/>
-      <c r="H22" s="31" t="s">
-        <v>35</v>
-      </c>
-      <c r="I22" s="7"/>
-      <c r="J22" s="7"/>
-      <c r="K22" s="7"/>
-      <c r="L22" s="7"/>
-      <c r="M22" s="7"/>
-      <c r="N22" s="7"/>
-      <c r="O22" s="7"/>
-      <c r="P22" s="7"/>
-      <c r="Q22" s="49" t="s">
-        <v>37</v>
-      </c>
-      <c r="R22" s="49"/>
-      <c r="S22" s="49"/>
-      <c r="T22" s="50"/>
-    </row>
-    <row r="23" spans="1:20" s="18" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="47"/>
-      <c r="B23" s="7"/>
-      <c r="C23" s="7"/>
-      <c r="D23" s="7"/>
-      <c r="E23" s="42"/>
-      <c r="F23" s="42"/>
-      <c r="G23" s="42"/>
-      <c r="H23" s="31" t="s">
-        <v>36</v>
-      </c>
-      <c r="I23" s="7"/>
-      <c r="J23" s="7"/>
-      <c r="K23" s="7"/>
-      <c r="L23" s="7"/>
-      <c r="M23" s="7"/>
-      <c r="N23" s="7"/>
-      <c r="O23" s="7"/>
-      <c r="P23" s="7"/>
-      <c r="Q23" s="51" t="s">
-        <v>38</v>
-      </c>
-      <c r="R23" s="51"/>
-      <c r="S23" s="51"/>
-      <c r="T23" s="52"/>
-    </row>
-    <row r="24" spans="1:20" s="18" customFormat="1" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A24" s="48"/>
-      <c r="B24" s="43"/>
-      <c r="C24" s="43"/>
-      <c r="D24" s="43"/>
-      <c r="E24" s="43"/>
-      <c r="F24" s="43"/>
-      <c r="G24" s="43"/>
-      <c r="H24" s="44" t="s">
-        <v>23</v>
-      </c>
-      <c r="I24" s="43"/>
-      <c r="J24" s="44" t="s">
-        <v>19</v>
-      </c>
-      <c r="K24" s="43"/>
-      <c r="L24" s="43"/>
-      <c r="M24" s="43"/>
-      <c r="N24" s="43"/>
-      <c r="O24" s="43"/>
-      <c r="P24" s="45"/>
-      <c r="Q24" s="56" t="s">
-        <v>48</v>
-      </c>
-      <c r="R24" s="56"/>
-      <c r="S24" s="56"/>
-      <c r="T24" s="57"/>
+      <c r="R24" s="69"/>
+      <c r="S24" s="69"/>
+      <c r="T24" s="70"/>
     </row>
     <row r="25" spans="1:20" s="18" customFormat="1" ht="18" customHeight="1" thickTop="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="5"/>
-      <c r="B25" s="5"/>
-      <c r="C25" s="5"/>
-      <c r="D25" s="5"/>
-      <c r="E25" s="5"/>
-      <c r="F25" s="5"/>
-      <c r="G25" s="5"/>
-      <c r="I25" s="5"/>
-      <c r="K25" s="5"/>
-      <c r="L25" s="5"/>
-      <c r="M25" s="5"/>
-      <c r="N25" s="5"/>
-      <c r="O25" s="5"/>
-      <c r="P25" s="36"/>
-      <c r="Q25" s="37"/>
-      <c r="R25" s="37"/>
-      <c r="S25" s="37"/>
-      <c r="T25" s="37"/>
+      <c r="A25" s="100"/>
+      <c r="B25" s="100"/>
+      <c r="C25" s="100"/>
+      <c r="D25" s="100"/>
+      <c r="E25" s="100"/>
+      <c r="F25" s="100"/>
+      <c r="G25" s="100"/>
+      <c r="H25" s="99"/>
+      <c r="I25" s="99"/>
+      <c r="J25" s="99"/>
+      <c r="K25" s="99"/>
+      <c r="L25" s="99"/>
+      <c r="M25" s="100"/>
+      <c r="N25" s="100"/>
+      <c r="O25" s="100"/>
+      <c r="P25" s="100"/>
+      <c r="Q25" s="101"/>
+      <c r="R25" s="101"/>
+      <c r="S25" s="101"/>
+      <c r="T25" s="101"/>
     </row>
     <row r="26" spans="1:20" s="18" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" s="27" t="s">
@@ -2692,7 +2716,7 @@
         <v>8</v>
       </c>
       <c r="G26" s="10" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="H26" s="10"/>
       <c r="I26" s="10"/>
@@ -2720,7 +2744,7 @@
         <v>8</v>
       </c>
       <c r="G27" s="5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H27" s="5"/>
       <c r="I27" s="5"/>
@@ -2748,7 +2772,7 @@
         <v>8</v>
       </c>
       <c r="G28" s="5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="H28" s="5"/>
       <c r="I28" s="5"/>
@@ -2776,7 +2800,7 @@
         <v>8</v>
       </c>
       <c r="G29" s="8" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H29" s="8"/>
       <c r="I29" s="8"/>
@@ -2815,92 +2839,92 @@
       <c r="T30" s="5"/>
     </row>
     <row r="31" spans="1:20" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A31" s="39" t="s">
+      <c r="A31" s="37" t="s">
+        <v>29</v>
+      </c>
+      <c r="B31" s="37"/>
+      <c r="C31" s="37"/>
+      <c r="D31" s="37"/>
+      <c r="E31" s="37"/>
+      <c r="F31" s="37"/>
+      <c r="G31" s="37"/>
+      <c r="H31" s="37"/>
+      <c r="I31" s="37"/>
+      <c r="J31" s="37"/>
+    </row>
+    <row r="32" spans="1:20" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A32" s="37"/>
+      <c r="B32" s="37"/>
+      <c r="C32" s="37"/>
+      <c r="D32" s="37"/>
+      <c r="E32" s="37"/>
+      <c r="F32" s="37"/>
+      <c r="G32" s="37"/>
+      <c r="H32" s="37"/>
+      <c r="I32" s="37"/>
+      <c r="J32" s="37"/>
+    </row>
+    <row r="33" spans="1:20" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A33" s="38">
+        <v>1</v>
+      </c>
+      <c r="B33" s="37" t="s">
         <v>30</v>
       </c>
-      <c r="B31" s="39"/>
-      <c r="C31" s="39"/>
-      <c r="D31" s="39"/>
-      <c r="E31" s="39"/>
-      <c r="F31" s="39"/>
-      <c r="G31" s="39"/>
-      <c r="H31" s="39"/>
-      <c r="I31" s="39"/>
-      <c r="J31" s="39"/>
-    </row>
-    <row r="32" spans="1:20" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A32" s="39"/>
-      <c r="B32" s="39"/>
-      <c r="C32" s="39"/>
-      <c r="D32" s="39"/>
-      <c r="E32" s="39"/>
-      <c r="F32" s="39"/>
-      <c r="G32" s="39"/>
-      <c r="H32" s="39"/>
-      <c r="I32" s="39"/>
-      <c r="J32" s="39"/>
-    </row>
-    <row r="33" spans="1:20" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A33" s="40">
-        <v>1</v>
-      </c>
-      <c r="B33" s="39" t="s">
+      <c r="C33" s="37"/>
+      <c r="D33" s="37"/>
+      <c r="E33" s="37"/>
+      <c r="F33" s="37"/>
+      <c r="G33" s="37"/>
+      <c r="H33" s="37"/>
+      <c r="I33" s="37"/>
+      <c r="J33" s="37"/>
+    </row>
+    <row r="34" spans="1:20" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A34" s="38">
+        <v>2</v>
+      </c>
+      <c r="B34" s="37" t="s">
         <v>31</v>
       </c>
-      <c r="C33" s="39"/>
-      <c r="D33" s="39"/>
-      <c r="E33" s="39"/>
-      <c r="F33" s="39"/>
-      <c r="G33" s="39"/>
-      <c r="H33" s="39"/>
-      <c r="I33" s="39"/>
-      <c r="J33" s="39"/>
-    </row>
-    <row r="34" spans="1:20" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A34" s="40">
-        <v>2</v>
-      </c>
-      <c r="B34" s="39" t="s">
+      <c r="C34" s="37"/>
+      <c r="D34" s="37"/>
+      <c r="E34" s="37"/>
+      <c r="F34" s="37"/>
+      <c r="G34" s="37"/>
+      <c r="H34" s="37"/>
+      <c r="I34" s="37"/>
+      <c r="J34" s="37"/>
+    </row>
+    <row r="35" spans="1:20" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A35" s="38">
+        <v>3</v>
+      </c>
+      <c r="B35" s="37" t="s">
         <v>32</v>
       </c>
-      <c r="C34" s="39"/>
-      <c r="D34" s="39"/>
-      <c r="E34" s="39"/>
-      <c r="F34" s="39"/>
-      <c r="G34" s="39"/>
-      <c r="H34" s="39"/>
-      <c r="I34" s="39"/>
-      <c r="J34" s="39"/>
-    </row>
-    <row r="35" spans="1:20" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A35" s="40">
-        <v>3</v>
-      </c>
-      <c r="B35" s="39" t="s">
-        <v>33</v>
-      </c>
-      <c r="C35" s="39"/>
-      <c r="D35" s="39"/>
-      <c r="E35" s="39"/>
-      <c r="F35" s="39"/>
-      <c r="G35" s="39"/>
-      <c r="H35" s="39"/>
-      <c r="I35" s="39"/>
-      <c r="J35" s="39"/>
+      <c r="C35" s="37"/>
+      <c r="D35" s="37"/>
+      <c r="E35" s="37"/>
+      <c r="F35" s="37"/>
+      <c r="G35" s="37"/>
+      <c r="H35" s="37"/>
+      <c r="I35" s="37"/>
+      <c r="J35" s="37"/>
     </row>
     <row r="36" spans="1:20" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A36" s="39"/>
-      <c r="B36" s="39" t="s">
-        <v>29</v>
-      </c>
-      <c r="C36" s="39"/>
-      <c r="D36" s="39"/>
-      <c r="E36" s="39"/>
-      <c r="F36" s="39"/>
-      <c r="G36" s="39"/>
-      <c r="H36" s="39"/>
-      <c r="I36" s="39"/>
-      <c r="J36" s="39"/>
+      <c r="A36" s="37"/>
+      <c r="B36" s="37" t="s">
+        <v>28</v>
+      </c>
+      <c r="C36" s="37"/>
+      <c r="D36" s="37"/>
+      <c r="E36" s="37"/>
+      <c r="F36" s="37"/>
+      <c r="G36" s="37"/>
+      <c r="H36" s="37"/>
+      <c r="I36" s="37"/>
+      <c r="J36" s="37"/>
     </row>
     <row r="37" spans="1:20" s="18" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A37" s="5"/>
@@ -2948,7 +2972,7 @@
     </row>
     <row r="39" spans="1:20" s="18" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A39" s="11" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B39" s="5"/>
       <c r="C39" s="5"/>
@@ -2972,7 +2996,7 @@
     </row>
     <row r="40" spans="1:20" s="18" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A40" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B40" s="5"/>
       <c r="C40" s="5"/>
@@ -3017,8 +3041,8 @@
       <c r="T41" s="5"/>
     </row>
     <row r="42" spans="1:20" s="18" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A42" s="38" t="s">
-        <v>28</v>
+      <c r="A42" s="36" t="s">
+        <v>27</v>
       </c>
       <c r="B42" s="5"/>
       <c r="C42" s="5"/>
@@ -3063,14 +3087,14 @@
       <c r="T43" s="5"/>
     </row>
     <row r="44" spans="1:20" s="18" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A44" s="55" t="s">
-        <v>27</v>
-      </c>
-      <c r="B44" s="55"/>
-      <c r="C44" s="55"/>
-      <c r="D44" s="55"/>
-      <c r="E44" s="55"/>
-      <c r="F44" s="55"/>
+      <c r="A44" s="68" t="s">
+        <v>26</v>
+      </c>
+      <c r="B44" s="68"/>
+      <c r="C44" s="68"/>
+      <c r="D44" s="68"/>
+      <c r="E44" s="68"/>
+      <c r="F44" s="68"/>
       <c r="G44" s="5"/>
       <c r="H44" s="5"/>
       <c r="I44" s="5"/>
@@ -3088,7 +3112,7 @@
     </row>
     <row r="45" spans="1:20" s="18" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A45" s="31" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B45" s="31"/>
       <c r="C45" s="31"/>
@@ -3669,28 +3693,26 @@
       <c r="W76" s="33"/>
     </row>
   </sheetData>
-  <mergeCells count="35">
-    <mergeCell ref="E21:G21"/>
-    <mergeCell ref="H21:L21"/>
-    <mergeCell ref="Q19:T19"/>
-    <mergeCell ref="M19:P19"/>
-    <mergeCell ref="H19:L19"/>
-    <mergeCell ref="H20:L20"/>
-    <mergeCell ref="M20:P20"/>
-    <mergeCell ref="Q20:T20"/>
-    <mergeCell ref="M21:P21"/>
-    <mergeCell ref="Q21:T21"/>
-    <mergeCell ref="A3:T3"/>
-    <mergeCell ref="A4:T4"/>
-    <mergeCell ref="A5:T5"/>
-    <mergeCell ref="A6:T6"/>
-    <mergeCell ref="N12:S12"/>
-    <mergeCell ref="E19:G19"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="C20:D20"/>
+  <mergeCells count="56">
+    <mergeCell ref="H25:L25"/>
+    <mergeCell ref="M25:P25"/>
+    <mergeCell ref="Q25:T25"/>
+    <mergeCell ref="E25:G25"/>
+    <mergeCell ref="A25:B25"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="E22:G22"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="M23:P23"/>
+    <mergeCell ref="M24:P24"/>
+    <mergeCell ref="H23:L23"/>
+    <mergeCell ref="H24:L24"/>
+    <mergeCell ref="A24:B24"/>
+    <mergeCell ref="A23:B23"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="C24:D24"/>
+    <mergeCell ref="E23:G23"/>
+    <mergeCell ref="E24:G24"/>
     <mergeCell ref="Q22:T22"/>
     <mergeCell ref="Q23:T23"/>
     <mergeCell ref="K14:N14"/>
@@ -3705,6 +3727,29 @@
     <mergeCell ref="H17:L18"/>
     <mergeCell ref="A20:B20"/>
     <mergeCell ref="E20:G20"/>
+    <mergeCell ref="M22:P22"/>
+    <mergeCell ref="H22:L22"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="A3:T3"/>
+    <mergeCell ref="A4:T4"/>
+    <mergeCell ref="A5:T5"/>
+    <mergeCell ref="A6:T6"/>
+    <mergeCell ref="N12:S12"/>
+    <mergeCell ref="E21:G21"/>
+    <mergeCell ref="H21:L21"/>
+    <mergeCell ref="Q19:T19"/>
+    <mergeCell ref="M19:P19"/>
+    <mergeCell ref="H19:L19"/>
+    <mergeCell ref="H20:L20"/>
+    <mergeCell ref="M20:P20"/>
+    <mergeCell ref="Q20:T20"/>
+    <mergeCell ref="M21:P21"/>
+    <mergeCell ref="Q21:T21"/>
+    <mergeCell ref="E19:G19"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <printOptions horizontalCentered="1"/>

--- a/RFQ Generator Beta Version/Templates/DE TEMPLATE.xlsx
+++ b/RFQ Generator Beta Version/Templates/DE TEMPLATE.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\source\repos\RFQ Generator Beta Version\RFQ Generator Beta Version\Templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0EF364E6-594C-43C3-812F-068C5F37803E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E95DB579-DFE7-44DF-A850-75D666F74ACD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{02CCD737-9343-44DD-A110-541534088332}"/>
   </bookViews>
@@ -16,8 +16,8 @@
     <sheet name="PRICED" sheetId="27" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">PRICED!$A$2:$T$45</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="0">PRICED!$2:$18</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">PRICED!$A$1:$T$42</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="0">PRICED!$1:$17</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="47">
   <si>
     <t>ITEM</t>
   </si>
@@ -141,18 +141,9 @@
     <t>total_price</t>
   </si>
   <si>
-    <t>SUB TOTAL</t>
-  </si>
-  <si>
-    <t>DISCOUNT</t>
-  </si>
-  <si>
     <t>sub_total</t>
   </si>
   <si>
-    <t>_discount</t>
-  </si>
-  <si>
     <t>client_name</t>
   </si>
   <si>
@@ -178,9 +169,6 @@
   </si>
   <si>
     <t>unit_price</t>
-  </si>
-  <si>
-    <t>summary_total_price</t>
   </si>
   <si>
     <t>_validity</t>
@@ -300,7 +288,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="16">
+  <borders count="12">
     <border>
       <left/>
       <right/>
@@ -400,26 +388,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="thick">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="thick">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="medium">
         <color indexed="64"/>
       </left>
@@ -428,26 +396,6 @@
         <color indexed="64"/>
       </top>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom style="thick">
-        <color indexed="64"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -467,7 +415,7 @@
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="165" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="102">
+  <cellXfs count="94">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -542,6 +490,126 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="39" fontId="5" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -551,24 +619,12 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -587,18 +643,6 @@
     <xf numFmtId="4" fontId="5" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -607,126 +651,6 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="4" fontId="5" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="5" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="39" fontId="5" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1419,13 +1343,13 @@
     <xdr:from>
       <xdr:col>6</xdr:col>
       <xdr:colOff>1202055</xdr:colOff>
-      <xdr:row>2</xdr:row>
+      <xdr:row>1</xdr:row>
       <xdr:rowOff>26670</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>19</xdr:col>
       <xdr:colOff>1914</xdr:colOff>
-      <xdr:row>7</xdr:row>
+      <xdr:row>6</xdr:row>
       <xdr:rowOff>228584</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -1620,14 +1544,14 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>99060</xdr:colOff>
-      <xdr:row>2</xdr:row>
+      <xdr:row>1</xdr:row>
       <xdr:rowOff>30480</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>434340</xdr:colOff>
-      <xdr:row>7</xdr:row>
-      <xdr:rowOff>144780</xdr:rowOff>
+      <xdr:colOff>538614</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>144779</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1694,13 +1618,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>39</xdr:row>
+      <xdr:row>36</xdr:row>
       <xdr:rowOff>152400</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>754380</xdr:colOff>
-      <xdr:row>43</xdr:row>
+      <xdr:colOff>754381</xdr:colOff>
+      <xdr:row>40</xdr:row>
       <xdr:rowOff>99060</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -2115,128 +2039,152 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{457F1634-390D-461A-B4FA-B698C0706EE9}">
-  <dimension ref="A2:W76"/>
+  <dimension ref="A1:W73"/>
   <sheetFormatPr defaultColWidth="3.6640625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="2" width="3.6640625" style="5" customWidth="1"/>
+    <col min="1" max="1" width="3.21875" style="5" customWidth="1"/>
+    <col min="2" max="2" width="2.44140625" style="5" customWidth="1"/>
     <col min="3" max="3" width="2.5546875" style="5" customWidth="1"/>
     <col min="4" max="4" width="3.33203125" style="5" customWidth="1"/>
     <col min="5" max="5" width="24.44140625" style="5" customWidth="1"/>
     <col min="6" max="6" width="2.33203125" style="5" customWidth="1"/>
-    <col min="7" max="7" width="41" style="5" customWidth="1"/>
+    <col min="7" max="7" width="51.44140625" style="5" customWidth="1"/>
     <col min="8" max="8" width="3.6640625" style="5" customWidth="1"/>
     <col min="9" max="9" width="2.5546875" style="5" customWidth="1"/>
-    <col min="10" max="11" width="3.6640625" style="5" hidden="1" customWidth="1"/>
-    <col min="12" max="12" width="5.6640625" style="5" customWidth="1"/>
+    <col min="10" max="10" width="3.6640625" style="5" hidden="1" customWidth="1"/>
+    <col min="11" max="11" width="3.33203125" style="5" customWidth="1"/>
+    <col min="12" max="12" width="1" style="5" customWidth="1"/>
     <col min="13" max="13" width="4" style="5" customWidth="1"/>
     <col min="14" max="14" width="4.44140625" style="5" customWidth="1"/>
-    <col min="15" max="15" width="3.6640625" style="5" customWidth="1"/>
-    <col min="16" max="16" width="2.88671875" style="5" customWidth="1"/>
-    <col min="17" max="17" width="3.5546875" style="5" customWidth="1"/>
+    <col min="15" max="15" width="2.88671875" style="5" customWidth="1"/>
+    <col min="16" max="16" width="0.33203125" style="5" customWidth="1"/>
+    <col min="17" max="17" width="0.88671875" style="5" customWidth="1"/>
     <col min="18" max="19" width="3.6640625" style="5" customWidth="1"/>
-    <col min="20" max="20" width="5.44140625" style="5" customWidth="1"/>
+    <col min="20" max="20" width="5.5546875" style="5" customWidth="1"/>
     <col min="21" max="16384" width="3.6640625" style="5"/>
   </cols>
   <sheetData>
+    <row r="1" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="1"/>
+      <c r="B1" s="1"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="3"/>
+      <c r="F1" s="4"/>
+      <c r="Q1" s="6"/>
+      <c r="R1" s="6"/>
+      <c r="S1" s="6"/>
+      <c r="T1" s="6"/>
+    </row>
     <row r="2" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="1"/>
-      <c r="B2" s="1"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="4"/>
-      <c r="Q2" s="6"/>
-      <c r="R2" s="6"/>
-      <c r="S2" s="6"/>
-      <c r="T2" s="6"/>
+      <c r="A2" s="76"/>
+      <c r="B2" s="76"/>
+      <c r="C2" s="76"/>
+      <c r="D2" s="76"/>
+      <c r="E2" s="76"/>
+      <c r="F2" s="76"/>
+      <c r="G2" s="76"/>
+      <c r="H2" s="76"/>
+      <c r="I2" s="76"/>
+      <c r="J2" s="76"/>
+      <c r="K2" s="76"/>
+      <c r="L2" s="76"/>
+      <c r="M2" s="76"/>
+      <c r="N2" s="76"/>
+      <c r="O2" s="76"/>
+      <c r="P2" s="76"/>
+      <c r="Q2" s="76"/>
+      <c r="R2" s="76"/>
+      <c r="S2" s="76"/>
+      <c r="T2" s="76"/>
     </row>
     <row r="3" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="55"/>
-      <c r="B3" s="55"/>
-      <c r="C3" s="55"/>
-      <c r="D3" s="55"/>
-      <c r="E3" s="55"/>
-      <c r="F3" s="55"/>
-      <c r="G3" s="55"/>
-      <c r="H3" s="55"/>
-      <c r="I3" s="55"/>
-      <c r="J3" s="55"/>
-      <c r="K3" s="55"/>
-      <c r="L3" s="55"/>
-      <c r="M3" s="55"/>
-      <c r="N3" s="55"/>
-      <c r="O3" s="55"/>
-      <c r="P3" s="55"/>
-      <c r="Q3" s="55"/>
-      <c r="R3" s="55"/>
-      <c r="S3" s="55"/>
-      <c r="T3" s="55"/>
-    </row>
-    <row r="4" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="56"/>
-      <c r="B4" s="56"/>
-      <c r="C4" s="56"/>
-      <c r="D4" s="56"/>
-      <c r="E4" s="56"/>
-      <c r="F4" s="56"/>
-      <c r="G4" s="56"/>
-      <c r="H4" s="56"/>
-      <c r="I4" s="56"/>
-      <c r="J4" s="56"/>
-      <c r="K4" s="56"/>
-      <c r="L4" s="56"/>
-      <c r="M4" s="56"/>
-      <c r="N4" s="56"/>
-      <c r="O4" s="56"/>
-      <c r="P4" s="56"/>
-      <c r="Q4" s="56"/>
-      <c r="R4" s="56"/>
-      <c r="S4" s="56"/>
-      <c r="T4" s="56"/>
-    </row>
-    <row r="5" spans="1:20" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="57"/>
-      <c r="B5" s="57"/>
-      <c r="C5" s="57"/>
-      <c r="D5" s="57"/>
-      <c r="E5" s="57"/>
-      <c r="F5" s="57"/>
-      <c r="G5" s="57"/>
-      <c r="H5" s="57"/>
-      <c r="I5" s="57"/>
-      <c r="J5" s="57"/>
-      <c r="K5" s="57"/>
-      <c r="L5" s="57"/>
-      <c r="M5" s="57"/>
-      <c r="N5" s="57"/>
-      <c r="O5" s="57"/>
-      <c r="P5" s="57"/>
-      <c r="Q5" s="57"/>
-      <c r="R5" s="57"/>
-      <c r="S5" s="57"/>
-      <c r="T5" s="57"/>
-    </row>
-    <row r="6" spans="1:20" ht="30.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="55"/>
-      <c r="B6" s="55"/>
-      <c r="C6" s="55"/>
-      <c r="D6" s="55"/>
-      <c r="E6" s="55"/>
-      <c r="F6" s="55"/>
-      <c r="G6" s="55"/>
-      <c r="H6" s="55"/>
-      <c r="I6" s="55"/>
-      <c r="J6" s="55"/>
-      <c r="K6" s="55"/>
-      <c r="L6" s="55"/>
-      <c r="M6" s="55"/>
-      <c r="N6" s="55"/>
-      <c r="O6" s="55"/>
-      <c r="P6" s="55"/>
-      <c r="Q6" s="55"/>
-      <c r="R6" s="55"/>
-      <c r="S6" s="55"/>
-      <c r="T6" s="55"/>
+      <c r="A3" s="77"/>
+      <c r="B3" s="77"/>
+      <c r="C3" s="77"/>
+      <c r="D3" s="77"/>
+      <c r="E3" s="77"/>
+      <c r="F3" s="77"/>
+      <c r="G3" s="77"/>
+      <c r="H3" s="77"/>
+      <c r="I3" s="77"/>
+      <c r="J3" s="77"/>
+      <c r="K3" s="77"/>
+      <c r="L3" s="77"/>
+      <c r="M3" s="77"/>
+      <c r="N3" s="77"/>
+      <c r="O3" s="77"/>
+      <c r="P3" s="77"/>
+      <c r="Q3" s="77"/>
+      <c r="R3" s="77"/>
+      <c r="S3" s="77"/>
+      <c r="T3" s="77"/>
+    </row>
+    <row r="4" spans="1:20" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="78"/>
+      <c r="B4" s="78"/>
+      <c r="C4" s="78"/>
+      <c r="D4" s="78"/>
+      <c r="E4" s="78"/>
+      <c r="F4" s="78"/>
+      <c r="G4" s="78"/>
+      <c r="H4" s="78"/>
+      <c r="I4" s="78"/>
+      <c r="J4" s="78"/>
+      <c r="K4" s="78"/>
+      <c r="L4" s="78"/>
+      <c r="M4" s="78"/>
+      <c r="N4" s="78"/>
+      <c r="O4" s="78"/>
+      <c r="P4" s="78"/>
+      <c r="Q4" s="78"/>
+      <c r="R4" s="78"/>
+      <c r="S4" s="78"/>
+      <c r="T4" s="78"/>
+    </row>
+    <row r="5" spans="1:20" ht="30.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="76"/>
+      <c r="B5" s="76"/>
+      <c r="C5" s="76"/>
+      <c r="D5" s="76"/>
+      <c r="E5" s="76"/>
+      <c r="F5" s="76"/>
+      <c r="G5" s="76"/>
+      <c r="H5" s="76"/>
+      <c r="I5" s="76"/>
+      <c r="J5" s="76"/>
+      <c r="K5" s="76"/>
+      <c r="L5" s="76"/>
+      <c r="M5" s="76"/>
+      <c r="N5" s="76"/>
+      <c r="O5" s="76"/>
+      <c r="P5" s="76"/>
+      <c r="Q5" s="76"/>
+      <c r="R5" s="76"/>
+      <c r="S5" s="76"/>
+      <c r="T5" s="76"/>
+    </row>
+    <row r="6" spans="1:20" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="7"/>
+      <c r="B6" s="7"/>
+      <c r="C6" s="7"/>
+      <c r="D6" s="7"/>
+      <c r="E6" s="7"/>
+      <c r="F6" s="7"/>
+      <c r="G6" s="7"/>
+      <c r="H6" s="7"/>
+      <c r="I6" s="7"/>
+      <c r="J6" s="7"/>
+      <c r="K6" s="7"/>
+      <c r="L6" s="7"/>
+      <c r="M6" s="7"/>
+      <c r="N6" s="7"/>
+      <c r="O6" s="7"/>
+      <c r="P6" s="7"/>
+      <c r="Q6" s="7"/>
+      <c r="R6" s="7"/>
+      <c r="S6" s="7"/>
+      <c r="T6" s="7"/>
     </row>
     <row r="7" spans="1:20" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="7"/>
@@ -2260,7 +2208,7 @@
       <c r="S7" s="7"/>
       <c r="T7" s="7"/>
     </row>
-    <row r="8" spans="1:20" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="7"/>
       <c r="B8" s="7"/>
       <c r="C8" s="7"/>
@@ -2282,470 +2230,468 @@
       <c r="S8" s="7"/>
       <c r="T8" s="7"/>
     </row>
-    <row r="9" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="7"/>
-      <c r="B9" s="7"/>
-      <c r="C9" s="7"/>
-      <c r="D9" s="7"/>
-      <c r="E9" s="7"/>
-      <c r="F9" s="7"/>
-      <c r="G9" s="7"/>
-      <c r="H9" s="7"/>
-      <c r="I9" s="7"/>
-      <c r="J9" s="7"/>
-      <c r="K9" s="7"/>
-      <c r="L9" s="7"/>
-      <c r="M9" s="7"/>
-      <c r="N9" s="7"/>
-      <c r="O9" s="7"/>
-      <c r="P9" s="7"/>
-      <c r="Q9" s="7"/>
-      <c r="R9" s="7"/>
-      <c r="S9" s="7"/>
-      <c r="T9" s="7"/>
-    </row>
-    <row r="10" spans="1:20" ht="6" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="8"/>
-      <c r="B10" s="8"/>
-      <c r="C10" s="8"/>
-      <c r="D10" s="8"/>
-      <c r="E10" s="8"/>
-      <c r="F10" s="8"/>
-      <c r="G10" s="8"/>
-      <c r="H10" s="8"/>
-      <c r="I10" s="8"/>
-      <c r="J10" s="8"/>
-      <c r="K10" s="8"/>
-      <c r="L10" s="8"/>
-      <c r="M10" s="8"/>
-      <c r="N10" s="8"/>
-      <c r="O10" s="8"/>
-      <c r="P10" s="8"/>
-      <c r="Q10" s="8"/>
-      <c r="R10" s="8"/>
-      <c r="S10" s="8"/>
-      <c r="T10" s="8"/>
+    <row r="9" spans="1:20" ht="6" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="8"/>
+      <c r="B9" s="8"/>
+      <c r="C9" s="8"/>
+      <c r="D9" s="8"/>
+      <c r="E9" s="8"/>
+      <c r="F9" s="8"/>
+      <c r="G9" s="8"/>
+      <c r="H9" s="8"/>
+      <c r="I9" s="8"/>
+      <c r="J9" s="8"/>
+      <c r="K9" s="8"/>
+      <c r="L9" s="8"/>
+      <c r="M9" s="8"/>
+      <c r="N9" s="8"/>
+      <c r="O9" s="8"/>
+      <c r="P9" s="8"/>
+      <c r="Q9" s="8"/>
+      <c r="R9" s="8"/>
+      <c r="S9" s="8"/>
+      <c r="T9" s="8"/>
+    </row>
+    <row r="10" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="B10" s="10"/>
+      <c r="C10" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="H10" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="I10" s="11"/>
+      <c r="J10" s="12"/>
+      <c r="K10" s="13"/>
+      <c r="M10" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="N10" s="14" t="s">
+        <v>36</v>
+      </c>
+      <c r="S10" s="10"/>
+      <c r="T10" s="15"/>
     </row>
     <row r="11" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="B11" s="10"/>
+      <c r="A11" s="16" t="s">
+        <v>3</v>
+      </c>
       <c r="C11" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D11" s="5" t="s">
-        <v>38</v>
-      </c>
+      <c r="D11" s="35"/>
+      <c r="E11" s="1"/>
       <c r="H11" s="11" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="I11" s="11"/>
-      <c r="J11" s="12"/>
-      <c r="K11" s="13" t="s">
-        <v>8</v>
-      </c>
+      <c r="J11" s="11"/>
+      <c r="K11" s="1"/>
       <c r="M11" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="N11" s="14" t="s">
-        <v>39</v>
-      </c>
-      <c r="S11" s="10"/>
-      <c r="T11" s="15"/>
+      <c r="N11" s="79" t="s">
+        <v>37</v>
+      </c>
+      <c r="O11" s="79"/>
+      <c r="P11" s="79"/>
+      <c r="Q11" s="79"/>
+      <c r="R11" s="79"/>
+      <c r="S11" s="79"/>
+      <c r="T11" s="17"/>
     </row>
     <row r="12" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="16" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D12" s="35"/>
-      <c r="E12" s="1"/>
       <c r="H12" s="11" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="I12" s="11"/>
       <c r="J12" s="11"/>
-      <c r="K12" s="1" t="s">
-        <v>8</v>
-      </c>
+      <c r="K12" s="1"/>
       <c r="M12" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="N12" s="58" t="s">
-        <v>40</v>
-      </c>
-      <c r="O12" s="58"/>
-      <c r="P12" s="58"/>
-      <c r="Q12" s="58"/>
-      <c r="R12" s="58"/>
-      <c r="S12" s="58"/>
+      <c r="N12" s="5" t="s">
+        <v>38</v>
+      </c>
       <c r="T12" s="17"/>
     </row>
     <row r="13" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="16" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="H13" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="I13" s="11"/>
-      <c r="J13" s="11"/>
-      <c r="K13" s="1" t="s">
+      <c r="E13" s="1"/>
+      <c r="K13" s="46"/>
+      <c r="L13" s="47"/>
+      <c r="M13" s="47"/>
+      <c r="N13" s="47"/>
+      <c r="O13" s="1"/>
+      <c r="P13" s="19"/>
+      <c r="Q13" s="1"/>
+      <c r="R13" s="1"/>
+      <c r="T13" s="17"/>
+    </row>
+    <row r="14" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A14" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="B14" s="8"/>
+      <c r="C14" s="21" t="s">
         <v>8</v>
       </c>
-      <c r="M13" s="1" t="s">
+      <c r="D14" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E14" s="22"/>
+      <c r="F14" s="22"/>
+      <c r="G14" s="22"/>
+      <c r="H14" s="8"/>
+      <c r="I14" s="8"/>
+      <c r="J14" s="8"/>
+      <c r="K14" s="8"/>
+      <c r="L14" s="23"/>
+      <c r="M14" s="8"/>
+      <c r="N14" s="60" t="s">
+        <v>24</v>
+      </c>
+      <c r="O14" s="60"/>
+      <c r="P14" s="60"/>
+      <c r="Q14" s="60"/>
+      <c r="R14" s="60"/>
+      <c r="S14" s="60"/>
+      <c r="T14" s="61"/>
+    </row>
+    <row r="15" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="39"/>
+      <c r="C15" s="1"/>
+      <c r="E15" s="24"/>
+      <c r="F15" s="24"/>
+      <c r="G15" s="24"/>
+      <c r="L15" s="18"/>
+      <c r="N15" s="7"/>
+      <c r="O15" s="7"/>
+      <c r="P15" s="7"/>
+      <c r="Q15" s="7"/>
+      <c r="R15" s="7"/>
+      <c r="S15" s="7"/>
+      <c r="T15" s="7"/>
+    </row>
+    <row r="16" spans="1:20" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="56" t="s">
+        <v>0</v>
+      </c>
+      <c r="B16" s="49"/>
+      <c r="C16" s="49" t="s">
+        <v>18</v>
+      </c>
+      <c r="D16" s="49"/>
+      <c r="E16" s="51" t="s">
+        <v>1</v>
+      </c>
+      <c r="F16" s="52"/>
+      <c r="G16" s="53"/>
+      <c r="H16" s="56" t="s">
+        <v>19</v>
+      </c>
+      <c r="I16" s="62"/>
+      <c r="J16" s="62"/>
+      <c r="K16" s="62"/>
+      <c r="L16" s="63"/>
+      <c r="M16" s="56" t="s">
+        <v>2</v>
+      </c>
+      <c r="N16" s="49"/>
+      <c r="O16" s="49"/>
+      <c r="P16" s="57"/>
+      <c r="Q16" s="56" t="s">
+        <v>11</v>
+      </c>
+      <c r="R16" s="49"/>
+      <c r="S16" s="49"/>
+      <c r="T16" s="57"/>
+    </row>
+    <row r="17" spans="1:20" s="25" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="58"/>
+      <c r="B17" s="50"/>
+      <c r="C17" s="50"/>
+      <c r="D17" s="50"/>
+      <c r="E17" s="54"/>
+      <c r="F17" s="54"/>
+      <c r="G17" s="55"/>
+      <c r="H17" s="64"/>
+      <c r="I17" s="65"/>
+      <c r="J17" s="65"/>
+      <c r="K17" s="65"/>
+      <c r="L17" s="66"/>
+      <c r="M17" s="58"/>
+      <c r="N17" s="50"/>
+      <c r="O17" s="50"/>
+      <c r="P17" s="59"/>
+      <c r="Q17" s="58"/>
+      <c r="R17" s="50"/>
+      <c r="S17" s="50"/>
+      <c r="T17" s="59"/>
+    </row>
+    <row r="18" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="74"/>
+      <c r="B18" s="75"/>
+      <c r="C18" s="74"/>
+      <c r="D18" s="75"/>
+      <c r="E18" s="91"/>
+      <c r="F18" s="92"/>
+      <c r="G18" s="93"/>
+      <c r="H18" s="74"/>
+      <c r="I18" s="84"/>
+      <c r="J18" s="84"/>
+      <c r="K18" s="84"/>
+      <c r="L18" s="75"/>
+      <c r="M18" s="74"/>
+      <c r="N18" s="84"/>
+      <c r="O18" s="84"/>
+      <c r="P18" s="75"/>
+      <c r="Q18" s="74"/>
+      <c r="R18" s="84"/>
+      <c r="S18" s="84"/>
+      <c r="T18" s="75"/>
+    </row>
+    <row r="19" spans="1:20" s="18" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="67" t="s">
+        <v>39</v>
+      </c>
+      <c r="B19" s="68"/>
+      <c r="C19" s="67" t="s">
+        <v>40</v>
+      </c>
+      <c r="D19" s="68"/>
+      <c r="E19" s="69" t="s">
+        <v>41</v>
+      </c>
+      <c r="F19" s="48"/>
+      <c r="G19" s="70"/>
+      <c r="H19" s="85" t="s">
+        <v>42</v>
+      </c>
+      <c r="I19" s="86"/>
+      <c r="J19" s="86"/>
+      <c r="K19" s="86"/>
+      <c r="L19" s="87"/>
+      <c r="M19" s="88" t="s">
+        <v>43</v>
+      </c>
+      <c r="N19" s="89"/>
+      <c r="O19" s="89"/>
+      <c r="P19" s="90"/>
+      <c r="Q19" s="88" t="s">
+        <v>33</v>
+      </c>
+      <c r="R19" s="89"/>
+      <c r="S19" s="89"/>
+      <c r="T19" s="90"/>
+    </row>
+    <row r="20" spans="1:20" s="18" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="72"/>
+      <c r="B20" s="73"/>
+      <c r="C20" s="72"/>
+      <c r="D20" s="73"/>
+      <c r="E20" s="80"/>
+      <c r="F20" s="81"/>
+      <c r="G20" s="82"/>
+      <c r="H20" s="72"/>
+      <c r="I20" s="83"/>
+      <c r="J20" s="83"/>
+      <c r="K20" s="83"/>
+      <c r="L20" s="73"/>
+      <c r="M20" s="72"/>
+      <c r="N20" s="83"/>
+      <c r="O20" s="83"/>
+      <c r="P20" s="73"/>
+      <c r="Q20" s="72"/>
+      <c r="R20" s="83"/>
+      <c r="S20" s="83"/>
+      <c r="T20" s="73"/>
+    </row>
+    <row r="21" spans="1:20" s="18" customFormat="1" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A21" s="40"/>
+      <c r="B21" s="41"/>
+      <c r="C21" s="41"/>
+      <c r="D21" s="41"/>
+      <c r="E21" s="71"/>
+      <c r="F21" s="71"/>
+      <c r="G21" s="71"/>
+      <c r="H21" s="41" t="s">
+        <v>22</v>
+      </c>
+      <c r="I21" s="41"/>
+      <c r="J21" s="41"/>
+      <c r="K21" s="41"/>
+      <c r="L21" s="41"/>
+      <c r="M21" s="41"/>
+      <c r="N21" s="41"/>
+      <c r="O21" s="41"/>
+      <c r="P21" s="41"/>
+      <c r="Q21" s="41" t="s">
+        <v>34</v>
+      </c>
+      <c r="R21" s="41"/>
+      <c r="S21" s="41"/>
+      <c r="T21" s="45"/>
+    </row>
+    <row r="22" spans="1:20" s="18" customFormat="1" ht="18" customHeight="1" thickTop="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="43"/>
+      <c r="B22" s="43"/>
+      <c r="C22" s="43"/>
+      <c r="D22" s="43"/>
+      <c r="E22" s="43"/>
+      <c r="F22" s="43"/>
+      <c r="G22" s="43"/>
+      <c r="H22" s="42"/>
+      <c r="I22" s="42"/>
+      <c r="J22" s="42"/>
+      <c r="K22" s="42"/>
+      <c r="L22" s="42"/>
+      <c r="M22" s="43"/>
+      <c r="N22" s="43"/>
+      <c r="O22" s="43"/>
+      <c r="P22" s="43"/>
+      <c r="Q22" s="44"/>
+      <c r="R22" s="44"/>
+      <c r="S22" s="44"/>
+      <c r="T22" s="44"/>
+    </row>
+    <row r="23" spans="1:20" s="18" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A23" s="27" t="s">
+        <v>12</v>
+      </c>
+      <c r="B23" s="10"/>
+      <c r="C23" s="10"/>
+      <c r="D23" s="10"/>
+      <c r="E23" s="10"/>
+      <c r="F23" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="N13" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="T13" s="17"/>
-    </row>
-    <row r="14" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="16" t="s">
-        <v>6</v>
-      </c>
-      <c r="C14" s="1" t="s">
+      <c r="G23" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="H23" s="10"/>
+      <c r="I23" s="10"/>
+      <c r="J23" s="10"/>
+      <c r="K23" s="10"/>
+      <c r="L23" s="10"/>
+      <c r="M23" s="10"/>
+      <c r="N23" s="10"/>
+      <c r="O23" s="10"/>
+      <c r="P23" s="10"/>
+      <c r="Q23" s="10"/>
+      <c r="R23" s="10"/>
+      <c r="S23" s="10"/>
+      <c r="T23" s="15"/>
+    </row>
+    <row r="24" spans="1:20" s="18" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A24" s="28" t="s">
+        <v>13</v>
+      </c>
+      <c r="B24" s="5"/>
+      <c r="C24" s="5"/>
+      <c r="D24" s="5"/>
+      <c r="E24" s="5"/>
+      <c r="F24" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="E14" s="1"/>
-      <c r="K14" s="66"/>
-      <c r="L14" s="67"/>
-      <c r="M14" s="67"/>
-      <c r="N14" s="67"/>
-      <c r="O14" s="1"/>
-      <c r="P14" s="19"/>
-      <c r="Q14" s="1"/>
-      <c r="R14" s="1"/>
-      <c r="T14" s="17"/>
-    </row>
-    <row r="15" spans="1:20" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A15" s="20" t="s">
-        <v>7</v>
-      </c>
-      <c r="B15" s="8"/>
-      <c r="C15" s="21" t="s">
+      <c r="G24" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="H24" s="5"/>
+      <c r="I24" s="5"/>
+      <c r="J24" s="5"/>
+      <c r="K24" s="5"/>
+      <c r="L24" s="5"/>
+      <c r="M24" s="5"/>
+      <c r="N24" s="5"/>
+      <c r="O24" s="5"/>
+      <c r="P24" s="5"/>
+      <c r="Q24" s="5"/>
+      <c r="R24" s="5"/>
+      <c r="S24" s="5"/>
+      <c r="T24" s="17"/>
+    </row>
+    <row r="25" spans="1:20" s="18" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A25" s="28" t="s">
+        <v>14</v>
+      </c>
+      <c r="B25" s="5"/>
+      <c r="C25" s="5"/>
+      <c r="D25" s="5"/>
+      <c r="E25" s="5"/>
+      <c r="F25" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D15" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="E15" s="22"/>
-      <c r="F15" s="22"/>
-      <c r="G15" s="22"/>
-      <c r="H15" s="8"/>
-      <c r="I15" s="8"/>
-      <c r="J15" s="8"/>
-      <c r="K15" s="8"/>
-      <c r="L15" s="23"/>
-      <c r="M15" s="8"/>
-      <c r="N15" s="82" t="s">
-        <v>24</v>
-      </c>
-      <c r="O15" s="82"/>
-      <c r="P15" s="82"/>
-      <c r="Q15" s="82"/>
-      <c r="R15" s="82"/>
-      <c r="S15" s="82"/>
-      <c r="T15" s="83"/>
-    </row>
-    <row r="16" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="39"/>
-      <c r="C16" s="1"/>
-      <c r="E16" s="24"/>
-      <c r="F16" s="24"/>
-      <c r="G16" s="24"/>
-      <c r="L16" s="18"/>
-      <c r="N16" s="7"/>
-      <c r="O16" s="7"/>
-      <c r="P16" s="7"/>
-      <c r="Q16" s="7"/>
-      <c r="R16" s="7"/>
-      <c r="S16" s="7"/>
-      <c r="T16" s="7"/>
-    </row>
-    <row r="17" spans="1:20" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="78" t="s">
-        <v>0</v>
-      </c>
-      <c r="B17" s="71"/>
-      <c r="C17" s="71" t="s">
-        <v>18</v>
-      </c>
-      <c r="D17" s="71"/>
-      <c r="E17" s="73" t="s">
-        <v>1</v>
-      </c>
-      <c r="F17" s="74"/>
-      <c r="G17" s="75"/>
-      <c r="H17" s="78" t="s">
-        <v>19</v>
-      </c>
-      <c r="I17" s="84"/>
-      <c r="J17" s="84"/>
-      <c r="K17" s="84"/>
-      <c r="L17" s="85"/>
-      <c r="M17" s="78" t="s">
-        <v>2</v>
-      </c>
-      <c r="N17" s="71"/>
-      <c r="O17" s="71"/>
-      <c r="P17" s="79"/>
-      <c r="Q17" s="78" t="s">
-        <v>11</v>
-      </c>
-      <c r="R17" s="71"/>
-      <c r="S17" s="71"/>
-      <c r="T17" s="79"/>
-    </row>
-    <row r="18" spans="1:20" s="25" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="80"/>
-      <c r="B18" s="72"/>
-      <c r="C18" s="72"/>
-      <c r="D18" s="72"/>
-      <c r="E18" s="76"/>
-      <c r="F18" s="76"/>
-      <c r="G18" s="77"/>
-      <c r="H18" s="86"/>
-      <c r="I18" s="87"/>
-      <c r="J18" s="87"/>
-      <c r="K18" s="87"/>
-      <c r="L18" s="88"/>
-      <c r="M18" s="80"/>
-      <c r="N18" s="72"/>
-      <c r="O18" s="72"/>
-      <c r="P18" s="81"/>
-      <c r="Q18" s="80"/>
-      <c r="R18" s="72"/>
-      <c r="S18" s="72"/>
-      <c r="T18" s="81"/>
-    </row>
-    <row r="19" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="46"/>
-      <c r="B19" s="48"/>
-      <c r="C19" s="46"/>
-      <c r="D19" s="48"/>
-      <c r="E19" s="59"/>
-      <c r="F19" s="60"/>
-      <c r="G19" s="61"/>
-      <c r="H19" s="46"/>
-      <c r="I19" s="47"/>
-      <c r="J19" s="47"/>
-      <c r="K19" s="47"/>
-      <c r="L19" s="48"/>
-      <c r="M19" s="46"/>
-      <c r="N19" s="47"/>
-      <c r="O19" s="47"/>
-      <c r="P19" s="48"/>
-      <c r="Q19" s="46"/>
-      <c r="R19" s="47"/>
-      <c r="S19" s="47"/>
-      <c r="T19" s="48"/>
-    </row>
-    <row r="20" spans="1:20" s="18" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="62" t="s">
-        <v>42</v>
-      </c>
-      <c r="B20" s="63"/>
-      <c r="C20" s="62" t="s">
-        <v>43</v>
-      </c>
-      <c r="D20" s="63"/>
-      <c r="E20" s="89" t="s">
-        <v>44</v>
-      </c>
-      <c r="F20" s="68"/>
-      <c r="G20" s="90"/>
-      <c r="H20" s="49" t="s">
+      <c r="G25" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="I20" s="50"/>
-      <c r="J20" s="50"/>
-      <c r="K20" s="50"/>
-      <c r="L20" s="51"/>
-      <c r="M20" s="52" t="s">
+      <c r="H25" s="5"/>
+      <c r="I25" s="5"/>
+      <c r="J25" s="5"/>
+      <c r="K25" s="5"/>
+      <c r="L25" s="5"/>
+      <c r="M25" s="5"/>
+      <c r="N25" s="5"/>
+      <c r="O25" s="5"/>
+      <c r="P25" s="5"/>
+      <c r="Q25" s="5"/>
+      <c r="R25" s="5"/>
+      <c r="S25" s="5"/>
+      <c r="T25" s="17"/>
+    </row>
+    <row r="26" spans="1:20" s="18" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A26" s="29" t="s">
+        <v>15</v>
+      </c>
+      <c r="B26" s="8"/>
+      <c r="C26" s="8"/>
+      <c r="D26" s="8"/>
+      <c r="E26" s="8"/>
+      <c r="F26" s="21" t="s">
+        <v>8</v>
+      </c>
+      <c r="G26" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="N20" s="53"/>
-      <c r="O20" s="53"/>
-      <c r="P20" s="54"/>
-      <c r="Q20" s="52" t="s">
-        <v>33</v>
-      </c>
-      <c r="R20" s="53"/>
-      <c r="S20" s="53"/>
-      <c r="T20" s="54"/>
-    </row>
-    <row r="21" spans="1:20" s="18" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="43"/>
-      <c r="B21" s="45"/>
-      <c r="C21" s="43"/>
-      <c r="D21" s="45"/>
-      <c r="E21" s="40"/>
-      <c r="F21" s="41"/>
-      <c r="G21" s="42"/>
-      <c r="H21" s="43"/>
-      <c r="I21" s="44"/>
-      <c r="J21" s="44"/>
-      <c r="K21" s="44"/>
-      <c r="L21" s="45"/>
-      <c r="M21" s="43"/>
-      <c r="N21" s="44"/>
-      <c r="O21" s="44"/>
-      <c r="P21" s="45"/>
-      <c r="Q21" s="43"/>
-      <c r="R21" s="44"/>
-      <c r="S21" s="44"/>
-      <c r="T21" s="45"/>
-    </row>
-    <row r="22" spans="1:20" s="18" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="93"/>
-      <c r="B22" s="64"/>
-      <c r="C22" s="64"/>
-      <c r="D22" s="64"/>
-      <c r="E22" s="92"/>
-      <c r="F22" s="92"/>
-      <c r="G22" s="92"/>
-      <c r="H22" s="64" t="s">
-        <v>34</v>
-      </c>
-      <c r="I22" s="64"/>
-      <c r="J22" s="64"/>
-      <c r="K22" s="64"/>
-      <c r="L22" s="64"/>
-      <c r="M22" s="64"/>
-      <c r="N22" s="64"/>
-      <c r="O22" s="64"/>
-      <c r="P22" s="64"/>
-      <c r="Q22" s="64" t="s">
-        <v>36</v>
-      </c>
-      <c r="R22" s="64"/>
-      <c r="S22" s="64"/>
-      <c r="T22" s="65"/>
-    </row>
-    <row r="23" spans="1:20" s="18" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="97"/>
-      <c r="B23" s="98"/>
-      <c r="C23" s="55"/>
-      <c r="D23" s="55"/>
-      <c r="E23" s="91"/>
-      <c r="F23" s="91"/>
-      <c r="G23" s="91"/>
-      <c r="H23" s="55" t="s">
-        <v>35</v>
-      </c>
-      <c r="I23" s="55"/>
-      <c r="J23" s="55"/>
-      <c r="K23" s="55"/>
-      <c r="L23" s="55"/>
-      <c r="M23" s="55"/>
-      <c r="N23" s="55"/>
-      <c r="O23" s="55"/>
-      <c r="P23" s="55"/>
-      <c r="Q23" s="55" t="s">
-        <v>37</v>
-      </c>
-      <c r="R23" s="55"/>
-      <c r="S23" s="55"/>
-      <c r="T23" s="63"/>
-    </row>
-    <row r="24" spans="1:20" s="18" customFormat="1" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A24" s="96"/>
-      <c r="B24" s="94"/>
-      <c r="C24" s="94"/>
-      <c r="D24" s="94"/>
-      <c r="E24" s="94"/>
-      <c r="F24" s="94"/>
-      <c r="G24" s="94"/>
-      <c r="H24" s="95" t="s">
-        <v>22</v>
-      </c>
-      <c r="I24" s="95"/>
-      <c r="J24" s="95"/>
-      <c r="K24" s="95"/>
-      <c r="L24" s="95"/>
-      <c r="M24" s="94"/>
-      <c r="N24" s="94"/>
-      <c r="O24" s="94"/>
-      <c r="P24" s="94"/>
-      <c r="Q24" s="69" t="s">
-        <v>47</v>
-      </c>
-      <c r="R24" s="69"/>
-      <c r="S24" s="69"/>
-      <c r="T24" s="70"/>
-    </row>
-    <row r="25" spans="1:20" s="18" customFormat="1" ht="18" customHeight="1" thickTop="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="100"/>
-      <c r="B25" s="100"/>
-      <c r="C25" s="100"/>
-      <c r="D25" s="100"/>
-      <c r="E25" s="100"/>
-      <c r="F25" s="100"/>
-      <c r="G25" s="100"/>
-      <c r="H25" s="99"/>
-      <c r="I25" s="99"/>
-      <c r="J25" s="99"/>
-      <c r="K25" s="99"/>
-      <c r="L25" s="99"/>
-      <c r="M25" s="100"/>
-      <c r="N25" s="100"/>
-      <c r="O25" s="100"/>
-      <c r="P25" s="100"/>
-      <c r="Q25" s="101"/>
-      <c r="R25" s="101"/>
-      <c r="S25" s="101"/>
-      <c r="T25" s="101"/>
-    </row>
-    <row r="26" spans="1:20" s="18" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A26" s="27" t="s">
-        <v>12</v>
-      </c>
-      <c r="B26" s="10"/>
-      <c r="C26" s="10"/>
-      <c r="D26" s="10"/>
-      <c r="E26" s="10"/>
-      <c r="F26" s="13" t="s">
-        <v>8</v>
-      </c>
-      <c r="G26" s="10" t="s">
-        <v>48</v>
-      </c>
-      <c r="H26" s="10"/>
-      <c r="I26" s="10"/>
-      <c r="J26" s="10"/>
-      <c r="K26" s="10"/>
-      <c r="L26" s="10"/>
-      <c r="M26" s="10"/>
-      <c r="N26" s="10"/>
-      <c r="O26" s="10"/>
-      <c r="P26" s="10"/>
-      <c r="Q26" s="10"/>
-      <c r="R26" s="10"/>
-      <c r="S26" s="10"/>
-      <c r="T26" s="15"/>
+      <c r="H26" s="8"/>
+      <c r="I26" s="8"/>
+      <c r="J26" s="8"/>
+      <c r="K26" s="8"/>
+      <c r="L26" s="8"/>
+      <c r="M26" s="8"/>
+      <c r="N26" s="8"/>
+      <c r="O26" s="8"/>
+      <c r="P26" s="8"/>
+      <c r="Q26" s="8"/>
+      <c r="R26" s="8"/>
+      <c r="S26" s="8"/>
+      <c r="T26" s="30"/>
     </row>
     <row r="27" spans="1:20" s="18" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A27" s="28" t="s">
-        <v>13</v>
-      </c>
+      <c r="A27" s="5"/>
       <c r="B27" s="5"/>
       <c r="C27" s="5"/>
       <c r="D27" s="5"/>
       <c r="E27" s="5"/>
-      <c r="F27" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="G27" s="5" t="s">
-        <v>25</v>
-      </c>
+      <c r="F27" s="1"/>
+      <c r="G27" s="5"/>
       <c r="H27" s="5"/>
       <c r="I27" s="5"/>
       <c r="J27" s="5"/>
@@ -2758,91 +2704,57 @@
       <c r="Q27" s="5"/>
       <c r="R27" s="5"/>
       <c r="S27" s="5"/>
-      <c r="T27" s="17"/>
-    </row>
-    <row r="28" spans="1:20" s="18" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="28" t="s">
-        <v>14</v>
-      </c>
-      <c r="B28" s="5"/>
-      <c r="C28" s="5"/>
-      <c r="D28" s="5"/>
-      <c r="E28" s="5"/>
-      <c r="F28" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="G28" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="H28" s="5"/>
-      <c r="I28" s="5"/>
-      <c r="J28" s="5"/>
-      <c r="K28" s="5"/>
-      <c r="L28" s="5"/>
-      <c r="M28" s="5"/>
-      <c r="N28" s="5"/>
-      <c r="O28" s="5"/>
-      <c r="P28" s="5"/>
-      <c r="Q28" s="5"/>
-      <c r="R28" s="5"/>
-      <c r="S28" s="5"/>
-      <c r="T28" s="17"/>
-    </row>
-    <row r="29" spans="1:20" s="18" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="29" t="s">
-        <v>15</v>
-      </c>
-      <c r="B29" s="8"/>
-      <c r="C29" s="8"/>
-      <c r="D29" s="8"/>
-      <c r="E29" s="8"/>
-      <c r="F29" s="21" t="s">
-        <v>8</v>
-      </c>
-      <c r="G29" s="8" t="s">
-        <v>50</v>
-      </c>
-      <c r="H29" s="8"/>
-      <c r="I29" s="8"/>
-      <c r="J29" s="8"/>
-      <c r="K29" s="8"/>
-      <c r="L29" s="8"/>
-      <c r="M29" s="8"/>
-      <c r="N29" s="8"/>
-      <c r="O29" s="8"/>
-      <c r="P29" s="8"/>
-      <c r="Q29" s="8"/>
-      <c r="R29" s="8"/>
-      <c r="S29" s="8"/>
-      <c r="T29" s="30"/>
-    </row>
-    <row r="30" spans="1:20" s="18" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="5"/>
-      <c r="B30" s="5"/>
-      <c r="C30" s="5"/>
-      <c r="D30" s="5"/>
-      <c r="E30" s="5"/>
-      <c r="F30" s="1"/>
-      <c r="G30" s="5"/>
-      <c r="H30" s="5"/>
-      <c r="I30" s="5"/>
-      <c r="J30" s="5"/>
-      <c r="K30" s="5"/>
-      <c r="L30" s="5"/>
-      <c r="M30" s="5"/>
-      <c r="N30" s="5"/>
-      <c r="O30" s="5"/>
-      <c r="P30" s="5"/>
-      <c r="Q30" s="5"/>
-      <c r="R30" s="5"/>
-      <c r="S30" s="5"/>
-      <c r="T30" s="5"/>
+      <c r="T27" s="5"/>
+    </row>
+    <row r="28" spans="1:20" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A28" s="37" t="s">
+        <v>29</v>
+      </c>
+      <c r="B28" s="37"/>
+      <c r="C28" s="37"/>
+      <c r="D28" s="37"/>
+      <c r="E28" s="37"/>
+      <c r="F28" s="37"/>
+      <c r="G28" s="37"/>
+      <c r="H28" s="37"/>
+      <c r="I28" s="37"/>
+      <c r="J28" s="37"/>
+    </row>
+    <row r="29" spans="1:20" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A29" s="37"/>
+      <c r="B29" s="37"/>
+      <c r="C29" s="37"/>
+      <c r="D29" s="37"/>
+      <c r="E29" s="37"/>
+      <c r="F29" s="37"/>
+      <c r="G29" s="37"/>
+      <c r="H29" s="37"/>
+      <c r="I29" s="37"/>
+      <c r="J29" s="37"/>
+    </row>
+    <row r="30" spans="1:20" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A30" s="38">
+        <v>1</v>
+      </c>
+      <c r="B30" s="37" t="s">
+        <v>30</v>
+      </c>
+      <c r="C30" s="37"/>
+      <c r="D30" s="37"/>
+      <c r="E30" s="37"/>
+      <c r="F30" s="37"/>
+      <c r="G30" s="37"/>
+      <c r="H30" s="37"/>
+      <c r="I30" s="37"/>
+      <c r="J30" s="37"/>
     </row>
     <row r="31" spans="1:20" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A31" s="37" t="s">
-        <v>29</v>
-      </c>
-      <c r="B31" s="37"/>
+      <c r="A31" s="38">
+        <v>2</v>
+      </c>
+      <c r="B31" s="37" t="s">
+        <v>31</v>
+      </c>
       <c r="C31" s="37"/>
       <c r="D31" s="37"/>
       <c r="E31" s="37"/>
@@ -2853,8 +2765,12 @@
       <c r="J31" s="37"/>
     </row>
     <row r="32" spans="1:20" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A32" s="37"/>
-      <c r="B32" s="37"/>
+      <c r="A32" s="38">
+        <v>3</v>
+      </c>
+      <c r="B32" s="37" t="s">
+        <v>32</v>
+      </c>
       <c r="C32" s="37"/>
       <c r="D32" s="37"/>
       <c r="E32" s="37"/>
@@ -2865,11 +2781,9 @@
       <c r="J32" s="37"/>
     </row>
     <row r="33" spans="1:20" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A33" s="38">
-        <v>1</v>
-      </c>
+      <c r="A33" s="37"/>
       <c r="B33" s="37" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C33" s="37"/>
       <c r="D33" s="37"/>
@@ -2880,65 +2794,89 @@
       <c r="I33" s="37"/>
       <c r="J33" s="37"/>
     </row>
-    <row r="34" spans="1:20" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A34" s="38">
-        <v>2</v>
-      </c>
-      <c r="B34" s="37" t="s">
-        <v>31</v>
-      </c>
-      <c r="C34" s="37"/>
-      <c r="D34" s="37"/>
-      <c r="E34" s="37"/>
-      <c r="F34" s="37"/>
-      <c r="G34" s="37"/>
-      <c r="H34" s="37"/>
-      <c r="I34" s="37"/>
-      <c r="J34" s="37"/>
-    </row>
-    <row r="35" spans="1:20" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A35" s="38">
-        <v>3</v>
-      </c>
-      <c r="B35" s="37" t="s">
-        <v>32</v>
-      </c>
-      <c r="C35" s="37"/>
-      <c r="D35" s="37"/>
-      <c r="E35" s="37"/>
-      <c r="F35" s="37"/>
-      <c r="G35" s="37"/>
-      <c r="H35" s="37"/>
-      <c r="I35" s="37"/>
-      <c r="J35" s="37"/>
-    </row>
-    <row r="36" spans="1:20" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A36" s="37"/>
-      <c r="B36" s="37" t="s">
-        <v>28</v>
-      </c>
-      <c r="C36" s="37"/>
-      <c r="D36" s="37"/>
-      <c r="E36" s="37"/>
-      <c r="F36" s="37"/>
-      <c r="G36" s="37"/>
-      <c r="H36" s="37"/>
-      <c r="I36" s="37"/>
-      <c r="J36" s="37"/>
+    <row r="34" spans="1:20" s="18" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A34" s="5"/>
+      <c r="B34" s="5"/>
+      <c r="C34" s="5"/>
+      <c r="D34" s="5"/>
+      <c r="E34" s="5"/>
+      <c r="F34" s="1"/>
+      <c r="G34" s="5"/>
+      <c r="H34" s="5"/>
+      <c r="I34" s="5"/>
+      <c r="J34" s="5"/>
+      <c r="K34" s="5"/>
+      <c r="L34" s="5"/>
+      <c r="M34" s="5"/>
+      <c r="N34" s="5"/>
+      <c r="O34" s="5"/>
+      <c r="P34" s="5"/>
+      <c r="Q34" s="5"/>
+      <c r="R34" s="5"/>
+      <c r="S34" s="5"/>
+      <c r="T34" s="5"/>
+    </row>
+    <row r="35" spans="1:20" s="18" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A35" s="5"/>
+      <c r="B35" s="5"/>
+      <c r="C35" s="5"/>
+      <c r="D35" s="5"/>
+      <c r="E35" s="5"/>
+      <c r="F35" s="1"/>
+      <c r="G35" s="5"/>
+      <c r="H35" s="5"/>
+      <c r="I35" s="5"/>
+      <c r="J35" s="5"/>
+      <c r="K35" s="5"/>
+      <c r="L35" s="5"/>
+      <c r="M35" s="5"/>
+      <c r="N35" s="5"/>
+      <c r="O35" s="5"/>
+      <c r="P35" s="5"/>
+      <c r="Q35" s="5"/>
+      <c r="R35" s="5"/>
+      <c r="S35" s="5"/>
+      <c r="T35" s="5"/>
+    </row>
+    <row r="36" spans="1:20" s="18" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A36" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="B36" s="5"/>
+      <c r="C36" s="5"/>
+      <c r="D36" s="5"/>
+      <c r="E36" s="7"/>
+      <c r="F36" s="7"/>
+      <c r="G36" s="7"/>
+      <c r="H36" s="7"/>
+      <c r="I36" s="7"/>
+      <c r="J36" s="7"/>
+      <c r="K36" s="7"/>
+      <c r="L36" s="7"/>
+      <c r="M36" s="5"/>
+      <c r="N36" s="5"/>
+      <c r="O36" s="5"/>
+      <c r="P36" s="5"/>
+      <c r="Q36" s="5"/>
+      <c r="R36" s="5"/>
+      <c r="S36" s="5"/>
+      <c r="T36" s="5"/>
     </row>
     <row r="37" spans="1:20" s="18" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A37" s="5"/>
+      <c r="A37" s="5" t="s">
+        <v>21</v>
+      </c>
       <c r="B37" s="5"/>
       <c r="C37" s="5"/>
       <c r="D37" s="5"/>
-      <c r="E37" s="5"/>
+      <c r="E37" s="1"/>
       <c r="F37" s="1"/>
-      <c r="G37" s="5"/>
-      <c r="H37" s="5"/>
-      <c r="I37" s="5"/>
-      <c r="J37" s="5"/>
-      <c r="K37" s="5"/>
-      <c r="L37" s="5"/>
+      <c r="G37" s="1"/>
+      <c r="H37" s="1"/>
+      <c r="I37" s="1"/>
+      <c r="J37" s="1"/>
+      <c r="K37" s="1"/>
+      <c r="L37" s="1"/>
       <c r="M37" s="5"/>
       <c r="N37" s="5"/>
       <c r="O37" s="5"/>
@@ -2953,14 +2891,14 @@
       <c r="B38" s="5"/>
       <c r="C38" s="5"/>
       <c r="D38" s="5"/>
-      <c r="E38" s="5"/>
-      <c r="F38" s="1"/>
-      <c r="G38" s="5"/>
-      <c r="H38" s="5"/>
-      <c r="I38" s="5"/>
-      <c r="J38" s="5"/>
-      <c r="K38" s="5"/>
-      <c r="L38" s="5"/>
+      <c r="E38" s="7"/>
+      <c r="F38" s="7"/>
+      <c r="G38" s="7"/>
+      <c r="H38" s="7"/>
+      <c r="I38" s="7"/>
+      <c r="J38" s="7"/>
+      <c r="K38" s="7"/>
+      <c r="L38" s="7"/>
       <c r="M38" s="5"/>
       <c r="N38" s="5"/>
       <c r="O38" s="5"/>
@@ -2971,8 +2909,8 @@
       <c r="T38" s="5"/>
     </row>
     <row r="39" spans="1:20" s="18" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A39" s="11" t="s">
-        <v>20</v>
+      <c r="A39" s="36" t="s">
+        <v>27</v>
       </c>
       <c r="B39" s="5"/>
       <c r="C39" s="5"/>
@@ -2995,20 +2933,18 @@
       <c r="T39" s="5"/>
     </row>
     <row r="40" spans="1:20" s="18" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A40" s="5" t="s">
-        <v>21</v>
-      </c>
+      <c r="A40" s="5"/>
       <c r="B40" s="5"/>
       <c r="C40" s="5"/>
       <c r="D40" s="5"/>
-      <c r="E40" s="1"/>
-      <c r="F40" s="1"/>
-      <c r="G40" s="1"/>
-      <c r="H40" s="1"/>
-      <c r="I40" s="1"/>
-      <c r="J40" s="1"/>
-      <c r="K40" s="1"/>
-      <c r="L40" s="1"/>
+      <c r="E40" s="5"/>
+      <c r="F40" s="5"/>
+      <c r="G40" s="5"/>
+      <c r="H40" s="5"/>
+      <c r="I40" s="5"/>
+      <c r="J40" s="5"/>
+      <c r="K40" s="5"/>
+      <c r="L40" s="5"/>
       <c r="M40" s="5"/>
       <c r="N40" s="5"/>
       <c r="O40" s="5"/>
@@ -3019,18 +2955,20 @@
       <c r="T40" s="5"/>
     </row>
     <row r="41" spans="1:20" s="18" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A41" s="5"/>
-      <c r="B41" s="5"/>
-      <c r="C41" s="5"/>
-      <c r="D41" s="5"/>
-      <c r="E41" s="7"/>
-      <c r="F41" s="7"/>
-      <c r="G41" s="7"/>
-      <c r="H41" s="7"/>
-      <c r="I41" s="7"/>
-      <c r="J41" s="7"/>
-      <c r="K41" s="7"/>
-      <c r="L41" s="7"/>
+      <c r="A41" s="48" t="s">
+        <v>26</v>
+      </c>
+      <c r="B41" s="48"/>
+      <c r="C41" s="48"/>
+      <c r="D41" s="48"/>
+      <c r="E41" s="48"/>
+      <c r="F41" s="48"/>
+      <c r="G41" s="5"/>
+      <c r="H41" s="5"/>
+      <c r="I41" s="5"/>
+      <c r="J41" s="11"/>
+      <c r="K41" s="11"/>
+      <c r="L41" s="11"/>
       <c r="M41" s="5"/>
       <c r="N41" s="5"/>
       <c r="O41" s="5"/>
@@ -3041,20 +2979,20 @@
       <c r="T41" s="5"/>
     </row>
     <row r="42" spans="1:20" s="18" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A42" s="36" t="s">
-        <v>27</v>
-      </c>
-      <c r="B42" s="5"/>
-      <c r="C42" s="5"/>
-      <c r="D42" s="5"/>
-      <c r="E42" s="7"/>
-      <c r="F42" s="7"/>
-      <c r="G42" s="7"/>
-      <c r="H42" s="7"/>
-      <c r="I42" s="7"/>
-      <c r="J42" s="7"/>
-      <c r="K42" s="7"/>
-      <c r="L42" s="7"/>
+      <c r="A42" s="31" t="s">
+        <v>23</v>
+      </c>
+      <c r="B42" s="31"/>
+      <c r="C42" s="31"/>
+      <c r="D42" s="31"/>
+      <c r="E42" s="5"/>
+      <c r="F42" s="5"/>
+      <c r="G42" s="5"/>
+      <c r="H42" s="5"/>
+      <c r="I42" s="5"/>
+      <c r="J42" s="11"/>
+      <c r="K42" s="11"/>
+      <c r="L42" s="11"/>
       <c r="M42" s="5"/>
       <c r="N42" s="5"/>
       <c r="O42" s="5"/>
@@ -3087,20 +3025,18 @@
       <c r="T43" s="5"/>
     </row>
     <row r="44" spans="1:20" s="18" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A44" s="68" t="s">
-        <v>26</v>
-      </c>
-      <c r="B44" s="68"/>
-      <c r="C44" s="68"/>
-      <c r="D44" s="68"/>
-      <c r="E44" s="68"/>
-      <c r="F44" s="68"/>
+      <c r="A44" s="5"/>
+      <c r="B44" s="5"/>
+      <c r="C44" s="5"/>
+      <c r="D44" s="5"/>
+      <c r="E44" s="5"/>
+      <c r="F44" s="5"/>
       <c r="G44" s="5"/>
       <c r="H44" s="5"/>
       <c r="I44" s="5"/>
-      <c r="J44" s="11"/>
-      <c r="K44" s="11"/>
-      <c r="L44" s="11"/>
+      <c r="J44" s="5"/>
+      <c r="K44" s="5"/>
+      <c r="L44" s="5"/>
       <c r="M44" s="5"/>
       <c r="N44" s="5"/>
       <c r="O44" s="5"/>
@@ -3111,20 +3047,18 @@
       <c r="T44" s="5"/>
     </row>
     <row r="45" spans="1:20" s="18" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A45" s="31" t="s">
-        <v>23</v>
-      </c>
-      <c r="B45" s="31"/>
-      <c r="C45" s="31"/>
-      <c r="D45" s="31"/>
+      <c r="A45" s="5"/>
+      <c r="B45" s="5"/>
+      <c r="C45" s="5"/>
+      <c r="D45" s="5"/>
       <c r="E45" s="5"/>
       <c r="F45" s="5"/>
       <c r="G45" s="5"/>
       <c r="H45" s="5"/>
       <c r="I45" s="5"/>
-      <c r="J45" s="11"/>
-      <c r="K45" s="11"/>
-      <c r="L45" s="11"/>
+      <c r="J45" s="5"/>
+      <c r="K45" s="5"/>
+      <c r="L45" s="5"/>
       <c r="M45" s="5"/>
       <c r="N45" s="5"/>
       <c r="O45" s="5"/>
@@ -3161,8 +3095,8 @@
       <c r="B47" s="5"/>
       <c r="C47" s="5"/>
       <c r="D47" s="5"/>
-      <c r="E47" s="5"/>
-      <c r="F47" s="5"/>
+      <c r="E47" s="34"/>
+      <c r="F47" s="34"/>
       <c r="G47" s="5"/>
       <c r="H47" s="5"/>
       <c r="I47" s="5"/>
@@ -3183,8 +3117,8 @@
       <c r="B48" s="5"/>
       <c r="C48" s="5"/>
       <c r="D48" s="5"/>
-      <c r="E48" s="5"/>
-      <c r="F48" s="5"/>
+      <c r="E48" s="7"/>
+      <c r="F48" s="7"/>
       <c r="G48" s="5"/>
       <c r="H48" s="5"/>
       <c r="I48" s="5"/>
@@ -3205,8 +3139,8 @@
       <c r="B49" s="5"/>
       <c r="C49" s="5"/>
       <c r="D49" s="5"/>
-      <c r="E49" s="5"/>
-      <c r="F49" s="5"/>
+      <c r="E49" s="31"/>
+      <c r="F49" s="31"/>
       <c r="G49" s="5"/>
       <c r="H49" s="5"/>
       <c r="I49" s="5"/>
@@ -3227,8 +3161,8 @@
       <c r="B50" s="5"/>
       <c r="C50" s="5"/>
       <c r="D50" s="5"/>
-      <c r="E50" s="34"/>
-      <c r="F50" s="34"/>
+      <c r="E50" s="5"/>
+      <c r="F50" s="5"/>
       <c r="G50" s="5"/>
       <c r="H50" s="5"/>
       <c r="I50" s="5"/>
@@ -3249,8 +3183,8 @@
       <c r="B51" s="5"/>
       <c r="C51" s="5"/>
       <c r="D51" s="5"/>
-      <c r="E51" s="7"/>
-      <c r="F51" s="7"/>
+      <c r="E51" s="5"/>
+      <c r="F51" s="5"/>
       <c r="G51" s="5"/>
       <c r="H51" s="5"/>
       <c r="I51" s="5"/>
@@ -3271,8 +3205,8 @@
       <c r="B52" s="5"/>
       <c r="C52" s="5"/>
       <c r="D52" s="5"/>
-      <c r="E52" s="31"/>
-      <c r="F52" s="31"/>
+      <c r="E52" s="5"/>
+      <c r="F52" s="5"/>
       <c r="G52" s="5"/>
       <c r="H52" s="5"/>
       <c r="I52" s="5"/>
@@ -3332,29 +3266,7 @@
       <c r="S54" s="5"/>
       <c r="T54" s="5"/>
     </row>
-    <row r="55" spans="1:20" s="18" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A55" s="5"/>
-      <c r="B55" s="5"/>
-      <c r="C55" s="5"/>
-      <c r="D55" s="5"/>
-      <c r="E55" s="5"/>
-      <c r="F55" s="5"/>
-      <c r="G55" s="5"/>
-      <c r="H55" s="5"/>
-      <c r="I55" s="5"/>
-      <c r="J55" s="5"/>
-      <c r="K55" s="5"/>
-      <c r="L55" s="5"/>
-      <c r="M55" s="5"/>
-      <c r="N55" s="5"/>
-      <c r="O55" s="5"/>
-      <c r="P55" s="5"/>
-      <c r="Q55" s="5"/>
-      <c r="R55" s="5"/>
-      <c r="S55" s="5"/>
-      <c r="T55" s="5"/>
-    </row>
-    <row r="56" spans="1:20" s="18" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:20" s="26" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A56" s="5"/>
       <c r="B56" s="5"/>
       <c r="C56" s="5"/>
@@ -3376,7 +3288,7 @@
       <c r="S56" s="5"/>
       <c r="T56" s="5"/>
     </row>
-    <row r="57" spans="1:20" s="18" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:20" s="26" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A57" s="5"/>
       <c r="B57" s="5"/>
       <c r="C57" s="5"/>
@@ -3398,7 +3310,29 @@
       <c r="S57" s="5"/>
       <c r="T57" s="5"/>
     </row>
-    <row r="59" spans="1:20" s="26" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:20" s="26" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A58" s="5"/>
+      <c r="B58" s="5"/>
+      <c r="C58" s="5"/>
+      <c r="D58" s="5"/>
+      <c r="E58" s="5"/>
+      <c r="F58" s="5"/>
+      <c r="G58" s="5"/>
+      <c r="H58" s="5"/>
+      <c r="I58" s="5"/>
+      <c r="J58" s="5"/>
+      <c r="K58" s="5"/>
+      <c r="L58" s="5"/>
+      <c r="M58" s="5"/>
+      <c r="N58" s="5"/>
+      <c r="O58" s="5"/>
+      <c r="P58" s="5"/>
+      <c r="Q58" s="5"/>
+      <c r="R58" s="5"/>
+      <c r="S58" s="5"/>
+      <c r="T58" s="5"/>
+    </row>
+    <row r="59" spans="1:20" s="26" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A59" s="5"/>
       <c r="B59" s="5"/>
       <c r="C59" s="5"/>
@@ -3420,7 +3354,7 @@
       <c r="S59" s="5"/>
       <c r="T59" s="5"/>
     </row>
-    <row r="60" spans="1:20" s="26" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:20" s="26" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A60" s="5"/>
       <c r="B60" s="5"/>
       <c r="C60" s="5"/>
@@ -3464,7 +3398,7 @@
       <c r="S61" s="5"/>
       <c r="T61" s="5"/>
     </row>
-    <row r="62" spans="1:20" s="26" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:20" s="26" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A62" s="5"/>
       <c r="B62" s="5"/>
       <c r="C62" s="5"/>
@@ -3530,50 +3464,6 @@
       <c r="S64" s="5"/>
       <c r="T64" s="5"/>
     </row>
-    <row r="65" spans="1:23" s="26" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A65" s="5"/>
-      <c r="B65" s="5"/>
-      <c r="C65" s="5"/>
-      <c r="D65" s="5"/>
-      <c r="E65" s="5"/>
-      <c r="F65" s="5"/>
-      <c r="G65" s="5"/>
-      <c r="H65" s="5"/>
-      <c r="I65" s="5"/>
-      <c r="J65" s="5"/>
-      <c r="K65" s="5"/>
-      <c r="L65" s="5"/>
-      <c r="M65" s="5"/>
-      <c r="N65" s="5"/>
-      <c r="O65" s="5"/>
-      <c r="P65" s="5"/>
-      <c r="Q65" s="5"/>
-      <c r="R65" s="5"/>
-      <c r="S65" s="5"/>
-      <c r="T65" s="5"/>
-    </row>
-    <row r="66" spans="1:23" s="26" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A66" s="5"/>
-      <c r="B66" s="5"/>
-      <c r="C66" s="5"/>
-      <c r="D66" s="5"/>
-      <c r="E66" s="5"/>
-      <c r="F66" s="5"/>
-      <c r="G66" s="5"/>
-      <c r="H66" s="5"/>
-      <c r="I66" s="5"/>
-      <c r="J66" s="5"/>
-      <c r="K66" s="5"/>
-      <c r="L66" s="5"/>
-      <c r="M66" s="5"/>
-      <c r="N66" s="5"/>
-      <c r="O66" s="5"/>
-      <c r="P66" s="5"/>
-      <c r="Q66" s="5"/>
-      <c r="R66" s="5"/>
-      <c r="S66" s="5"/>
-      <c r="T66" s="5"/>
-    </row>
     <row r="67" spans="1:23" s="26" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A67" s="5"/>
       <c r="B67" s="5"/>
@@ -3596,51 +3486,51 @@
       <c r="S67" s="5"/>
       <c r="T67" s="5"/>
     </row>
-    <row r="70" spans="1:23" s="26" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A70" s="5"/>
-      <c r="B70" s="5"/>
-      <c r="C70" s="5"/>
-      <c r="D70" s="5"/>
-      <c r="E70" s="5"/>
-      <c r="F70" s="5"/>
-      <c r="G70" s="5"/>
-      <c r="H70" s="5"/>
-      <c r="I70" s="5"/>
-      <c r="J70" s="5"/>
-      <c r="K70" s="5"/>
-      <c r="L70" s="5"/>
-      <c r="M70" s="5"/>
-      <c r="N70" s="5"/>
-      <c r="O70" s="5"/>
-      <c r="P70" s="5"/>
-      <c r="Q70" s="5"/>
-      <c r="R70" s="5"/>
-      <c r="S70" s="5"/>
-      <c r="T70" s="5"/>
-    </row>
-    <row r="71" spans="1:23" s="26" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A71" s="5"/>
-      <c r="B71" s="5"/>
-      <c r="C71" s="5"/>
-      <c r="D71" s="5"/>
-      <c r="E71" s="5"/>
-      <c r="F71" s="5"/>
-      <c r="G71" s="5"/>
-      <c r="H71" s="5"/>
-      <c r="I71" s="5"/>
-      <c r="J71" s="5"/>
-      <c r="K71" s="5"/>
-      <c r="L71" s="5"/>
-      <c r="M71" s="5"/>
-      <c r="N71" s="5"/>
-      <c r="O71" s="5"/>
-      <c r="P71" s="5"/>
-      <c r="Q71" s="5"/>
-      <c r="R71" s="5"/>
-      <c r="S71" s="5"/>
-      <c r="T71" s="5"/>
-    </row>
-    <row r="72" spans="1:23" s="26" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:23" s="26" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A68" s="5"/>
+      <c r="B68" s="5"/>
+      <c r="C68" s="5"/>
+      <c r="D68" s="5"/>
+      <c r="E68" s="5"/>
+      <c r="F68" s="5"/>
+      <c r="G68" s="5"/>
+      <c r="H68" s="5"/>
+      <c r="I68" s="5"/>
+      <c r="J68" s="5"/>
+      <c r="K68" s="5"/>
+      <c r="L68" s="5"/>
+      <c r="M68" s="5"/>
+      <c r="N68" s="5"/>
+      <c r="O68" s="5"/>
+      <c r="P68" s="5"/>
+      <c r="Q68" s="5"/>
+      <c r="R68" s="5"/>
+      <c r="S68" s="5"/>
+      <c r="T68" s="5"/>
+    </row>
+    <row r="69" spans="1:23" s="26" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A69" s="5"/>
+      <c r="B69" s="5"/>
+      <c r="C69" s="5"/>
+      <c r="D69" s="5"/>
+      <c r="E69" s="5"/>
+      <c r="F69" s="5"/>
+      <c r="G69" s="5"/>
+      <c r="H69" s="5"/>
+      <c r="I69" s="5"/>
+      <c r="J69" s="5"/>
+      <c r="K69" s="5"/>
+      <c r="L69" s="5"/>
+      <c r="M69" s="5"/>
+      <c r="N69" s="5"/>
+      <c r="O69" s="5"/>
+      <c r="P69" s="5"/>
+      <c r="Q69" s="5"/>
+      <c r="R69" s="5"/>
+      <c r="S69" s="5"/>
+      <c r="T69" s="5"/>
+    </row>
+    <row r="72" spans="1:23" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A72" s="5"/>
       <c r="B72" s="5"/>
       <c r="C72" s="5"/>
@@ -3661,95 +3551,61 @@
       <c r="R72" s="5"/>
       <c r="S72" s="5"/>
       <c r="T72" s="5"/>
-    </row>
-    <row r="75" spans="1:23" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A75" s="5"/>
-      <c r="B75" s="5"/>
-      <c r="C75" s="5"/>
-      <c r="D75" s="5"/>
-      <c r="E75" s="5"/>
-      <c r="F75" s="5"/>
-      <c r="G75" s="5"/>
-      <c r="H75" s="5"/>
-      <c r="I75" s="5"/>
-      <c r="J75" s="5"/>
-      <c r="K75" s="5"/>
-      <c r="L75" s="5"/>
-      <c r="M75" s="5"/>
-      <c r="N75" s="5"/>
-      <c r="O75" s="5"/>
-      <c r="P75" s="5"/>
-      <c r="Q75" s="5"/>
-      <c r="R75" s="5"/>
-      <c r="S75" s="5"/>
-      <c r="T75" s="5"/>
-      <c r="U75" s="32"/>
-      <c r="V75" s="32"/>
-      <c r="W75" s="32"/>
-    </row>
-    <row r="76" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="U76" s="33"/>
-      <c r="V76" s="33"/>
-      <c r="W76" s="33"/>
+      <c r="U72" s="32"/>
+      <c r="V72" s="32"/>
+      <c r="W72" s="32"/>
+    </row>
+    <row r="73" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="U73" s="33"/>
+      <c r="V73" s="33"/>
+      <c r="W73" s="33"/>
     </row>
   </sheetData>
-  <mergeCells count="56">
-    <mergeCell ref="H25:L25"/>
-    <mergeCell ref="M25:P25"/>
-    <mergeCell ref="Q25:T25"/>
-    <mergeCell ref="E25:G25"/>
-    <mergeCell ref="A25:B25"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="E22:G22"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="M23:P23"/>
-    <mergeCell ref="M24:P24"/>
-    <mergeCell ref="H23:L23"/>
-    <mergeCell ref="H24:L24"/>
-    <mergeCell ref="A24:B24"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="C24:D24"/>
-    <mergeCell ref="E23:G23"/>
-    <mergeCell ref="E24:G24"/>
-    <mergeCell ref="Q22:T22"/>
-    <mergeCell ref="Q23:T23"/>
-    <mergeCell ref="K14:N14"/>
-    <mergeCell ref="A44:F44"/>
-    <mergeCell ref="Q24:T24"/>
-    <mergeCell ref="C17:D18"/>
-    <mergeCell ref="E17:G18"/>
-    <mergeCell ref="M17:P18"/>
-    <mergeCell ref="N15:T15"/>
-    <mergeCell ref="A17:B18"/>
-    <mergeCell ref="Q17:T18"/>
-    <mergeCell ref="H17:L18"/>
+  <mergeCells count="44">
+    <mergeCell ref="Q19:T19"/>
+    <mergeCell ref="M20:P20"/>
+    <mergeCell ref="Q20:T20"/>
+    <mergeCell ref="E18:G18"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="C18:D18"/>
     <mergeCell ref="A20:B20"/>
-    <mergeCell ref="E20:G20"/>
-    <mergeCell ref="M22:P22"/>
-    <mergeCell ref="H22:L22"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="A19:B19"/>
     <mergeCell ref="C19:D19"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="A2:T2"/>
     <mergeCell ref="A3:T3"/>
     <mergeCell ref="A4:T4"/>
     <mergeCell ref="A5:T5"/>
-    <mergeCell ref="A6:T6"/>
-    <mergeCell ref="N12:S12"/>
+    <mergeCell ref="N11:S11"/>
+    <mergeCell ref="E20:G20"/>
+    <mergeCell ref="H20:L20"/>
+    <mergeCell ref="Q18:T18"/>
+    <mergeCell ref="M18:P18"/>
+    <mergeCell ref="H18:L18"/>
+    <mergeCell ref="H19:L19"/>
+    <mergeCell ref="M19:P19"/>
+    <mergeCell ref="K13:N13"/>
+    <mergeCell ref="A41:F41"/>
+    <mergeCell ref="C16:D17"/>
+    <mergeCell ref="E16:G17"/>
+    <mergeCell ref="M16:P17"/>
+    <mergeCell ref="N14:T14"/>
+    <mergeCell ref="A16:B17"/>
+    <mergeCell ref="Q16:T17"/>
+    <mergeCell ref="H16:L17"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="E19:G19"/>
+    <mergeCell ref="M21:P21"/>
+    <mergeCell ref="H21:L21"/>
     <mergeCell ref="E21:G21"/>
-    <mergeCell ref="H21:L21"/>
-    <mergeCell ref="Q19:T19"/>
-    <mergeCell ref="M19:P19"/>
-    <mergeCell ref="H19:L19"/>
-    <mergeCell ref="H20:L20"/>
-    <mergeCell ref="M20:P20"/>
-    <mergeCell ref="Q20:T20"/>
-    <mergeCell ref="M21:P21"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="H22:L22"/>
+    <mergeCell ref="M22:P22"/>
+    <mergeCell ref="Q22:T22"/>
+    <mergeCell ref="E22:G22"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="C22:D22"/>
     <mergeCell ref="Q21:T21"/>
-    <mergeCell ref="E19:G19"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <printOptions horizontalCentered="1"/>
